--- a/data/2FEB_25_26/players_25_26_2FEB_games.xlsx
+++ b/data/2FEB_25_26/players_25_26_2FEB_games.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI323"/>
+  <dimension ref="A1:AI337"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38921,6 +38921,1672 @@
       </c>
       <c r="AI323" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>24</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>200</v>
+      </c>
+      <c r="F324" t="n">
+        <v>81</v>
+      </c>
+      <c r="G324" t="n">
+        <v>23</v>
+      </c>
+      <c r="H324" t="n">
+        <v>34</v>
+      </c>
+      <c r="I324" t="n">
+        <v>8</v>
+      </c>
+      <c r="J324" t="n">
+        <v>24</v>
+      </c>
+      <c r="K324" t="n">
+        <v>11</v>
+      </c>
+      <c r="L324" t="n">
+        <v>13</v>
+      </c>
+      <c r="M324" t="n">
+        <v>7</v>
+      </c>
+      <c r="N324" t="n">
+        <v>22</v>
+      </c>
+      <c r="O324" t="n">
+        <v>15</v>
+      </c>
+      <c r="P324" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>10</v>
+      </c>
+      <c r="R324" t="n">
+        <v>24</v>
+      </c>
+      <c r="S324" t="n">
+        <v>18</v>
+      </c>
+      <c r="T324" t="n">
+        <v>3</v>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="V324" t="n">
+        <v>79</v>
+      </c>
+      <c r="W324" t="n">
+        <v>73.72</v>
+      </c>
+      <c r="X324" t="n">
+        <v>1.09875203472599</v>
+      </c>
+      <c r="Y324" t="n">
+        <v>66.72</v>
+      </c>
+      <c r="Z324" t="n">
+        <v>121.4028776978417</v>
+      </c>
+      <c r="AA324" t="n">
+        <v>0.9440726577437858</v>
+      </c>
+      <c r="AB324" t="n">
+        <v>107.2204125950054</v>
+      </c>
+      <c r="AC324" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AD324" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="AE324" t="n">
+        <v>0.5087719298245614</v>
+      </c>
+      <c r="AF324" t="n">
+        <v>14.18246510283632</v>
+      </c>
+      <c r="AG324" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="AH324" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="AI324" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>24</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>200</v>
+      </c>
+      <c r="F325" t="n">
+        <v>93</v>
+      </c>
+      <c r="G325" t="n">
+        <v>18</v>
+      </c>
+      <c r="H325" t="n">
+        <v>34</v>
+      </c>
+      <c r="I325" t="n">
+        <v>13</v>
+      </c>
+      <c r="J325" t="n">
+        <v>19</v>
+      </c>
+      <c r="K325" t="n">
+        <v>18</v>
+      </c>
+      <c r="L325" t="n">
+        <v>28</v>
+      </c>
+      <c r="M325" t="n">
+        <v>7</v>
+      </c>
+      <c r="N325" t="n">
+        <v>23</v>
+      </c>
+      <c r="O325" t="n">
+        <v>24</v>
+      </c>
+      <c r="P325" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>15</v>
+      </c>
+      <c r="R325" t="n">
+        <v>16</v>
+      </c>
+      <c r="S325" t="n">
+        <v>23</v>
+      </c>
+      <c r="T325" t="n">
+        <v>1</v>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>2487923</t>
+        </is>
+      </c>
+      <c r="V325" t="n">
+        <v>83</v>
+      </c>
+      <c r="W325" t="n">
+        <v>80.31999999999999</v>
+      </c>
+      <c r="X325" t="n">
+        <v>1.157868525896415</v>
+      </c>
+      <c r="Y325" t="n">
+        <v>73.31999999999999</v>
+      </c>
+      <c r="Z325" t="n">
+        <v>126.8412438625205</v>
+      </c>
+      <c r="AA325" t="n">
+        <v>0.8257063270990848</v>
+      </c>
+      <c r="AB325" t="n">
+        <v>104.3762575452716</v>
+      </c>
+      <c r="AC325" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="AD325" t="n">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="AE325" t="n">
+        <v>0.4411764705882353</v>
+      </c>
+      <c r="AF325" t="n">
+        <v>22.46498631724883</v>
+      </c>
+      <c r="AG325" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="AH325" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="AI325" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>24</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>200</v>
+      </c>
+      <c r="F326" t="n">
+        <v>58</v>
+      </c>
+      <c r="G326" t="n">
+        <v>16</v>
+      </c>
+      <c r="H326" t="n">
+        <v>37</v>
+      </c>
+      <c r="I326" t="n">
+        <v>6</v>
+      </c>
+      <c r="J326" t="n">
+        <v>32</v>
+      </c>
+      <c r="K326" t="n">
+        <v>8</v>
+      </c>
+      <c r="L326" t="n">
+        <v>18</v>
+      </c>
+      <c r="M326" t="n">
+        <v>17</v>
+      </c>
+      <c r="N326" t="n">
+        <v>25</v>
+      </c>
+      <c r="O326" t="n">
+        <v>6</v>
+      </c>
+      <c r="P326" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q326" t="n">
+        <v>10</v>
+      </c>
+      <c r="R326" t="n">
+        <v>20</v>
+      </c>
+      <c r="S326" t="n">
+        <v>22</v>
+      </c>
+      <c r="T326" t="n">
+        <v>2</v>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>2487926</t>
+        </is>
+      </c>
+      <c r="V326" t="n">
+        <v>70</v>
+      </c>
+      <c r="W326" t="n">
+        <v>86.92</v>
+      </c>
+      <c r="X326" t="n">
+        <v>0.6672802577082374</v>
+      </c>
+      <c r="Y326" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="Z326" t="n">
+        <v>82.95194508009153</v>
+      </c>
+      <c r="AA326" t="n">
+        <v>0.9039256198347108</v>
+      </c>
+      <c r="AB326" t="n">
+        <v>100.8064516129032</v>
+      </c>
+      <c r="AC326" t="n">
+        <v>0.3541666666666667</v>
+      </c>
+      <c r="AD326" t="n">
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="AE326" t="n">
+        <v>0.5185185185185185</v>
+      </c>
+      <c r="AF326" t="n">
+        <v>-17.8545065328117</v>
+      </c>
+      <c r="AG326" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="AH326" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="AI326" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>24</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>200</v>
+      </c>
+      <c r="F327" t="n">
+        <v>83</v>
+      </c>
+      <c r="G327" t="n">
+        <v>23</v>
+      </c>
+      <c r="H327" t="n">
+        <v>44</v>
+      </c>
+      <c r="I327" t="n">
+        <v>9</v>
+      </c>
+      <c r="J327" t="n">
+        <v>22</v>
+      </c>
+      <c r="K327" t="n">
+        <v>10</v>
+      </c>
+      <c r="L327" t="n">
+        <v>16</v>
+      </c>
+      <c r="M327" t="n">
+        <v>7</v>
+      </c>
+      <c r="N327" t="n">
+        <v>23</v>
+      </c>
+      <c r="O327" t="n">
+        <v>18</v>
+      </c>
+      <c r="P327" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>13</v>
+      </c>
+      <c r="R327" t="n">
+        <v>18</v>
+      </c>
+      <c r="S327" t="n">
+        <v>18</v>
+      </c>
+      <c r="T327" t="n">
+        <v>2</v>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="V327" t="n">
+        <v>81</v>
+      </c>
+      <c r="W327" t="n">
+        <v>86.03999999999999</v>
+      </c>
+      <c r="X327" t="n">
+        <v>0.9646675964667597</v>
+      </c>
+      <c r="Y327" t="n">
+        <v>79.03999999999999</v>
+      </c>
+      <c r="Z327" t="n">
+        <v>105.0101214574899</v>
+      </c>
+      <c r="AA327" t="n">
+        <v>0.8996001776988006</v>
+      </c>
+      <c r="AB327" t="n">
+        <v>106.5228826933193</v>
+      </c>
+      <c r="AC327" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="AD327" t="n">
+        <v>0.6216216216216216</v>
+      </c>
+      <c r="AE327" t="n">
+        <v>0.4347826086956522</v>
+      </c>
+      <c r="AF327" t="n">
+        <v>-1.51276123582943</v>
+      </c>
+      <c r="AG327" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH327" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="AI327" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>24</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>200</v>
+      </c>
+      <c r="F328" t="n">
+        <v>75</v>
+      </c>
+      <c r="G328" t="n">
+        <v>21</v>
+      </c>
+      <c r="H328" t="n">
+        <v>38</v>
+      </c>
+      <c r="I328" t="n">
+        <v>5</v>
+      </c>
+      <c r="J328" t="n">
+        <v>17</v>
+      </c>
+      <c r="K328" t="n">
+        <v>18</v>
+      </c>
+      <c r="L328" t="n">
+        <v>34</v>
+      </c>
+      <c r="M328" t="n">
+        <v>8</v>
+      </c>
+      <c r="N328" t="n">
+        <v>29</v>
+      </c>
+      <c r="O328" t="n">
+        <v>11</v>
+      </c>
+      <c r="P328" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q328" t="n">
+        <v>12</v>
+      </c>
+      <c r="R328" t="n">
+        <v>20</v>
+      </c>
+      <c r="S328" t="n">
+        <v>28</v>
+      </c>
+      <c r="T328" t="n">
+        <v>4</v>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="V328" t="n">
+        <v>70</v>
+      </c>
+      <c r="W328" t="n">
+        <v>81.96000000000001</v>
+      </c>
+      <c r="X328" t="n">
+        <v>0.9150805270863835</v>
+      </c>
+      <c r="Y328" t="n">
+        <v>73.96000000000001</v>
+      </c>
+      <c r="Z328" t="n">
+        <v>101.4061654948621</v>
+      </c>
+      <c r="AA328" t="n">
+        <v>0.7651945780498469</v>
+      </c>
+      <c r="AB328" t="n">
+        <v>90.34589571502323</v>
+      </c>
+      <c r="AC328" t="n">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="AD328" t="n">
+        <v>0.6744186046511628</v>
+      </c>
+      <c r="AE328" t="n">
+        <v>0.4743589743589743</v>
+      </c>
+      <c r="AF328" t="n">
+        <v>11.06026977983885</v>
+      </c>
+      <c r="AG328" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="AH328" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="AI328" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>24</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>225</v>
+      </c>
+      <c r="F329" t="n">
+        <v>86</v>
+      </c>
+      <c r="G329" t="n">
+        <v>18</v>
+      </c>
+      <c r="H329" t="n">
+        <v>33</v>
+      </c>
+      <c r="I329" t="n">
+        <v>9</v>
+      </c>
+      <c r="J329" t="n">
+        <v>25</v>
+      </c>
+      <c r="K329" t="n">
+        <v>23</v>
+      </c>
+      <c r="L329" t="n">
+        <v>31</v>
+      </c>
+      <c r="M329" t="n">
+        <v>7</v>
+      </c>
+      <c r="N329" t="n">
+        <v>21</v>
+      </c>
+      <c r="O329" t="n">
+        <v>12</v>
+      </c>
+      <c r="P329" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>13</v>
+      </c>
+      <c r="R329" t="n">
+        <v>22</v>
+      </c>
+      <c r="S329" t="n">
+        <v>25</v>
+      </c>
+      <c r="T329" t="n">
+        <v>0</v>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="V329" t="n">
+        <v>84</v>
+      </c>
+      <c r="W329" t="n">
+        <v>84.64</v>
+      </c>
+      <c r="X329" t="n">
+        <v>1.016068052930057</v>
+      </c>
+      <c r="Y329" t="n">
+        <v>77.64</v>
+      </c>
+      <c r="Z329" t="n">
+        <v>110.7676455435343</v>
+      </c>
+      <c r="AA329" t="n">
+        <v>0.9740259740259739</v>
+      </c>
+      <c r="AB329" t="n">
+        <v>102.1400778210117</v>
+      </c>
+      <c r="AC329" t="n">
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="AD329" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AE329" t="n">
+        <v>0.5185185185185185</v>
+      </c>
+      <c r="AF329" t="n">
+        <v>8.627567722522599</v>
+      </c>
+      <c r="AG329" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="AH329" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="AI329" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>24</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>200</v>
+      </c>
+      <c r="F330" t="n">
+        <v>70</v>
+      </c>
+      <c r="G330" t="n">
+        <v>16</v>
+      </c>
+      <c r="H330" t="n">
+        <v>29</v>
+      </c>
+      <c r="I330" t="n">
+        <v>7</v>
+      </c>
+      <c r="J330" t="n">
+        <v>26</v>
+      </c>
+      <c r="K330" t="n">
+        <v>17</v>
+      </c>
+      <c r="L330" t="n">
+        <v>26</v>
+      </c>
+      <c r="M330" t="n">
+        <v>8</v>
+      </c>
+      <c r="N330" t="n">
+        <v>31</v>
+      </c>
+      <c r="O330" t="n">
+        <v>11</v>
+      </c>
+      <c r="P330" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>11</v>
+      </c>
+      <c r="R330" t="n">
+        <v>22</v>
+      </c>
+      <c r="S330" t="n">
+        <v>19</v>
+      </c>
+      <c r="T330" t="n">
+        <v>4</v>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>2487926</t>
+        </is>
+      </c>
+      <c r="V330" t="n">
+        <v>58</v>
+      </c>
+      <c r="W330" t="n">
+        <v>77.44</v>
+      </c>
+      <c r="X330" t="n">
+        <v>0.9039256198347108</v>
+      </c>
+      <c r="Y330" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="Z330" t="n">
+        <v>100.8064516129032</v>
+      </c>
+      <c r="AA330" t="n">
+        <v>0.6672802577082374</v>
+      </c>
+      <c r="AB330" t="n">
+        <v>82.95194508009153</v>
+      </c>
+      <c r="AC330" t="n">
+        <v>0.2424242424242424</v>
+      </c>
+      <c r="AD330" t="n">
+        <v>0.6458333333333334</v>
+      </c>
+      <c r="AE330" t="n">
+        <v>0.4814814814814815</v>
+      </c>
+      <c r="AF330" t="n">
+        <v>17.8545065328117</v>
+      </c>
+      <c r="AG330" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="AH330" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="AI330" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>24</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>200</v>
+      </c>
+      <c r="F331" t="n">
+        <v>83</v>
+      </c>
+      <c r="G331" t="n">
+        <v>26</v>
+      </c>
+      <c r="H331" t="n">
+        <v>62</v>
+      </c>
+      <c r="I331" t="n">
+        <v>8</v>
+      </c>
+      <c r="J331" t="n">
+        <v>25</v>
+      </c>
+      <c r="K331" t="n">
+        <v>7</v>
+      </c>
+      <c r="L331" t="n">
+        <v>8</v>
+      </c>
+      <c r="M331" t="n">
+        <v>21</v>
+      </c>
+      <c r="N331" t="n">
+        <v>17</v>
+      </c>
+      <c r="O331" t="n">
+        <v>22</v>
+      </c>
+      <c r="P331" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>10</v>
+      </c>
+      <c r="R331" t="n">
+        <v>23</v>
+      </c>
+      <c r="S331" t="n">
+        <v>16</v>
+      </c>
+      <c r="T331" t="n">
+        <v>2</v>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>2487923</t>
+        </is>
+      </c>
+      <c r="V331" t="n">
+        <v>93</v>
+      </c>
+      <c r="W331" t="n">
+        <v>100.52</v>
+      </c>
+      <c r="X331" t="n">
+        <v>0.8257063270990848</v>
+      </c>
+      <c r="Y331" t="n">
+        <v>79.52</v>
+      </c>
+      <c r="Z331" t="n">
+        <v>104.3762575452716</v>
+      </c>
+      <c r="AA331" t="n">
+        <v>1.157868525896415</v>
+      </c>
+      <c r="AB331" t="n">
+        <v>126.8412438625205</v>
+      </c>
+      <c r="AC331" t="n">
+        <v>0.4772727272727273</v>
+      </c>
+      <c r="AD331" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="AE331" t="n">
+        <v>0.5588235294117647</v>
+      </c>
+      <c r="AF331" t="n">
+        <v>-22.46498631724883</v>
+      </c>
+      <c r="AG331" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="AH331" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="AI331" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>24</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>200</v>
+      </c>
+      <c r="F332" t="n">
+        <v>81</v>
+      </c>
+      <c r="G332" t="n">
+        <v>21</v>
+      </c>
+      <c r="H332" t="n">
+        <v>45</v>
+      </c>
+      <c r="I332" t="n">
+        <v>10</v>
+      </c>
+      <c r="J332" t="n">
+        <v>23</v>
+      </c>
+      <c r="K332" t="n">
+        <v>9</v>
+      </c>
+      <c r="L332" t="n">
+        <v>16</v>
+      </c>
+      <c r="M332" t="n">
+        <v>14</v>
+      </c>
+      <c r="N332" t="n">
+        <v>25</v>
+      </c>
+      <c r="O332" t="n">
+        <v>19</v>
+      </c>
+      <c r="P332" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>15</v>
+      </c>
+      <c r="R332" t="n">
+        <v>18</v>
+      </c>
+      <c r="S332" t="n">
+        <v>18</v>
+      </c>
+      <c r="T332" t="n">
+        <v>3</v>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="V332" t="n">
+        <v>83</v>
+      </c>
+      <c r="W332" t="n">
+        <v>90.03999999999999</v>
+      </c>
+      <c r="X332" t="n">
+        <v>0.8996001776988006</v>
+      </c>
+      <c r="Y332" t="n">
+        <v>76.03999999999999</v>
+      </c>
+      <c r="Z332" t="n">
+        <v>106.5228826933193</v>
+      </c>
+      <c r="AA332" t="n">
+        <v>0.9646675964667597</v>
+      </c>
+      <c r="AB332" t="n">
+        <v>105.0101214574899</v>
+      </c>
+      <c r="AC332" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="AD332" t="n">
+        <v>0.78125</v>
+      </c>
+      <c r="AE332" t="n">
+        <v>0.5652173913043478</v>
+      </c>
+      <c r="AF332" t="n">
+        <v>1.51276123582943</v>
+      </c>
+      <c r="AG332" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH332" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="AI332" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>24</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>200</v>
+      </c>
+      <c r="F333" t="n">
+        <v>79</v>
+      </c>
+      <c r="G333" t="n">
+        <v>15</v>
+      </c>
+      <c r="H333" t="n">
+        <v>34</v>
+      </c>
+      <c r="I333" t="n">
+        <v>11</v>
+      </c>
+      <c r="J333" t="n">
+        <v>30</v>
+      </c>
+      <c r="K333" t="n">
+        <v>16</v>
+      </c>
+      <c r="L333" t="n">
+        <v>22</v>
+      </c>
+      <c r="M333" t="n">
+        <v>10</v>
+      </c>
+      <c r="N333" t="n">
+        <v>18</v>
+      </c>
+      <c r="O333" t="n">
+        <v>8</v>
+      </c>
+      <c r="P333" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q333" t="n">
+        <v>10</v>
+      </c>
+      <c r="R333" t="n">
+        <v>18</v>
+      </c>
+      <c r="S333" t="n">
+        <v>24</v>
+      </c>
+      <c r="T333" t="n">
+        <v>1</v>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="V333" t="n">
+        <v>81</v>
+      </c>
+      <c r="W333" t="n">
+        <v>83.68000000000001</v>
+      </c>
+      <c r="X333" t="n">
+        <v>0.9440726577437858</v>
+      </c>
+      <c r="Y333" t="n">
+        <v>73.68000000000001</v>
+      </c>
+      <c r="Z333" t="n">
+        <v>107.2204125950054</v>
+      </c>
+      <c r="AA333" t="n">
+        <v>1.09875203472599</v>
+      </c>
+      <c r="AB333" t="n">
+        <v>121.4028776978417</v>
+      </c>
+      <c r="AC333" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AD333" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AE333" t="n">
+        <v>0.4912280701754386</v>
+      </c>
+      <c r="AF333" t="n">
+        <v>-14.18246510283632</v>
+      </c>
+      <c r="AG333" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="AH333" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="AI333" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>24</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>200</v>
+      </c>
+      <c r="F334" t="n">
+        <v>84</v>
+      </c>
+      <c r="G334" t="n">
+        <v>18</v>
+      </c>
+      <c r="H334" t="n">
+        <v>36</v>
+      </c>
+      <c r="I334" t="n">
+        <v>12</v>
+      </c>
+      <c r="J334" t="n">
+        <v>30</v>
+      </c>
+      <c r="K334" t="n">
+        <v>12</v>
+      </c>
+      <c r="L334" t="n">
+        <v>22</v>
+      </c>
+      <c r="M334" t="n">
+        <v>12</v>
+      </c>
+      <c r="N334" t="n">
+        <v>18</v>
+      </c>
+      <c r="O334" t="n">
+        <v>17</v>
+      </c>
+      <c r="P334" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q334" t="n">
+        <v>11</v>
+      </c>
+      <c r="R334" t="n">
+        <v>33</v>
+      </c>
+      <c r="S334" t="n">
+        <v>19</v>
+      </c>
+      <c r="T334" t="n">
+        <v>2</v>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="V334" t="n">
+        <v>91</v>
+      </c>
+      <c r="W334" t="n">
+        <v>86.68000000000001</v>
+      </c>
+      <c r="X334" t="n">
+        <v>0.9690816797415781</v>
+      </c>
+      <c r="Y334" t="n">
+        <v>74.68000000000001</v>
+      </c>
+      <c r="Z334" t="n">
+        <v>112.4799143010177</v>
+      </c>
+      <c r="AA334" t="n">
+        <v>1.082817705854355</v>
+      </c>
+      <c r="AB334" t="n">
+        <v>122.9065370070232</v>
+      </c>
+      <c r="AC334" t="n">
+        <v>0.3428571428571429</v>
+      </c>
+      <c r="AD334" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="AE334" t="n">
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AF334" t="n">
+        <v>-10.42662270600557</v>
+      </c>
+      <c r="AG334" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="AH334" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="AI334" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>24</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>225</v>
+      </c>
+      <c r="F335" t="n">
+        <v>84</v>
+      </c>
+      <c r="G335" t="n">
+        <v>14</v>
+      </c>
+      <c r="H335" t="n">
+        <v>31</v>
+      </c>
+      <c r="I335" t="n">
+        <v>13</v>
+      </c>
+      <c r="J335" t="n">
+        <v>26</v>
+      </c>
+      <c r="K335" t="n">
+        <v>17</v>
+      </c>
+      <c r="L335" t="n">
+        <v>21</v>
+      </c>
+      <c r="M335" t="n">
+        <v>4</v>
+      </c>
+      <c r="N335" t="n">
+        <v>22</v>
+      </c>
+      <c r="O335" t="n">
+        <v>16</v>
+      </c>
+      <c r="P335" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q335" t="n">
+        <v>20</v>
+      </c>
+      <c r="R335" t="n">
+        <v>25</v>
+      </c>
+      <c r="S335" t="n">
+        <v>22</v>
+      </c>
+      <c r="T335" t="n">
+        <v>1</v>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="V335" t="n">
+        <v>86</v>
+      </c>
+      <c r="W335" t="n">
+        <v>86.24000000000001</v>
+      </c>
+      <c r="X335" t="n">
+        <v>0.9740259740259739</v>
+      </c>
+      <c r="Y335" t="n">
+        <v>82.24000000000001</v>
+      </c>
+      <c r="Z335" t="n">
+        <v>102.1400778210117</v>
+      </c>
+      <c r="AA335" t="n">
+        <v>1.016068052930057</v>
+      </c>
+      <c r="AB335" t="n">
+        <v>110.7676455435343</v>
+      </c>
+      <c r="AC335" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AD335" t="n">
+        <v>0.7586206896551724</v>
+      </c>
+      <c r="AE335" t="n">
+        <v>0.4814814814814815</v>
+      </c>
+      <c r="AF335" t="n">
+        <v>-8.627567722522599</v>
+      </c>
+      <c r="AG335" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="AH335" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="AI335" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>24</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>200</v>
+      </c>
+      <c r="F336" t="n">
+        <v>70</v>
+      </c>
+      <c r="G336" t="n">
+        <v>15</v>
+      </c>
+      <c r="H336" t="n">
+        <v>38</v>
+      </c>
+      <c r="I336" t="n">
+        <v>10</v>
+      </c>
+      <c r="J336" t="n">
+        <v>32</v>
+      </c>
+      <c r="K336" t="n">
+        <v>10</v>
+      </c>
+      <c r="L336" t="n">
+        <v>17</v>
+      </c>
+      <c r="M336" t="n">
+        <v>14</v>
+      </c>
+      <c r="N336" t="n">
+        <v>27</v>
+      </c>
+      <c r="O336" t="n">
+        <v>9</v>
+      </c>
+      <c r="P336" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q336" t="n">
+        <v>14</v>
+      </c>
+      <c r="R336" t="n">
+        <v>28</v>
+      </c>
+      <c r="S336" t="n">
+        <v>20</v>
+      </c>
+      <c r="T336" t="n">
+        <v>3</v>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="V336" t="n">
+        <v>75</v>
+      </c>
+      <c r="W336" t="n">
+        <v>91.48</v>
+      </c>
+      <c r="X336" t="n">
+        <v>0.7651945780498469</v>
+      </c>
+      <c r="Y336" t="n">
+        <v>77.48</v>
+      </c>
+      <c r="Z336" t="n">
+        <v>90.34589571502323</v>
+      </c>
+      <c r="AA336" t="n">
+        <v>0.9150805270863835</v>
+      </c>
+      <c r="AB336" t="n">
+        <v>101.4061654948621</v>
+      </c>
+      <c r="AC336" t="n">
+        <v>0.3255813953488372</v>
+      </c>
+      <c r="AD336" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="AE336" t="n">
+        <v>0.5256410256410257</v>
+      </c>
+      <c r="AF336" t="n">
+        <v>-11.06026977983885</v>
+      </c>
+      <c r="AG336" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="AH336" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="AI336" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>24</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>200</v>
+      </c>
+      <c r="F337" t="n">
+        <v>91</v>
+      </c>
+      <c r="G337" t="n">
+        <v>15</v>
+      </c>
+      <c r="H337" t="n">
+        <v>28</v>
+      </c>
+      <c r="I337" t="n">
+        <v>10</v>
+      </c>
+      <c r="J337" t="n">
+        <v>28</v>
+      </c>
+      <c r="K337" t="n">
+        <v>31</v>
+      </c>
+      <c r="L337" t="n">
+        <v>41</v>
+      </c>
+      <c r="M337" t="n">
+        <v>10</v>
+      </c>
+      <c r="N337" t="n">
+        <v>23</v>
+      </c>
+      <c r="O337" t="n">
+        <v>15</v>
+      </c>
+      <c r="P337" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q337" t="n">
+        <v>10</v>
+      </c>
+      <c r="R337" t="n">
+        <v>19</v>
+      </c>
+      <c r="S337" t="n">
+        <v>31</v>
+      </c>
+      <c r="T337" t="n">
+        <v>3</v>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="V337" t="n">
+        <v>84</v>
+      </c>
+      <c r="W337" t="n">
+        <v>84.03999999999999</v>
+      </c>
+      <c r="X337" t="n">
+        <v>1.082817705854355</v>
+      </c>
+      <c r="Y337" t="n">
+        <v>74.03999999999999</v>
+      </c>
+      <c r="Z337" t="n">
+        <v>122.9065370070232</v>
+      </c>
+      <c r="AA337" t="n">
+        <v>0.9690816797415781</v>
+      </c>
+      <c r="AB337" t="n">
+        <v>112.4799143010177</v>
+      </c>
+      <c r="AC337" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="AD337" t="n">
+        <v>0.6571428571428571</v>
+      </c>
+      <c r="AE337" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="AF337" t="n">
+        <v>10.42662270600557</v>
+      </c>
+      <c r="AG337" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="AH337" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="AI337" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/2FEB_25_26/players_25_26_2FEB_games.xlsx
+++ b/data/2FEB_25_26/players_25_26_2FEB_games.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI323"/>
+  <dimension ref="A1:AI351"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38921,6 +38921,3338 @@
       </c>
       <c r="AI323" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>24</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>200</v>
+      </c>
+      <c r="F324" t="n">
+        <v>81</v>
+      </c>
+      <c r="G324" t="n">
+        <v>23</v>
+      </c>
+      <c r="H324" t="n">
+        <v>34</v>
+      </c>
+      <c r="I324" t="n">
+        <v>8</v>
+      </c>
+      <c r="J324" t="n">
+        <v>24</v>
+      </c>
+      <c r="K324" t="n">
+        <v>11</v>
+      </c>
+      <c r="L324" t="n">
+        <v>13</v>
+      </c>
+      <c r="M324" t="n">
+        <v>7</v>
+      </c>
+      <c r="N324" t="n">
+        <v>22</v>
+      </c>
+      <c r="O324" t="n">
+        <v>15</v>
+      </c>
+      <c r="P324" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>10</v>
+      </c>
+      <c r="R324" t="n">
+        <v>24</v>
+      </c>
+      <c r="S324" t="n">
+        <v>18</v>
+      </c>
+      <c r="T324" t="n">
+        <v>3</v>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="V324" t="n">
+        <v>79</v>
+      </c>
+      <c r="W324" t="n">
+        <v>73.72</v>
+      </c>
+      <c r="X324" t="n">
+        <v>1.09875203472599</v>
+      </c>
+      <c r="Y324" t="n">
+        <v>66.72</v>
+      </c>
+      <c r="Z324" t="n">
+        <v>121.4028776978417</v>
+      </c>
+      <c r="AA324" t="n">
+        <v>0.9440726577437858</v>
+      </c>
+      <c r="AB324" t="n">
+        <v>107.2204125950054</v>
+      </c>
+      <c r="AC324" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AD324" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="AE324" t="n">
+        <v>0.5087719298245614</v>
+      </c>
+      <c r="AF324" t="n">
+        <v>14.18246510283632</v>
+      </c>
+      <c r="AG324" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="AH324" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="AI324" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>24</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>200</v>
+      </c>
+      <c r="F325" t="n">
+        <v>93</v>
+      </c>
+      <c r="G325" t="n">
+        <v>18</v>
+      </c>
+      <c r="H325" t="n">
+        <v>34</v>
+      </c>
+      <c r="I325" t="n">
+        <v>13</v>
+      </c>
+      <c r="J325" t="n">
+        <v>19</v>
+      </c>
+      <c r="K325" t="n">
+        <v>18</v>
+      </c>
+      <c r="L325" t="n">
+        <v>28</v>
+      </c>
+      <c r="M325" t="n">
+        <v>7</v>
+      </c>
+      <c r="N325" t="n">
+        <v>23</v>
+      </c>
+      <c r="O325" t="n">
+        <v>24</v>
+      </c>
+      <c r="P325" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>15</v>
+      </c>
+      <c r="R325" t="n">
+        <v>16</v>
+      </c>
+      <c r="S325" t="n">
+        <v>23</v>
+      </c>
+      <c r="T325" t="n">
+        <v>1</v>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>2487923</t>
+        </is>
+      </c>
+      <c r="V325" t="n">
+        <v>83</v>
+      </c>
+      <c r="W325" t="n">
+        <v>80.31999999999999</v>
+      </c>
+      <c r="X325" t="n">
+        <v>1.157868525896415</v>
+      </c>
+      <c r="Y325" t="n">
+        <v>73.31999999999999</v>
+      </c>
+      <c r="Z325" t="n">
+        <v>126.8412438625205</v>
+      </c>
+      <c r="AA325" t="n">
+        <v>0.8257063270990848</v>
+      </c>
+      <c r="AB325" t="n">
+        <v>104.3762575452716</v>
+      </c>
+      <c r="AC325" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="AD325" t="n">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="AE325" t="n">
+        <v>0.4411764705882353</v>
+      </c>
+      <c r="AF325" t="n">
+        <v>22.46498631724883</v>
+      </c>
+      <c r="AG325" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="AH325" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="AI325" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>24</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>200</v>
+      </c>
+      <c r="F326" t="n">
+        <v>58</v>
+      </c>
+      <c r="G326" t="n">
+        <v>16</v>
+      </c>
+      <c r="H326" t="n">
+        <v>37</v>
+      </c>
+      <c r="I326" t="n">
+        <v>6</v>
+      </c>
+      <c r="J326" t="n">
+        <v>32</v>
+      </c>
+      <c r="K326" t="n">
+        <v>8</v>
+      </c>
+      <c r="L326" t="n">
+        <v>18</v>
+      </c>
+      <c r="M326" t="n">
+        <v>17</v>
+      </c>
+      <c r="N326" t="n">
+        <v>25</v>
+      </c>
+      <c r="O326" t="n">
+        <v>6</v>
+      </c>
+      <c r="P326" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q326" t="n">
+        <v>10</v>
+      </c>
+      <c r="R326" t="n">
+        <v>20</v>
+      </c>
+      <c r="S326" t="n">
+        <v>22</v>
+      </c>
+      <c r="T326" t="n">
+        <v>2</v>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>2487926</t>
+        </is>
+      </c>
+      <c r="V326" t="n">
+        <v>70</v>
+      </c>
+      <c r="W326" t="n">
+        <v>86.92</v>
+      </c>
+      <c r="X326" t="n">
+        <v>0.6672802577082374</v>
+      </c>
+      <c r="Y326" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="Z326" t="n">
+        <v>82.95194508009153</v>
+      </c>
+      <c r="AA326" t="n">
+        <v>0.9039256198347108</v>
+      </c>
+      <c r="AB326" t="n">
+        <v>100.8064516129032</v>
+      </c>
+      <c r="AC326" t="n">
+        <v>0.3541666666666667</v>
+      </c>
+      <c r="AD326" t="n">
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="AE326" t="n">
+        <v>0.5185185185185185</v>
+      </c>
+      <c r="AF326" t="n">
+        <v>-17.8545065328117</v>
+      </c>
+      <c r="AG326" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="AH326" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="AI326" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>24</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>200</v>
+      </c>
+      <c r="F327" t="n">
+        <v>83</v>
+      </c>
+      <c r="G327" t="n">
+        <v>23</v>
+      </c>
+      <c r="H327" t="n">
+        <v>44</v>
+      </c>
+      <c r="I327" t="n">
+        <v>9</v>
+      </c>
+      <c r="J327" t="n">
+        <v>22</v>
+      </c>
+      <c r="K327" t="n">
+        <v>10</v>
+      </c>
+      <c r="L327" t="n">
+        <v>16</v>
+      </c>
+      <c r="M327" t="n">
+        <v>7</v>
+      </c>
+      <c r="N327" t="n">
+        <v>23</v>
+      </c>
+      <c r="O327" t="n">
+        <v>18</v>
+      </c>
+      <c r="P327" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>13</v>
+      </c>
+      <c r="R327" t="n">
+        <v>18</v>
+      </c>
+      <c r="S327" t="n">
+        <v>18</v>
+      </c>
+      <c r="T327" t="n">
+        <v>2</v>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="V327" t="n">
+        <v>81</v>
+      </c>
+      <c r="W327" t="n">
+        <v>86.03999999999999</v>
+      </c>
+      <c r="X327" t="n">
+        <v>0.9646675964667597</v>
+      </c>
+      <c r="Y327" t="n">
+        <v>79.03999999999999</v>
+      </c>
+      <c r="Z327" t="n">
+        <v>105.0101214574899</v>
+      </c>
+      <c r="AA327" t="n">
+        <v>0.8996001776988006</v>
+      </c>
+      <c r="AB327" t="n">
+        <v>106.5228826933193</v>
+      </c>
+      <c r="AC327" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="AD327" t="n">
+        <v>0.6216216216216216</v>
+      </c>
+      <c r="AE327" t="n">
+        <v>0.4347826086956522</v>
+      </c>
+      <c r="AF327" t="n">
+        <v>-1.51276123582943</v>
+      </c>
+      <c r="AG327" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH327" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="AI327" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>24</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>200</v>
+      </c>
+      <c r="F328" t="n">
+        <v>75</v>
+      </c>
+      <c r="G328" t="n">
+        <v>21</v>
+      </c>
+      <c r="H328" t="n">
+        <v>38</v>
+      </c>
+      <c r="I328" t="n">
+        <v>5</v>
+      </c>
+      <c r="J328" t="n">
+        <v>17</v>
+      </c>
+      <c r="K328" t="n">
+        <v>18</v>
+      </c>
+      <c r="L328" t="n">
+        <v>34</v>
+      </c>
+      <c r="M328" t="n">
+        <v>8</v>
+      </c>
+      <c r="N328" t="n">
+        <v>29</v>
+      </c>
+      <c r="O328" t="n">
+        <v>11</v>
+      </c>
+      <c r="P328" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q328" t="n">
+        <v>12</v>
+      </c>
+      <c r="R328" t="n">
+        <v>20</v>
+      </c>
+      <c r="S328" t="n">
+        <v>28</v>
+      </c>
+      <c r="T328" t="n">
+        <v>4</v>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="V328" t="n">
+        <v>70</v>
+      </c>
+      <c r="W328" t="n">
+        <v>81.96000000000001</v>
+      </c>
+      <c r="X328" t="n">
+        <v>0.9150805270863835</v>
+      </c>
+      <c r="Y328" t="n">
+        <v>73.96000000000001</v>
+      </c>
+      <c r="Z328" t="n">
+        <v>101.4061654948621</v>
+      </c>
+      <c r="AA328" t="n">
+        <v>0.7651945780498469</v>
+      </c>
+      <c r="AB328" t="n">
+        <v>90.34589571502323</v>
+      </c>
+      <c r="AC328" t="n">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="AD328" t="n">
+        <v>0.6744186046511628</v>
+      </c>
+      <c r="AE328" t="n">
+        <v>0.4743589743589743</v>
+      </c>
+      <c r="AF328" t="n">
+        <v>11.06026977983885</v>
+      </c>
+      <c r="AG328" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="AH328" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="AI328" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>24</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>225</v>
+      </c>
+      <c r="F329" t="n">
+        <v>86</v>
+      </c>
+      <c r="G329" t="n">
+        <v>18</v>
+      </c>
+      <c r="H329" t="n">
+        <v>33</v>
+      </c>
+      <c r="I329" t="n">
+        <v>9</v>
+      </c>
+      <c r="J329" t="n">
+        <v>25</v>
+      </c>
+      <c r="K329" t="n">
+        <v>23</v>
+      </c>
+      <c r="L329" t="n">
+        <v>31</v>
+      </c>
+      <c r="M329" t="n">
+        <v>7</v>
+      </c>
+      <c r="N329" t="n">
+        <v>21</v>
+      </c>
+      <c r="O329" t="n">
+        <v>12</v>
+      </c>
+      <c r="P329" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>13</v>
+      </c>
+      <c r="R329" t="n">
+        <v>22</v>
+      </c>
+      <c r="S329" t="n">
+        <v>25</v>
+      </c>
+      <c r="T329" t="n">
+        <v>0</v>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="V329" t="n">
+        <v>84</v>
+      </c>
+      <c r="W329" t="n">
+        <v>84.64</v>
+      </c>
+      <c r="X329" t="n">
+        <v>1.016068052930057</v>
+      </c>
+      <c r="Y329" t="n">
+        <v>77.64</v>
+      </c>
+      <c r="Z329" t="n">
+        <v>110.7676455435343</v>
+      </c>
+      <c r="AA329" t="n">
+        <v>0.9740259740259739</v>
+      </c>
+      <c r="AB329" t="n">
+        <v>102.1400778210117</v>
+      </c>
+      <c r="AC329" t="n">
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="AD329" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AE329" t="n">
+        <v>0.5185185185185185</v>
+      </c>
+      <c r="AF329" t="n">
+        <v>8.627567722522599</v>
+      </c>
+      <c r="AG329" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="AH329" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="AI329" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>24</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>200</v>
+      </c>
+      <c r="F330" t="n">
+        <v>70</v>
+      </c>
+      <c r="G330" t="n">
+        <v>16</v>
+      </c>
+      <c r="H330" t="n">
+        <v>29</v>
+      </c>
+      <c r="I330" t="n">
+        <v>7</v>
+      </c>
+      <c r="J330" t="n">
+        <v>26</v>
+      </c>
+      <c r="K330" t="n">
+        <v>17</v>
+      </c>
+      <c r="L330" t="n">
+        <v>26</v>
+      </c>
+      <c r="M330" t="n">
+        <v>8</v>
+      </c>
+      <c r="N330" t="n">
+        <v>31</v>
+      </c>
+      <c r="O330" t="n">
+        <v>11</v>
+      </c>
+      <c r="P330" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>11</v>
+      </c>
+      <c r="R330" t="n">
+        <v>22</v>
+      </c>
+      <c r="S330" t="n">
+        <v>19</v>
+      </c>
+      <c r="T330" t="n">
+        <v>4</v>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>2487926</t>
+        </is>
+      </c>
+      <c r="V330" t="n">
+        <v>58</v>
+      </c>
+      <c r="W330" t="n">
+        <v>77.44</v>
+      </c>
+      <c r="X330" t="n">
+        <v>0.9039256198347108</v>
+      </c>
+      <c r="Y330" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="Z330" t="n">
+        <v>100.8064516129032</v>
+      </c>
+      <c r="AA330" t="n">
+        <v>0.6672802577082374</v>
+      </c>
+      <c r="AB330" t="n">
+        <v>82.95194508009153</v>
+      </c>
+      <c r="AC330" t="n">
+        <v>0.2424242424242424</v>
+      </c>
+      <c r="AD330" t="n">
+        <v>0.6458333333333334</v>
+      </c>
+      <c r="AE330" t="n">
+        <v>0.4814814814814815</v>
+      </c>
+      <c r="AF330" t="n">
+        <v>17.8545065328117</v>
+      </c>
+      <c r="AG330" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="AH330" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="AI330" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>24</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>200</v>
+      </c>
+      <c r="F331" t="n">
+        <v>83</v>
+      </c>
+      <c r="G331" t="n">
+        <v>26</v>
+      </c>
+      <c r="H331" t="n">
+        <v>62</v>
+      </c>
+      <c r="I331" t="n">
+        <v>8</v>
+      </c>
+      <c r="J331" t="n">
+        <v>25</v>
+      </c>
+      <c r="K331" t="n">
+        <v>7</v>
+      </c>
+      <c r="L331" t="n">
+        <v>8</v>
+      </c>
+      <c r="M331" t="n">
+        <v>21</v>
+      </c>
+      <c r="N331" t="n">
+        <v>17</v>
+      </c>
+      <c r="O331" t="n">
+        <v>22</v>
+      </c>
+      <c r="P331" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>10</v>
+      </c>
+      <c r="R331" t="n">
+        <v>23</v>
+      </c>
+      <c r="S331" t="n">
+        <v>16</v>
+      </c>
+      <c r="T331" t="n">
+        <v>2</v>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>2487923</t>
+        </is>
+      </c>
+      <c r="V331" t="n">
+        <v>93</v>
+      </c>
+      <c r="W331" t="n">
+        <v>100.52</v>
+      </c>
+      <c r="X331" t="n">
+        <v>0.8257063270990848</v>
+      </c>
+      <c r="Y331" t="n">
+        <v>79.52</v>
+      </c>
+      <c r="Z331" t="n">
+        <v>104.3762575452716</v>
+      </c>
+      <c r="AA331" t="n">
+        <v>1.157868525896415</v>
+      </c>
+      <c r="AB331" t="n">
+        <v>126.8412438625205</v>
+      </c>
+      <c r="AC331" t="n">
+        <v>0.4772727272727273</v>
+      </c>
+      <c r="AD331" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="AE331" t="n">
+        <v>0.5588235294117647</v>
+      </c>
+      <c r="AF331" t="n">
+        <v>-22.46498631724883</v>
+      </c>
+      <c r="AG331" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="AH331" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="AI331" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>24</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>200</v>
+      </c>
+      <c r="F332" t="n">
+        <v>81</v>
+      </c>
+      <c r="G332" t="n">
+        <v>21</v>
+      </c>
+      <c r="H332" t="n">
+        <v>45</v>
+      </c>
+      <c r="I332" t="n">
+        <v>10</v>
+      </c>
+      <c r="J332" t="n">
+        <v>23</v>
+      </c>
+      <c r="K332" t="n">
+        <v>9</v>
+      </c>
+      <c r="L332" t="n">
+        <v>16</v>
+      </c>
+      <c r="M332" t="n">
+        <v>14</v>
+      </c>
+      <c r="N332" t="n">
+        <v>25</v>
+      </c>
+      <c r="O332" t="n">
+        <v>19</v>
+      </c>
+      <c r="P332" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>15</v>
+      </c>
+      <c r="R332" t="n">
+        <v>18</v>
+      </c>
+      <c r="S332" t="n">
+        <v>18</v>
+      </c>
+      <c r="T332" t="n">
+        <v>3</v>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="V332" t="n">
+        <v>83</v>
+      </c>
+      <c r="W332" t="n">
+        <v>90.03999999999999</v>
+      </c>
+      <c r="X332" t="n">
+        <v>0.8996001776988006</v>
+      </c>
+      <c r="Y332" t="n">
+        <v>76.03999999999999</v>
+      </c>
+      <c r="Z332" t="n">
+        <v>106.5228826933193</v>
+      </c>
+      <c r="AA332" t="n">
+        <v>0.9646675964667597</v>
+      </c>
+      <c r="AB332" t="n">
+        <v>105.0101214574899</v>
+      </c>
+      <c r="AC332" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="AD332" t="n">
+        <v>0.78125</v>
+      </c>
+      <c r="AE332" t="n">
+        <v>0.5652173913043478</v>
+      </c>
+      <c r="AF332" t="n">
+        <v>1.51276123582943</v>
+      </c>
+      <c r="AG332" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH332" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="AI332" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>24</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>200</v>
+      </c>
+      <c r="F333" t="n">
+        <v>79</v>
+      </c>
+      <c r="G333" t="n">
+        <v>15</v>
+      </c>
+      <c r="H333" t="n">
+        <v>34</v>
+      </c>
+      <c r="I333" t="n">
+        <v>11</v>
+      </c>
+      <c r="J333" t="n">
+        <v>30</v>
+      </c>
+      <c r="K333" t="n">
+        <v>16</v>
+      </c>
+      <c r="L333" t="n">
+        <v>22</v>
+      </c>
+      <c r="M333" t="n">
+        <v>10</v>
+      </c>
+      <c r="N333" t="n">
+        <v>18</v>
+      </c>
+      <c r="O333" t="n">
+        <v>8</v>
+      </c>
+      <c r="P333" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q333" t="n">
+        <v>10</v>
+      </c>
+      <c r="R333" t="n">
+        <v>18</v>
+      </c>
+      <c r="S333" t="n">
+        <v>24</v>
+      </c>
+      <c r="T333" t="n">
+        <v>1</v>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="V333" t="n">
+        <v>81</v>
+      </c>
+      <c r="W333" t="n">
+        <v>83.68000000000001</v>
+      </c>
+      <c r="X333" t="n">
+        <v>0.9440726577437858</v>
+      </c>
+      <c r="Y333" t="n">
+        <v>73.68000000000001</v>
+      </c>
+      <c r="Z333" t="n">
+        <v>107.2204125950054</v>
+      </c>
+      <c r="AA333" t="n">
+        <v>1.09875203472599</v>
+      </c>
+      <c r="AB333" t="n">
+        <v>121.4028776978417</v>
+      </c>
+      <c r="AC333" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AD333" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AE333" t="n">
+        <v>0.4912280701754386</v>
+      </c>
+      <c r="AF333" t="n">
+        <v>-14.18246510283632</v>
+      </c>
+      <c r="AG333" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="AH333" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="AI333" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>24</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>200</v>
+      </c>
+      <c r="F334" t="n">
+        <v>84</v>
+      </c>
+      <c r="G334" t="n">
+        <v>18</v>
+      </c>
+      <c r="H334" t="n">
+        <v>36</v>
+      </c>
+      <c r="I334" t="n">
+        <v>12</v>
+      </c>
+      <c r="J334" t="n">
+        <v>30</v>
+      </c>
+      <c r="K334" t="n">
+        <v>12</v>
+      </c>
+      <c r="L334" t="n">
+        <v>22</v>
+      </c>
+      <c r="M334" t="n">
+        <v>12</v>
+      </c>
+      <c r="N334" t="n">
+        <v>18</v>
+      </c>
+      <c r="O334" t="n">
+        <v>17</v>
+      </c>
+      <c r="P334" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q334" t="n">
+        <v>11</v>
+      </c>
+      <c r="R334" t="n">
+        <v>33</v>
+      </c>
+      <c r="S334" t="n">
+        <v>19</v>
+      </c>
+      <c r="T334" t="n">
+        <v>2</v>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="V334" t="n">
+        <v>91</v>
+      </c>
+      <c r="W334" t="n">
+        <v>86.68000000000001</v>
+      </c>
+      <c r="X334" t="n">
+        <v>0.9690816797415781</v>
+      </c>
+      <c r="Y334" t="n">
+        <v>74.68000000000001</v>
+      </c>
+      <c r="Z334" t="n">
+        <v>112.4799143010177</v>
+      </c>
+      <c r="AA334" t="n">
+        <v>1.082817705854355</v>
+      </c>
+      <c r="AB334" t="n">
+        <v>122.9065370070232</v>
+      </c>
+      <c r="AC334" t="n">
+        <v>0.3428571428571429</v>
+      </c>
+      <c r="AD334" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="AE334" t="n">
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AF334" t="n">
+        <v>-10.42662270600557</v>
+      </c>
+      <c r="AG334" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="AH334" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="AI334" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>24</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>225</v>
+      </c>
+      <c r="F335" t="n">
+        <v>84</v>
+      </c>
+      <c r="G335" t="n">
+        <v>14</v>
+      </c>
+      <c r="H335" t="n">
+        <v>31</v>
+      </c>
+      <c r="I335" t="n">
+        <v>13</v>
+      </c>
+      <c r="J335" t="n">
+        <v>26</v>
+      </c>
+      <c r="K335" t="n">
+        <v>17</v>
+      </c>
+      <c r="L335" t="n">
+        <v>21</v>
+      </c>
+      <c r="M335" t="n">
+        <v>4</v>
+      </c>
+      <c r="N335" t="n">
+        <v>22</v>
+      </c>
+      <c r="O335" t="n">
+        <v>16</v>
+      </c>
+      <c r="P335" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q335" t="n">
+        <v>20</v>
+      </c>
+      <c r="R335" t="n">
+        <v>25</v>
+      </c>
+      <c r="S335" t="n">
+        <v>22</v>
+      </c>
+      <c r="T335" t="n">
+        <v>1</v>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="V335" t="n">
+        <v>86</v>
+      </c>
+      <c r="W335" t="n">
+        <v>86.24000000000001</v>
+      </c>
+      <c r="X335" t="n">
+        <v>0.9740259740259739</v>
+      </c>
+      <c r="Y335" t="n">
+        <v>82.24000000000001</v>
+      </c>
+      <c r="Z335" t="n">
+        <v>102.1400778210117</v>
+      </c>
+      <c r="AA335" t="n">
+        <v>1.016068052930057</v>
+      </c>
+      <c r="AB335" t="n">
+        <v>110.7676455435343</v>
+      </c>
+      <c r="AC335" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AD335" t="n">
+        <v>0.7586206896551724</v>
+      </c>
+      <c r="AE335" t="n">
+        <v>0.4814814814814815</v>
+      </c>
+      <c r="AF335" t="n">
+        <v>-8.627567722522599</v>
+      </c>
+      <c r="AG335" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="AH335" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="AI335" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>24</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>200</v>
+      </c>
+      <c r="F336" t="n">
+        <v>70</v>
+      </c>
+      <c r="G336" t="n">
+        <v>15</v>
+      </c>
+      <c r="H336" t="n">
+        <v>38</v>
+      </c>
+      <c r="I336" t="n">
+        <v>10</v>
+      </c>
+      <c r="J336" t="n">
+        <v>32</v>
+      </c>
+      <c r="K336" t="n">
+        <v>10</v>
+      </c>
+      <c r="L336" t="n">
+        <v>17</v>
+      </c>
+      <c r="M336" t="n">
+        <v>14</v>
+      </c>
+      <c r="N336" t="n">
+        <v>27</v>
+      </c>
+      <c r="O336" t="n">
+        <v>9</v>
+      </c>
+      <c r="P336" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q336" t="n">
+        <v>14</v>
+      </c>
+      <c r="R336" t="n">
+        <v>28</v>
+      </c>
+      <c r="S336" t="n">
+        <v>20</v>
+      </c>
+      <c r="T336" t="n">
+        <v>3</v>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="V336" t="n">
+        <v>75</v>
+      </c>
+      <c r="W336" t="n">
+        <v>91.48</v>
+      </c>
+      <c r="X336" t="n">
+        <v>0.7651945780498469</v>
+      </c>
+      <c r="Y336" t="n">
+        <v>77.48</v>
+      </c>
+      <c r="Z336" t="n">
+        <v>90.34589571502323</v>
+      </c>
+      <c r="AA336" t="n">
+        <v>0.9150805270863835</v>
+      </c>
+      <c r="AB336" t="n">
+        <v>101.4061654948621</v>
+      </c>
+      <c r="AC336" t="n">
+        <v>0.3255813953488372</v>
+      </c>
+      <c r="AD336" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="AE336" t="n">
+        <v>0.5256410256410257</v>
+      </c>
+      <c r="AF336" t="n">
+        <v>-11.06026977983885</v>
+      </c>
+      <c r="AG336" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="AH336" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="AI336" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>24</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>200</v>
+      </c>
+      <c r="F337" t="n">
+        <v>91</v>
+      </c>
+      <c r="G337" t="n">
+        <v>15</v>
+      </c>
+      <c r="H337" t="n">
+        <v>28</v>
+      </c>
+      <c r="I337" t="n">
+        <v>10</v>
+      </c>
+      <c r="J337" t="n">
+        <v>28</v>
+      </c>
+      <c r="K337" t="n">
+        <v>31</v>
+      </c>
+      <c r="L337" t="n">
+        <v>41</v>
+      </c>
+      <c r="M337" t="n">
+        <v>10</v>
+      </c>
+      <c r="N337" t="n">
+        <v>23</v>
+      </c>
+      <c r="O337" t="n">
+        <v>15</v>
+      </c>
+      <c r="P337" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q337" t="n">
+        <v>10</v>
+      </c>
+      <c r="R337" t="n">
+        <v>19</v>
+      </c>
+      <c r="S337" t="n">
+        <v>31</v>
+      </c>
+      <c r="T337" t="n">
+        <v>3</v>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="V337" t="n">
+        <v>84</v>
+      </c>
+      <c r="W337" t="n">
+        <v>84.03999999999999</v>
+      </c>
+      <c r="X337" t="n">
+        <v>1.082817705854355</v>
+      </c>
+      <c r="Y337" t="n">
+        <v>74.03999999999999</v>
+      </c>
+      <c r="Z337" t="n">
+        <v>122.9065370070232</v>
+      </c>
+      <c r="AA337" t="n">
+        <v>0.9690816797415781</v>
+      </c>
+      <c r="AB337" t="n">
+        <v>112.4799143010177</v>
+      </c>
+      <c r="AC337" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="AD337" t="n">
+        <v>0.6571428571428571</v>
+      </c>
+      <c r="AE337" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="AF337" t="n">
+        <v>10.42662270600557</v>
+      </c>
+      <c r="AG337" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="AH337" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="AI337" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>25</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>200</v>
+      </c>
+      <c r="F338" t="n">
+        <v>102</v>
+      </c>
+      <c r="G338" t="n">
+        <v>22</v>
+      </c>
+      <c r="H338" t="n">
+        <v>29</v>
+      </c>
+      <c r="I338" t="n">
+        <v>17</v>
+      </c>
+      <c r="J338" t="n">
+        <v>38</v>
+      </c>
+      <c r="K338" t="n">
+        <v>7</v>
+      </c>
+      <c r="L338" t="n">
+        <v>9</v>
+      </c>
+      <c r="M338" t="n">
+        <v>8</v>
+      </c>
+      <c r="N338" t="n">
+        <v>26</v>
+      </c>
+      <c r="O338" t="n">
+        <v>19</v>
+      </c>
+      <c r="P338" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q338" t="n">
+        <v>10</v>
+      </c>
+      <c r="R338" t="n">
+        <v>21</v>
+      </c>
+      <c r="S338" t="n">
+        <v>11</v>
+      </c>
+      <c r="T338" t="n">
+        <v>2</v>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>2487933</t>
+        </is>
+      </c>
+      <c r="V338" t="n">
+        <v>71</v>
+      </c>
+      <c r="W338" t="n">
+        <v>80.96000000000001</v>
+      </c>
+      <c r="X338" t="n">
+        <v>1.259881422924901</v>
+      </c>
+      <c r="Y338" t="n">
+        <v>72.96000000000001</v>
+      </c>
+      <c r="Z338" t="n">
+        <v>139.8026315789473</v>
+      </c>
+      <c r="AA338" t="n">
+        <v>0.8919597989949749</v>
+      </c>
+      <c r="AB338" t="n">
+        <v>102.0114942528736</v>
+      </c>
+      <c r="AC338" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="AD338" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="AE338" t="n">
+        <v>0.5964912280701754</v>
+      </c>
+      <c r="AF338" t="n">
+        <v>37.79113732607377</v>
+      </c>
+      <c r="AG338" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="AH338" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="AI338" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>25</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>200</v>
+      </c>
+      <c r="F339" t="n">
+        <v>87</v>
+      </c>
+      <c r="G339" t="n">
+        <v>18</v>
+      </c>
+      <c r="H339" t="n">
+        <v>31</v>
+      </c>
+      <c r="I339" t="n">
+        <v>7</v>
+      </c>
+      <c r="J339" t="n">
+        <v>20</v>
+      </c>
+      <c r="K339" t="n">
+        <v>30</v>
+      </c>
+      <c r="L339" t="n">
+        <v>43</v>
+      </c>
+      <c r="M339" t="n">
+        <v>3</v>
+      </c>
+      <c r="N339" t="n">
+        <v>34</v>
+      </c>
+      <c r="O339" t="n">
+        <v>17</v>
+      </c>
+      <c r="P339" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q339" t="n">
+        <v>11</v>
+      </c>
+      <c r="R339" t="n">
+        <v>20</v>
+      </c>
+      <c r="S339" t="n">
+        <v>30</v>
+      </c>
+      <c r="T339" t="n">
+        <v>1</v>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>2487931</t>
+        </is>
+      </c>
+      <c r="V339" t="n">
+        <v>75</v>
+      </c>
+      <c r="W339" t="n">
+        <v>80.92</v>
+      </c>
+      <c r="X339" t="n">
+        <v>1.075135936727632</v>
+      </c>
+      <c r="Y339" t="n">
+        <v>77.92</v>
+      </c>
+      <c r="Z339" t="n">
+        <v>111.652977412731</v>
+      </c>
+      <c r="AA339" t="n">
+        <v>0.8971291866028709</v>
+      </c>
+      <c r="AB339" t="n">
+        <v>96.64948453608248</v>
+      </c>
+      <c r="AC339" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AD339" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AE339" t="n">
+        <v>0.578125</v>
+      </c>
+      <c r="AF339" t="n">
+        <v>15.00349287664852</v>
+      </c>
+      <c r="AG339" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="AH339" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="AI339" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>25</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>200</v>
+      </c>
+      <c r="F340" t="n">
+        <v>98</v>
+      </c>
+      <c r="G340" t="n">
+        <v>25</v>
+      </c>
+      <c r="H340" t="n">
+        <v>40</v>
+      </c>
+      <c r="I340" t="n">
+        <v>6</v>
+      </c>
+      <c r="J340" t="n">
+        <v>29</v>
+      </c>
+      <c r="K340" t="n">
+        <v>30</v>
+      </c>
+      <c r="L340" t="n">
+        <v>39</v>
+      </c>
+      <c r="M340" t="n">
+        <v>12</v>
+      </c>
+      <c r="N340" t="n">
+        <v>26</v>
+      </c>
+      <c r="O340" t="n">
+        <v>6</v>
+      </c>
+      <c r="P340" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q340" t="n">
+        <v>8</v>
+      </c>
+      <c r="R340" t="n">
+        <v>25</v>
+      </c>
+      <c r="S340" t="n">
+        <v>28</v>
+      </c>
+      <c r="T340" t="n">
+        <v>0</v>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>2487927</t>
+        </is>
+      </c>
+      <c r="V340" t="n">
+        <v>85</v>
+      </c>
+      <c r="W340" t="n">
+        <v>94.16</v>
+      </c>
+      <c r="X340" t="n">
+        <v>1.040781648258284</v>
+      </c>
+      <c r="Y340" t="n">
+        <v>82.16</v>
+      </c>
+      <c r="Z340" t="n">
+        <v>119.2794547224927</v>
+      </c>
+      <c r="AA340" t="n">
+        <v>0.9948501872659177</v>
+      </c>
+      <c r="AB340" t="n">
+        <v>106.9989929506546</v>
+      </c>
+      <c r="AC340" t="n">
+        <v>0.3243243243243243</v>
+      </c>
+      <c r="AD340" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AE340" t="n">
+        <v>0.5507246376811594</v>
+      </c>
+      <c r="AF340" t="n">
+        <v>12.28046177183812</v>
+      </c>
+      <c r="AG340" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="AH340" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="AI340" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>25</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>200</v>
+      </c>
+      <c r="F341" t="n">
+        <v>68</v>
+      </c>
+      <c r="G341" t="n">
+        <v>24</v>
+      </c>
+      <c r="H341" t="n">
+        <v>43</v>
+      </c>
+      <c r="I341" t="n">
+        <v>0</v>
+      </c>
+      <c r="J341" t="n">
+        <v>13</v>
+      </c>
+      <c r="K341" t="n">
+        <v>20</v>
+      </c>
+      <c r="L341" t="n">
+        <v>27</v>
+      </c>
+      <c r="M341" t="n">
+        <v>6</v>
+      </c>
+      <c r="N341" t="n">
+        <v>23</v>
+      </c>
+      <c r="O341" t="n">
+        <v>17</v>
+      </c>
+      <c r="P341" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q341" t="n">
+        <v>13</v>
+      </c>
+      <c r="R341" t="n">
+        <v>21</v>
+      </c>
+      <c r="S341" t="n">
+        <v>24</v>
+      </c>
+      <c r="T341" t="n">
+        <v>2</v>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>2487929</t>
+        </is>
+      </c>
+      <c r="V341" t="n">
+        <v>85</v>
+      </c>
+      <c r="W341" t="n">
+        <v>80.88</v>
+      </c>
+      <c r="X341" t="n">
+        <v>0.8407517309594461</v>
+      </c>
+      <c r="Y341" t="n">
+        <v>74.88</v>
+      </c>
+      <c r="Z341" t="n">
+        <v>90.81196581196582</v>
+      </c>
+      <c r="AA341" t="n">
+        <v>0.9792626728110599</v>
+      </c>
+      <c r="AB341" t="n">
+        <v>110.6770833333333</v>
+      </c>
+      <c r="AC341" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="AD341" t="n">
+        <v>0.696969696969697</v>
+      </c>
+      <c r="AE341" t="n">
+        <v>0.4393939393939394</v>
+      </c>
+      <c r="AF341" t="n">
+        <v>-19.86511752136752</v>
+      </c>
+      <c r="AG341" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="AH341" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="AI341" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>25</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>200</v>
+      </c>
+      <c r="F342" t="n">
+        <v>66</v>
+      </c>
+      <c r="G342" t="n">
+        <v>7</v>
+      </c>
+      <c r="H342" t="n">
+        <v>25</v>
+      </c>
+      <c r="I342" t="n">
+        <v>13</v>
+      </c>
+      <c r="J342" t="n">
+        <v>31</v>
+      </c>
+      <c r="K342" t="n">
+        <v>13</v>
+      </c>
+      <c r="L342" t="n">
+        <v>22</v>
+      </c>
+      <c r="M342" t="n">
+        <v>6</v>
+      </c>
+      <c r="N342" t="n">
+        <v>25</v>
+      </c>
+      <c r="O342" t="n">
+        <v>12</v>
+      </c>
+      <c r="P342" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q342" t="n">
+        <v>13</v>
+      </c>
+      <c r="R342" t="n">
+        <v>24</v>
+      </c>
+      <c r="S342" t="n">
+        <v>20</v>
+      </c>
+      <c r="T342" t="n">
+        <v>1</v>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>2487928</t>
+        </is>
+      </c>
+      <c r="V342" t="n">
+        <v>64</v>
+      </c>
+      <c r="W342" t="n">
+        <v>78.68000000000001</v>
+      </c>
+      <c r="X342" t="n">
+        <v>0.838840874428063</v>
+      </c>
+      <c r="Y342" t="n">
+        <v>72.68000000000001</v>
+      </c>
+      <c r="Z342" t="n">
+        <v>90.80902586681341</v>
+      </c>
+      <c r="AA342" t="n">
+        <v>0.7403979639055993</v>
+      </c>
+      <c r="AB342" t="n">
+        <v>83.7257980115123</v>
+      </c>
+      <c r="AC342" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="AD342" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AE342" t="n">
+        <v>0.4626865671641791</v>
+      </c>
+      <c r="AF342" t="n">
+        <v>7.083227855301118</v>
+      </c>
+      <c r="AG342" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="AH342" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="AI342" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>25</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>200</v>
+      </c>
+      <c r="F343" t="n">
+        <v>75</v>
+      </c>
+      <c r="G343" t="n">
+        <v>16</v>
+      </c>
+      <c r="H343" t="n">
+        <v>31</v>
+      </c>
+      <c r="I343" t="n">
+        <v>11</v>
+      </c>
+      <c r="J343" t="n">
+        <v>37</v>
+      </c>
+      <c r="K343" t="n">
+        <v>10</v>
+      </c>
+      <c r="L343" t="n">
+        <v>15</v>
+      </c>
+      <c r="M343" t="n">
+        <v>6</v>
+      </c>
+      <c r="N343" t="n">
+        <v>21</v>
+      </c>
+      <c r="O343" t="n">
+        <v>11</v>
+      </c>
+      <c r="P343" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q343" t="n">
+        <v>9</v>
+      </c>
+      <c r="R343" t="n">
+        <v>31</v>
+      </c>
+      <c r="S343" t="n">
+        <v>20</v>
+      </c>
+      <c r="T343" t="n">
+        <v>2</v>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>2487931</t>
+        </is>
+      </c>
+      <c r="V343" t="n">
+        <v>87</v>
+      </c>
+      <c r="W343" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="X343" t="n">
+        <v>0.8971291866028709</v>
+      </c>
+      <c r="Y343" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="Z343" t="n">
+        <v>96.64948453608248</v>
+      </c>
+      <c r="AA343" t="n">
+        <v>1.075135936727632</v>
+      </c>
+      <c r="AB343" t="n">
+        <v>111.652977412731</v>
+      </c>
+      <c r="AC343" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AD343" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AE343" t="n">
+        <v>0.421875</v>
+      </c>
+      <c r="AF343" t="n">
+        <v>-15.00349287664852</v>
+      </c>
+      <c r="AG343" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="AH343" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="AI343" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>25</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>200</v>
+      </c>
+      <c r="F344" t="n">
+        <v>64</v>
+      </c>
+      <c r="G344" t="n">
+        <v>14</v>
+      </c>
+      <c r="H344" t="n">
+        <v>38</v>
+      </c>
+      <c r="I344" t="n">
+        <v>6</v>
+      </c>
+      <c r="J344" t="n">
+        <v>21</v>
+      </c>
+      <c r="K344" t="n">
+        <v>18</v>
+      </c>
+      <c r="L344" t="n">
+        <v>26</v>
+      </c>
+      <c r="M344" t="n">
+        <v>10</v>
+      </c>
+      <c r="N344" t="n">
+        <v>26</v>
+      </c>
+      <c r="O344" t="n">
+        <v>6</v>
+      </c>
+      <c r="P344" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q344" t="n">
+        <v>16</v>
+      </c>
+      <c r="R344" t="n">
+        <v>20</v>
+      </c>
+      <c r="S344" t="n">
+        <v>23</v>
+      </c>
+      <c r="T344" t="n">
+        <v>0</v>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>2487928</t>
+        </is>
+      </c>
+      <c r="V344" t="n">
+        <v>66</v>
+      </c>
+      <c r="W344" t="n">
+        <v>86.44</v>
+      </c>
+      <c r="X344" t="n">
+        <v>0.7403979639055993</v>
+      </c>
+      <c r="Y344" t="n">
+        <v>76.44</v>
+      </c>
+      <c r="Z344" t="n">
+        <v>83.7257980115123</v>
+      </c>
+      <c r="AA344" t="n">
+        <v>0.838840874428063</v>
+      </c>
+      <c r="AB344" t="n">
+        <v>90.80902586681341</v>
+      </c>
+      <c r="AC344" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AD344" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AE344" t="n">
+        <v>0.5373134328358209</v>
+      </c>
+      <c r="AF344" t="n">
+        <v>-7.083227855301118</v>
+      </c>
+      <c r="AG344" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="AH344" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="AI344" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>25</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>200</v>
+      </c>
+      <c r="F345" t="n">
+        <v>85</v>
+      </c>
+      <c r="G345" t="n">
+        <v>26</v>
+      </c>
+      <c r="H345" t="n">
+        <v>45</v>
+      </c>
+      <c r="I345" t="n">
+        <v>8</v>
+      </c>
+      <c r="J345" t="n">
+        <v>24</v>
+      </c>
+      <c r="K345" t="n">
+        <v>9</v>
+      </c>
+      <c r="L345" t="n">
+        <v>17</v>
+      </c>
+      <c r="M345" t="n">
+        <v>16</v>
+      </c>
+      <c r="N345" t="n">
+        <v>29</v>
+      </c>
+      <c r="O345" t="n">
+        <v>18</v>
+      </c>
+      <c r="P345" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q345" t="n">
+        <v>22</v>
+      </c>
+      <c r="R345" t="n">
+        <v>22</v>
+      </c>
+      <c r="S345" t="n">
+        <v>17</v>
+      </c>
+      <c r="T345" t="n">
+        <v>4</v>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>2487930</t>
+        </is>
+      </c>
+      <c r="V345" t="n">
+        <v>73</v>
+      </c>
+      <c r="W345" t="n">
+        <v>98.48</v>
+      </c>
+      <c r="X345" t="n">
+        <v>0.8631194151096669</v>
+      </c>
+      <c r="Y345" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="Z345" t="n">
+        <v>103.0552861299709</v>
+      </c>
+      <c r="AA345" t="n">
+        <v>0.7674516400336416</v>
+      </c>
+      <c r="AB345" t="n">
+        <v>85.76127819548871</v>
+      </c>
+      <c r="AC345" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="AD345" t="n">
+        <v>0.7435897435897436</v>
+      </c>
+      <c r="AE345" t="n">
+        <v>0.6164383561643836</v>
+      </c>
+      <c r="AF345" t="n">
+        <v>17.29400793448218</v>
+      </c>
+      <c r="AG345" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="AH345" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI345" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>25</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>200</v>
+      </c>
+      <c r="F346" t="n">
+        <v>73</v>
+      </c>
+      <c r="G346" t="n">
+        <v>21</v>
+      </c>
+      <c r="H346" t="n">
+        <v>42</v>
+      </c>
+      <c r="I346" t="n">
+        <v>6</v>
+      </c>
+      <c r="J346" t="n">
+        <v>24</v>
+      </c>
+      <c r="K346" t="n">
+        <v>13</v>
+      </c>
+      <c r="L346" t="n">
+        <v>23</v>
+      </c>
+      <c r="M346" t="n">
+        <v>10</v>
+      </c>
+      <c r="N346" t="n">
+        <v>18</v>
+      </c>
+      <c r="O346" t="n">
+        <v>12</v>
+      </c>
+      <c r="P346" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q346" t="n">
+        <v>19</v>
+      </c>
+      <c r="R346" t="n">
+        <v>17</v>
+      </c>
+      <c r="S346" t="n">
+        <v>22</v>
+      </c>
+      <c r="T346" t="n">
+        <v>4</v>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>2487930</t>
+        </is>
+      </c>
+      <c r="V346" t="n">
+        <v>85</v>
+      </c>
+      <c r="W346" t="n">
+        <v>95.12</v>
+      </c>
+      <c r="X346" t="n">
+        <v>0.7674516400336416</v>
+      </c>
+      <c r="Y346" t="n">
+        <v>85.12</v>
+      </c>
+      <c r="Z346" t="n">
+        <v>85.76127819548871</v>
+      </c>
+      <c r="AA346" t="n">
+        <v>0.8631194151096669</v>
+      </c>
+      <c r="AB346" t="n">
+        <v>103.0552861299709</v>
+      </c>
+      <c r="AC346" t="n">
+        <v>0.2564102564102564</v>
+      </c>
+      <c r="AD346" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="AE346" t="n">
+        <v>0.3835616438356164</v>
+      </c>
+      <c r="AF346" t="n">
+        <v>-17.29400793448218</v>
+      </c>
+      <c r="AG346" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="AH346" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI346" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>25</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>200</v>
+      </c>
+      <c r="F347" t="n">
+        <v>70</v>
+      </c>
+      <c r="G347" t="n">
+        <v>18</v>
+      </c>
+      <c r="H347" t="n">
+        <v>40</v>
+      </c>
+      <c r="I347" t="n">
+        <v>9</v>
+      </c>
+      <c r="J347" t="n">
+        <v>25</v>
+      </c>
+      <c r="K347" t="n">
+        <v>7</v>
+      </c>
+      <c r="L347" t="n">
+        <v>7</v>
+      </c>
+      <c r="M347" t="n">
+        <v>11</v>
+      </c>
+      <c r="N347" t="n">
+        <v>21</v>
+      </c>
+      <c r="O347" t="n">
+        <v>18</v>
+      </c>
+      <c r="P347" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>10</v>
+      </c>
+      <c r="R347" t="n">
+        <v>16</v>
+      </c>
+      <c r="S347" t="n">
+        <v>16</v>
+      </c>
+      <c r="T347" t="n">
+        <v>0</v>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>2487932</t>
+        </is>
+      </c>
+      <c r="V347" t="n">
+        <v>68</v>
+      </c>
+      <c r="W347" t="n">
+        <v>78.08</v>
+      </c>
+      <c r="X347" t="n">
+        <v>0.896516393442623</v>
+      </c>
+      <c r="Y347" t="n">
+        <v>67.08</v>
+      </c>
+      <c r="Z347" t="n">
+        <v>104.3530113297555</v>
+      </c>
+      <c r="AA347" t="n">
+        <v>0.8966244725738396</v>
+      </c>
+      <c r="AB347" t="n">
+        <v>103.2806804374241</v>
+      </c>
+      <c r="AC347" t="n">
+        <v>0.3235294117647059</v>
+      </c>
+      <c r="AD347" t="n">
+        <v>0.6774193548387096</v>
+      </c>
+      <c r="AE347" t="n">
+        <v>0.4923076923076923</v>
+      </c>
+      <c r="AF347" t="n">
+        <v>1.072330892331465</v>
+      </c>
+      <c r="AG347" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="AH347" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="AI347" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>25</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>200</v>
+      </c>
+      <c r="F348" t="n">
+        <v>71</v>
+      </c>
+      <c r="G348" t="n">
+        <v>16</v>
+      </c>
+      <c r="H348" t="n">
+        <v>37</v>
+      </c>
+      <c r="I348" t="n">
+        <v>9</v>
+      </c>
+      <c r="J348" t="n">
+        <v>25</v>
+      </c>
+      <c r="K348" t="n">
+        <v>12</v>
+      </c>
+      <c r="L348" t="n">
+        <v>15</v>
+      </c>
+      <c r="M348" t="n">
+        <v>10</v>
+      </c>
+      <c r="N348" t="n">
+        <v>13</v>
+      </c>
+      <c r="O348" t="n">
+        <v>9</v>
+      </c>
+      <c r="P348" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>11</v>
+      </c>
+      <c r="R348" t="n">
+        <v>11</v>
+      </c>
+      <c r="S348" t="n">
+        <v>21</v>
+      </c>
+      <c r="T348" t="n">
+        <v>0</v>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>2487933</t>
+        </is>
+      </c>
+      <c r="V348" t="n">
+        <v>102</v>
+      </c>
+      <c r="W348" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="X348" t="n">
+        <v>0.8919597989949749</v>
+      </c>
+      <c r="Y348" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="Z348" t="n">
+        <v>102.0114942528736</v>
+      </c>
+      <c r="AA348" t="n">
+        <v>1.259881422924901</v>
+      </c>
+      <c r="AB348" t="n">
+        <v>139.8026315789473</v>
+      </c>
+      <c r="AC348" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="AD348" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="AE348" t="n">
+        <v>0.4035087719298245</v>
+      </c>
+      <c r="AF348" t="n">
+        <v>-37.79113732607377</v>
+      </c>
+      <c r="AG348" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="AH348" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="AI348" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>25</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>200</v>
+      </c>
+      <c r="F349" t="n">
+        <v>68</v>
+      </c>
+      <c r="G349" t="n">
+        <v>20</v>
+      </c>
+      <c r="H349" t="n">
+        <v>37</v>
+      </c>
+      <c r="I349" t="n">
+        <v>7</v>
+      </c>
+      <c r="J349" t="n">
+        <v>24</v>
+      </c>
+      <c r="K349" t="n">
+        <v>7</v>
+      </c>
+      <c r="L349" t="n">
+        <v>11</v>
+      </c>
+      <c r="M349" t="n">
+        <v>10</v>
+      </c>
+      <c r="N349" t="n">
+        <v>23</v>
+      </c>
+      <c r="O349" t="n">
+        <v>15</v>
+      </c>
+      <c r="P349" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>10</v>
+      </c>
+      <c r="R349" t="n">
+        <v>16</v>
+      </c>
+      <c r="S349" t="n">
+        <v>16</v>
+      </c>
+      <c r="T349" t="n">
+        <v>4</v>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>2487932</t>
+        </is>
+      </c>
+      <c r="V349" t="n">
+        <v>70</v>
+      </c>
+      <c r="W349" t="n">
+        <v>75.84</v>
+      </c>
+      <c r="X349" t="n">
+        <v>0.8966244725738396</v>
+      </c>
+      <c r="Y349" t="n">
+        <v>65.84</v>
+      </c>
+      <c r="Z349" t="n">
+        <v>103.2806804374241</v>
+      </c>
+      <c r="AA349" t="n">
+        <v>0.896516393442623</v>
+      </c>
+      <c r="AB349" t="n">
+        <v>104.3530113297555</v>
+      </c>
+      <c r="AC349" t="n">
+        <v>0.3225806451612903</v>
+      </c>
+      <c r="AD349" t="n">
+        <v>0.6764705882352942</v>
+      </c>
+      <c r="AE349" t="n">
+        <v>0.5076923076923077</v>
+      </c>
+      <c r="AF349" t="n">
+        <v>-1.072330892331465</v>
+      </c>
+      <c r="AG349" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="AH349" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="AI349" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>25</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>200</v>
+      </c>
+      <c r="F350" t="n">
+        <v>85</v>
+      </c>
+      <c r="G350" t="n">
+        <v>24</v>
+      </c>
+      <c r="H350" t="n">
+        <v>35</v>
+      </c>
+      <c r="I350" t="n">
+        <v>8</v>
+      </c>
+      <c r="J350" t="n">
+        <v>31</v>
+      </c>
+      <c r="K350" t="n">
+        <v>13</v>
+      </c>
+      <c r="L350" t="n">
+        <v>20</v>
+      </c>
+      <c r="M350" t="n">
+        <v>10</v>
+      </c>
+      <c r="N350" t="n">
+        <v>27</v>
+      </c>
+      <c r="O350" t="n">
+        <v>22</v>
+      </c>
+      <c r="P350" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>12</v>
+      </c>
+      <c r="R350" t="n">
+        <v>24</v>
+      </c>
+      <c r="S350" t="n">
+        <v>21</v>
+      </c>
+      <c r="T350" t="n">
+        <v>0</v>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>2487929</t>
+        </is>
+      </c>
+      <c r="V350" t="n">
+        <v>68</v>
+      </c>
+      <c r="W350" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="X350" t="n">
+        <v>0.9792626728110599</v>
+      </c>
+      <c r="Y350" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="Z350" t="n">
+        <v>110.6770833333333</v>
+      </c>
+      <c r="AA350" t="n">
+        <v>0.8407517309594461</v>
+      </c>
+      <c r="AB350" t="n">
+        <v>90.81196581196582</v>
+      </c>
+      <c r="AC350" t="n">
+        <v>0.303030303030303</v>
+      </c>
+      <c r="AD350" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="AE350" t="n">
+        <v>0.5606060606060606</v>
+      </c>
+      <c r="AF350" t="n">
+        <v>19.86511752136752</v>
+      </c>
+      <c r="AG350" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="AH350" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="AI350" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>25</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>200</v>
+      </c>
+      <c r="F351" t="n">
+        <v>85</v>
+      </c>
+      <c r="G351" t="n">
+        <v>22</v>
+      </c>
+      <c r="H351" t="n">
+        <v>44</v>
+      </c>
+      <c r="I351" t="n">
+        <v>7</v>
+      </c>
+      <c r="J351" t="n">
+        <v>19</v>
+      </c>
+      <c r="K351" t="n">
+        <v>20</v>
+      </c>
+      <c r="L351" t="n">
+        <v>26</v>
+      </c>
+      <c r="M351" t="n">
+        <v>6</v>
+      </c>
+      <c r="N351" t="n">
+        <v>25</v>
+      </c>
+      <c r="O351" t="n">
+        <v>19</v>
+      </c>
+      <c r="P351" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>11</v>
+      </c>
+      <c r="R351" t="n">
+        <v>30</v>
+      </c>
+      <c r="S351" t="n">
+        <v>25</v>
+      </c>
+      <c r="T351" t="n">
+        <v>0</v>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>2487927</t>
+        </is>
+      </c>
+      <c r="V351" t="n">
+        <v>98</v>
+      </c>
+      <c r="W351" t="n">
+        <v>85.44</v>
+      </c>
+      <c r="X351" t="n">
+        <v>0.9948501872659177</v>
+      </c>
+      <c r="Y351" t="n">
+        <v>79.44</v>
+      </c>
+      <c r="Z351" t="n">
+        <v>106.9989929506546</v>
+      </c>
+      <c r="AA351" t="n">
+        <v>1.040781648258284</v>
+      </c>
+      <c r="AB351" t="n">
+        <v>119.2794547224927</v>
+      </c>
+      <c r="AC351" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="AD351" t="n">
+        <v>0.6756756756756757</v>
+      </c>
+      <c r="AE351" t="n">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="AF351" t="n">
+        <v>-12.28046177183812</v>
+      </c>
+      <c r="AG351" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="AH351" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="AI351" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/2FEB_25_26/players_25_26_2FEB_games.xlsx
+++ b/data/2FEB_25_26/players_25_26_2FEB_games.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI351"/>
+  <dimension ref="A1:AI365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -42252,6 +42252,1672 @@
         </is>
       </c>
       <c r="AI351" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>26</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>200</v>
+      </c>
+      <c r="F352" t="n">
+        <v>100</v>
+      </c>
+      <c r="G352" t="n">
+        <v>26</v>
+      </c>
+      <c r="H352" t="n">
+        <v>42</v>
+      </c>
+      <c r="I352" t="n">
+        <v>9</v>
+      </c>
+      <c r="J352" t="n">
+        <v>21</v>
+      </c>
+      <c r="K352" t="n">
+        <v>21</v>
+      </c>
+      <c r="L352" t="n">
+        <v>24</v>
+      </c>
+      <c r="M352" t="n">
+        <v>9</v>
+      </c>
+      <c r="N352" t="n">
+        <v>22</v>
+      </c>
+      <c r="O352" t="n">
+        <v>18</v>
+      </c>
+      <c r="P352" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>10</v>
+      </c>
+      <c r="R352" t="n">
+        <v>23</v>
+      </c>
+      <c r="S352" t="n">
+        <v>24</v>
+      </c>
+      <c r="T352" t="n">
+        <v>1</v>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>2487934</t>
+        </is>
+      </c>
+      <c r="V352" t="n">
+        <v>84</v>
+      </c>
+      <c r="W352" t="n">
+        <v>83.56</v>
+      </c>
+      <c r="X352" t="n">
+        <v>1.196744853997128</v>
+      </c>
+      <c r="Y352" t="n">
+        <v>74.56</v>
+      </c>
+      <c r="Z352" t="n">
+        <v>134.1201716738197</v>
+      </c>
+      <c r="AA352" t="n">
+        <v>0.9896324222431668</v>
+      </c>
+      <c r="AB352" t="n">
+        <v>109.261186264308</v>
+      </c>
+      <c r="AC352" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD352" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="AE352" t="n">
+        <v>0.543859649122807</v>
+      </c>
+      <c r="AF352" t="n">
+        <v>24.8589854095117</v>
+      </c>
+      <c r="AG352" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="AH352" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="AI352" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>26</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>200</v>
+      </c>
+      <c r="F353" t="n">
+        <v>75</v>
+      </c>
+      <c r="G353" t="n">
+        <v>22</v>
+      </c>
+      <c r="H353" t="n">
+        <v>42</v>
+      </c>
+      <c r="I353" t="n">
+        <v>7</v>
+      </c>
+      <c r="J353" t="n">
+        <v>17</v>
+      </c>
+      <c r="K353" t="n">
+        <v>10</v>
+      </c>
+      <c r="L353" t="n">
+        <v>17</v>
+      </c>
+      <c r="M353" t="n">
+        <v>6</v>
+      </c>
+      <c r="N353" t="n">
+        <v>20</v>
+      </c>
+      <c r="O353" t="n">
+        <v>18</v>
+      </c>
+      <c r="P353" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>15</v>
+      </c>
+      <c r="R353" t="n">
+        <v>22</v>
+      </c>
+      <c r="S353" t="n">
+        <v>19</v>
+      </c>
+      <c r="T353" t="n">
+        <v>0</v>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>2487936</t>
+        </is>
+      </c>
+      <c r="V353" t="n">
+        <v>84</v>
+      </c>
+      <c r="W353" t="n">
+        <v>81.48</v>
+      </c>
+      <c r="X353" t="n">
+        <v>0.9204712812960235</v>
+      </c>
+      <c r="Y353" t="n">
+        <v>75.48</v>
+      </c>
+      <c r="Z353" t="n">
+        <v>99.36406995230524</v>
+      </c>
+      <c r="AA353" t="n">
+        <v>0.9726725335803613</v>
+      </c>
+      <c r="AB353" t="n">
+        <v>111.4649681528662</v>
+      </c>
+      <c r="AC353" t="n">
+        <v>0.2068965517241379</v>
+      </c>
+      <c r="AD353" t="n">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="AE353" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="AF353" t="n">
+        <v>-12.10089820056101</v>
+      </c>
+      <c r="AG353" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="AH353" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="AI353" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>26</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>200</v>
+      </c>
+      <c r="F354" t="n">
+        <v>77</v>
+      </c>
+      <c r="G354" t="n">
+        <v>16</v>
+      </c>
+      <c r="H354" t="n">
+        <v>36</v>
+      </c>
+      <c r="I354" t="n">
+        <v>10</v>
+      </c>
+      <c r="J354" t="n">
+        <v>29</v>
+      </c>
+      <c r="K354" t="n">
+        <v>15</v>
+      </c>
+      <c r="L354" t="n">
+        <v>24</v>
+      </c>
+      <c r="M354" t="n">
+        <v>13</v>
+      </c>
+      <c r="N354" t="n">
+        <v>18</v>
+      </c>
+      <c r="O354" t="n">
+        <v>9</v>
+      </c>
+      <c r="P354" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>10</v>
+      </c>
+      <c r="R354" t="n">
+        <v>21</v>
+      </c>
+      <c r="S354" t="n">
+        <v>24</v>
+      </c>
+      <c r="T354" t="n">
+        <v>2</v>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>2487940</t>
+        </is>
+      </c>
+      <c r="V354" t="n">
+        <v>75</v>
+      </c>
+      <c r="W354" t="n">
+        <v>85.56</v>
+      </c>
+      <c r="X354" t="n">
+        <v>0.8999532491818607</v>
+      </c>
+      <c r="Y354" t="n">
+        <v>72.56</v>
+      </c>
+      <c r="Z354" t="n">
+        <v>106.1190738699008</v>
+      </c>
+      <c r="AA354" t="n">
+        <v>0.8449752140603877</v>
+      </c>
+      <c r="AB354" t="n">
+        <v>103.0786146234195</v>
+      </c>
+      <c r="AC354" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AD354" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="AE354" t="n">
+        <v>0.4189189189189189</v>
+      </c>
+      <c r="AF354" t="n">
+        <v>3.040459246481305</v>
+      </c>
+      <c r="AG354" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="AH354" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="AI354" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>26</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>200</v>
+      </c>
+      <c r="F355" t="n">
+        <v>69</v>
+      </c>
+      <c r="G355" t="n">
+        <v>13</v>
+      </c>
+      <c r="H355" t="n">
+        <v>31</v>
+      </c>
+      <c r="I355" t="n">
+        <v>9</v>
+      </c>
+      <c r="J355" t="n">
+        <v>25</v>
+      </c>
+      <c r="K355" t="n">
+        <v>16</v>
+      </c>
+      <c r="L355" t="n">
+        <v>30</v>
+      </c>
+      <c r="M355" t="n">
+        <v>11</v>
+      </c>
+      <c r="N355" t="n">
+        <v>25</v>
+      </c>
+      <c r="O355" t="n">
+        <v>14</v>
+      </c>
+      <c r="P355" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>18</v>
+      </c>
+      <c r="R355" t="n">
+        <v>22</v>
+      </c>
+      <c r="S355" t="n">
+        <v>23</v>
+      </c>
+      <c r="T355" t="n">
+        <v>2</v>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>2487939</t>
+        </is>
+      </c>
+      <c r="V355" t="n">
+        <v>80</v>
+      </c>
+      <c r="W355" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="X355" t="n">
+        <v>0.7912844036697247</v>
+      </c>
+      <c r="Y355" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="Z355" t="n">
+        <v>90.55118110236221</v>
+      </c>
+      <c r="AA355" t="n">
+        <v>0.9000900090009001</v>
+      </c>
+      <c r="AB355" t="n">
+        <v>108.283703302653</v>
+      </c>
+      <c r="AC355" t="n">
+        <v>0.3055555555555556</v>
+      </c>
+      <c r="AD355" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AE355" t="n">
+        <v>0.4736842105263158</v>
+      </c>
+      <c r="AF355" t="n">
+        <v>-17.73252220029075</v>
+      </c>
+      <c r="AG355" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="AH355" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="AI355" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>26</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>200</v>
+      </c>
+      <c r="F356" t="n">
+        <v>75</v>
+      </c>
+      <c r="G356" t="n">
+        <v>17</v>
+      </c>
+      <c r="H356" t="n">
+        <v>35</v>
+      </c>
+      <c r="I356" t="n">
+        <v>7</v>
+      </c>
+      <c r="J356" t="n">
+        <v>25</v>
+      </c>
+      <c r="K356" t="n">
+        <v>20</v>
+      </c>
+      <c r="L356" t="n">
+        <v>29</v>
+      </c>
+      <c r="M356" t="n">
+        <v>16</v>
+      </c>
+      <c r="N356" t="n">
+        <v>27</v>
+      </c>
+      <c r="O356" t="n">
+        <v>17</v>
+      </c>
+      <c r="P356" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>16</v>
+      </c>
+      <c r="R356" t="n">
+        <v>24</v>
+      </c>
+      <c r="S356" t="n">
+        <v>21</v>
+      </c>
+      <c r="T356" t="n">
+        <v>1</v>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>2487940</t>
+        </is>
+      </c>
+      <c r="V356" t="n">
+        <v>77</v>
+      </c>
+      <c r="W356" t="n">
+        <v>88.75999999999999</v>
+      </c>
+      <c r="X356" t="n">
+        <v>0.8449752140603877</v>
+      </c>
+      <c r="Y356" t="n">
+        <v>72.75999999999999</v>
+      </c>
+      <c r="Z356" t="n">
+        <v>103.0786146234195</v>
+      </c>
+      <c r="AA356" t="n">
+        <v>0.8999532491818607</v>
+      </c>
+      <c r="AB356" t="n">
+        <v>106.1190738699008</v>
+      </c>
+      <c r="AC356" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="AD356" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="AE356" t="n">
+        <v>0.581081081081081</v>
+      </c>
+      <c r="AF356" t="n">
+        <v>-3.040459246481305</v>
+      </c>
+      <c r="AG356" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="AH356" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="AI356" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>26</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>200</v>
+      </c>
+      <c r="F357" t="n">
+        <v>83</v>
+      </c>
+      <c r="G357" t="n">
+        <v>21</v>
+      </c>
+      <c r="H357" t="n">
+        <v>36</v>
+      </c>
+      <c r="I357" t="n">
+        <v>11</v>
+      </c>
+      <c r="J357" t="n">
+        <v>32</v>
+      </c>
+      <c r="K357" t="n">
+        <v>8</v>
+      </c>
+      <c r="L357" t="n">
+        <v>8</v>
+      </c>
+      <c r="M357" t="n">
+        <v>11</v>
+      </c>
+      <c r="N357" t="n">
+        <v>31</v>
+      </c>
+      <c r="O357" t="n">
+        <v>19</v>
+      </c>
+      <c r="P357" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>18</v>
+      </c>
+      <c r="R357" t="n">
+        <v>18</v>
+      </c>
+      <c r="S357" t="n">
+        <v>15</v>
+      </c>
+      <c r="T357" t="n">
+        <v>1</v>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>2487937</t>
+        </is>
+      </c>
+      <c r="V357" t="n">
+        <v>54</v>
+      </c>
+      <c r="W357" t="n">
+        <v>89.52000000000001</v>
+      </c>
+      <c r="X357" t="n">
+        <v>0.9271671134941911</v>
+      </c>
+      <c r="Y357" t="n">
+        <v>78.52000000000001</v>
+      </c>
+      <c r="Z357" t="n">
+        <v>105.7055527254203</v>
+      </c>
+      <c r="AA357" t="n">
+        <v>0.6493506493506493</v>
+      </c>
+      <c r="AB357" t="n">
+        <v>69.98444790046656</v>
+      </c>
+      <c r="AC357" t="n">
+        <v>0.3235294117647059</v>
+      </c>
+      <c r="AD357" t="n">
+        <v>0.8378378378378378</v>
+      </c>
+      <c r="AE357" t="n">
+        <v>0.5915492957746479</v>
+      </c>
+      <c r="AF357" t="n">
+        <v>35.7211048249537</v>
+      </c>
+      <c r="AG357" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH357" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="AI357" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>26</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>200</v>
+      </c>
+      <c r="F358" t="n">
+        <v>80</v>
+      </c>
+      <c r="G358" t="n">
+        <v>15</v>
+      </c>
+      <c r="H358" t="n">
+        <v>29</v>
+      </c>
+      <c r="I358" t="n">
+        <v>11</v>
+      </c>
+      <c r="J358" t="n">
+        <v>33</v>
+      </c>
+      <c r="K358" t="n">
+        <v>17</v>
+      </c>
+      <c r="L358" t="n">
+        <v>27</v>
+      </c>
+      <c r="M358" t="n">
+        <v>15</v>
+      </c>
+      <c r="N358" t="n">
+        <v>25</v>
+      </c>
+      <c r="O358" t="n">
+        <v>16</v>
+      </c>
+      <c r="P358" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>15</v>
+      </c>
+      <c r="R358" t="n">
+        <v>24</v>
+      </c>
+      <c r="S358" t="n">
+        <v>22</v>
+      </c>
+      <c r="T358" t="n">
+        <v>2</v>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>2487939</t>
+        </is>
+      </c>
+      <c r="V358" t="n">
+        <v>69</v>
+      </c>
+      <c r="W358" t="n">
+        <v>88.88</v>
+      </c>
+      <c r="X358" t="n">
+        <v>0.9000900090009001</v>
+      </c>
+      <c r="Y358" t="n">
+        <v>73.88</v>
+      </c>
+      <c r="Z358" t="n">
+        <v>108.283703302653</v>
+      </c>
+      <c r="AA358" t="n">
+        <v>0.7912844036697247</v>
+      </c>
+      <c r="AB358" t="n">
+        <v>90.55118110236221</v>
+      </c>
+      <c r="AC358" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AD358" t="n">
+        <v>0.6944444444444444</v>
+      </c>
+      <c r="AE358" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+      <c r="AF358" t="n">
+        <v>17.73252220029075</v>
+      </c>
+      <c r="AG358" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="AH358" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="AI358" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>26</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>200</v>
+      </c>
+      <c r="F359" t="n">
+        <v>88</v>
+      </c>
+      <c r="G359" t="n">
+        <v>31</v>
+      </c>
+      <c r="H359" t="n">
+        <v>53</v>
+      </c>
+      <c r="I359" t="n">
+        <v>5</v>
+      </c>
+      <c r="J359" t="n">
+        <v>12</v>
+      </c>
+      <c r="K359" t="n">
+        <v>11</v>
+      </c>
+      <c r="L359" t="n">
+        <v>19</v>
+      </c>
+      <c r="M359" t="n">
+        <v>7</v>
+      </c>
+      <c r="N359" t="n">
+        <v>24</v>
+      </c>
+      <c r="O359" t="n">
+        <v>18</v>
+      </c>
+      <c r="P359" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>12</v>
+      </c>
+      <c r="R359" t="n">
+        <v>25</v>
+      </c>
+      <c r="S359" t="n">
+        <v>21</v>
+      </c>
+      <c r="T359" t="n">
+        <v>3</v>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>2487938</t>
+        </is>
+      </c>
+      <c r="V359" t="n">
+        <v>91</v>
+      </c>
+      <c r="W359" t="n">
+        <v>85.36</v>
+      </c>
+      <c r="X359" t="n">
+        <v>1.030927835051547</v>
+      </c>
+      <c r="Y359" t="n">
+        <v>78.36</v>
+      </c>
+      <c r="Z359" t="n">
+        <v>112.3021949974477</v>
+      </c>
+      <c r="AA359" t="n">
+        <v>0.9964958388085853</v>
+      </c>
+      <c r="AB359" t="n">
+        <v>114.7251638930913</v>
+      </c>
+      <c r="AC359" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="AD359" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE359" t="n">
+        <v>0.4696969696969697</v>
+      </c>
+      <c r="AF359" t="n">
+        <v>-2.422968895643621</v>
+      </c>
+      <c r="AG359" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="AH359" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="AI359" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>26</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>200</v>
+      </c>
+      <c r="F360" t="n">
+        <v>54</v>
+      </c>
+      <c r="G360" t="n">
+        <v>14</v>
+      </c>
+      <c r="H360" t="n">
+        <v>39</v>
+      </c>
+      <c r="I360" t="n">
+        <v>5</v>
+      </c>
+      <c r="J360" t="n">
+        <v>22</v>
+      </c>
+      <c r="K360" t="n">
+        <v>11</v>
+      </c>
+      <c r="L360" t="n">
+        <v>14</v>
+      </c>
+      <c r="M360" t="n">
+        <v>6</v>
+      </c>
+      <c r="N360" t="n">
+        <v>23</v>
+      </c>
+      <c r="O360" t="n">
+        <v>8</v>
+      </c>
+      <c r="P360" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>16</v>
+      </c>
+      <c r="R360" t="n">
+        <v>15</v>
+      </c>
+      <c r="S360" t="n">
+        <v>18</v>
+      </c>
+      <c r="T360" t="n">
+        <v>1</v>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>2487937</t>
+        </is>
+      </c>
+      <c r="V360" t="n">
+        <v>83</v>
+      </c>
+      <c r="W360" t="n">
+        <v>83.16</v>
+      </c>
+      <c r="X360" t="n">
+        <v>0.6493506493506493</v>
+      </c>
+      <c r="Y360" t="n">
+        <v>77.16</v>
+      </c>
+      <c r="Z360" t="n">
+        <v>69.98444790046656</v>
+      </c>
+      <c r="AA360" t="n">
+        <v>0.9271671134941911</v>
+      </c>
+      <c r="AB360" t="n">
+        <v>105.7055527254203</v>
+      </c>
+      <c r="AC360" t="n">
+        <v>0.1621621621621622</v>
+      </c>
+      <c r="AD360" t="n">
+        <v>0.6764705882352942</v>
+      </c>
+      <c r="AE360" t="n">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="AF360" t="n">
+        <v>-35.7211048249537</v>
+      </c>
+      <c r="AG360" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH360" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="AI360" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>26</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>200</v>
+      </c>
+      <c r="F361" t="n">
+        <v>84</v>
+      </c>
+      <c r="G361" t="n">
+        <v>26</v>
+      </c>
+      <c r="H361" t="n">
+        <v>37</v>
+      </c>
+      <c r="I361" t="n">
+        <v>6</v>
+      </c>
+      <c r="J361" t="n">
+        <v>29</v>
+      </c>
+      <c r="K361" t="n">
+        <v>14</v>
+      </c>
+      <c r="L361" t="n">
+        <v>19</v>
+      </c>
+      <c r="M361" t="n">
+        <v>11</v>
+      </c>
+      <c r="N361" t="n">
+        <v>23</v>
+      </c>
+      <c r="O361" t="n">
+        <v>18</v>
+      </c>
+      <c r="P361" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>12</v>
+      </c>
+      <c r="R361" t="n">
+        <v>19</v>
+      </c>
+      <c r="S361" t="n">
+        <v>21</v>
+      </c>
+      <c r="T361" t="n">
+        <v>4</v>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>2487936</t>
+        </is>
+      </c>
+      <c r="V361" t="n">
+        <v>75</v>
+      </c>
+      <c r="W361" t="n">
+        <v>86.36</v>
+      </c>
+      <c r="X361" t="n">
+        <v>0.9726725335803613</v>
+      </c>
+      <c r="Y361" t="n">
+        <v>75.36</v>
+      </c>
+      <c r="Z361" t="n">
+        <v>111.4649681528662</v>
+      </c>
+      <c r="AA361" t="n">
+        <v>0.9204712812960235</v>
+      </c>
+      <c r="AB361" t="n">
+        <v>99.36406995230524</v>
+      </c>
+      <c r="AC361" t="n">
+        <v>0.3548387096774194</v>
+      </c>
+      <c r="AD361" t="n">
+        <v>0.7931034482758621</v>
+      </c>
+      <c r="AE361" t="n">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="AF361" t="n">
+        <v>12.10089820056101</v>
+      </c>
+      <c r="AG361" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="AH361" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="AI361" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>26</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>200</v>
+      </c>
+      <c r="F362" t="n">
+        <v>73</v>
+      </c>
+      <c r="G362" t="n">
+        <v>10</v>
+      </c>
+      <c r="H362" t="n">
+        <v>29</v>
+      </c>
+      <c r="I362" t="n">
+        <v>12</v>
+      </c>
+      <c r="J362" t="n">
+        <v>30</v>
+      </c>
+      <c r="K362" t="n">
+        <v>17</v>
+      </c>
+      <c r="L362" t="n">
+        <v>20</v>
+      </c>
+      <c r="M362" t="n">
+        <v>10</v>
+      </c>
+      <c r="N362" t="n">
+        <v>18</v>
+      </c>
+      <c r="O362" t="n">
+        <v>13</v>
+      </c>
+      <c r="P362" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>13</v>
+      </c>
+      <c r="R362" t="n">
+        <v>29</v>
+      </c>
+      <c r="S362" t="n">
+        <v>20</v>
+      </c>
+      <c r="T362" t="n">
+        <v>1</v>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>2487935</t>
+        </is>
+      </c>
+      <c r="V362" t="n">
+        <v>69</v>
+      </c>
+      <c r="W362" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="X362" t="n">
+        <v>0.9034653465346535</v>
+      </c>
+      <c r="Y362" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="Z362" t="n">
+        <v>103.1073446327684</v>
+      </c>
+      <c r="AA362" t="n">
+        <v>0.7649667405764966</v>
+      </c>
+      <c r="AB362" t="n">
+        <v>88.23529411764706</v>
+      </c>
+      <c r="AC362" t="n">
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="AD362" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AE362" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AF362" t="n">
+        <v>14.8720505151213</v>
+      </c>
+      <c r="AG362" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="AH362" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="AI362" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>26</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>200</v>
+      </c>
+      <c r="F363" t="n">
+        <v>69</v>
+      </c>
+      <c r="G363" t="n">
+        <v>14</v>
+      </c>
+      <c r="H363" t="n">
+        <v>28</v>
+      </c>
+      <c r="I363" t="n">
+        <v>8</v>
+      </c>
+      <c r="J363" t="n">
+        <v>29</v>
+      </c>
+      <c r="K363" t="n">
+        <v>17</v>
+      </c>
+      <c r="L363" t="n">
+        <v>30</v>
+      </c>
+      <c r="M363" t="n">
+        <v>12</v>
+      </c>
+      <c r="N363" t="n">
+        <v>24</v>
+      </c>
+      <c r="O363" t="n">
+        <v>13</v>
+      </c>
+      <c r="P363" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>20</v>
+      </c>
+      <c r="R363" t="n">
+        <v>20</v>
+      </c>
+      <c r="S363" t="n">
+        <v>29</v>
+      </c>
+      <c r="T363" t="n">
+        <v>3</v>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>2487935</t>
+        </is>
+      </c>
+      <c r="V363" t="n">
+        <v>73</v>
+      </c>
+      <c r="W363" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="X363" t="n">
+        <v>0.7649667405764966</v>
+      </c>
+      <c r="Y363" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="Z363" t="n">
+        <v>88.23529411764706</v>
+      </c>
+      <c r="AA363" t="n">
+        <v>0.9034653465346535</v>
+      </c>
+      <c r="AB363" t="n">
+        <v>103.1073446327684</v>
+      </c>
+      <c r="AC363" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD363" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="AE363" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="AF363" t="n">
+        <v>-14.8720505151213</v>
+      </c>
+      <c r="AG363" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="AH363" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="AI363" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>26</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>200</v>
+      </c>
+      <c r="F364" t="n">
+        <v>91</v>
+      </c>
+      <c r="G364" t="n">
+        <v>18</v>
+      </c>
+      <c r="H364" t="n">
+        <v>38</v>
+      </c>
+      <c r="I364" t="n">
+        <v>14</v>
+      </c>
+      <c r="J364" t="n">
+        <v>27</v>
+      </c>
+      <c r="K364" t="n">
+        <v>13</v>
+      </c>
+      <c r="L364" t="n">
+        <v>28</v>
+      </c>
+      <c r="M364" t="n">
+        <v>12</v>
+      </c>
+      <c r="N364" t="n">
+        <v>23</v>
+      </c>
+      <c r="O364" t="n">
+        <v>17</v>
+      </c>
+      <c r="P364" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>14</v>
+      </c>
+      <c r="R364" t="n">
+        <v>22</v>
+      </c>
+      <c r="S364" t="n">
+        <v>25</v>
+      </c>
+      <c r="T364" t="n">
+        <v>3</v>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>2487938</t>
+        </is>
+      </c>
+      <c r="V364" t="n">
+        <v>88</v>
+      </c>
+      <c r="W364" t="n">
+        <v>91.31999999999999</v>
+      </c>
+      <c r="X364" t="n">
+        <v>0.9964958388085853</v>
+      </c>
+      <c r="Y364" t="n">
+        <v>79.31999999999999</v>
+      </c>
+      <c r="Z364" t="n">
+        <v>114.7251638930913</v>
+      </c>
+      <c r="AA364" t="n">
+        <v>1.030927835051547</v>
+      </c>
+      <c r="AB364" t="n">
+        <v>112.3021949974477</v>
+      </c>
+      <c r="AC364" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD364" t="n">
+        <v>0.7666666666666667</v>
+      </c>
+      <c r="AE364" t="n">
+        <v>0.5303030303030303</v>
+      </c>
+      <c r="AF364" t="n">
+        <v>2.422968895643621</v>
+      </c>
+      <c r="AG364" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="AH364" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="AI364" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>26</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>200</v>
+      </c>
+      <c r="F365" t="n">
+        <v>84</v>
+      </c>
+      <c r="G365" t="n">
+        <v>25</v>
+      </c>
+      <c r="H365" t="n">
+        <v>45</v>
+      </c>
+      <c r="I365" t="n">
+        <v>5</v>
+      </c>
+      <c r="J365" t="n">
+        <v>16</v>
+      </c>
+      <c r="K365" t="n">
+        <v>19</v>
+      </c>
+      <c r="L365" t="n">
+        <v>27</v>
+      </c>
+      <c r="M365" t="n">
+        <v>8</v>
+      </c>
+      <c r="N365" t="n">
+        <v>18</v>
+      </c>
+      <c r="O365" t="n">
+        <v>12</v>
+      </c>
+      <c r="P365" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>12</v>
+      </c>
+      <c r="R365" t="n">
+        <v>24</v>
+      </c>
+      <c r="S365" t="n">
+        <v>23</v>
+      </c>
+      <c r="T365" t="n">
+        <v>2</v>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>2487934</t>
+        </is>
+      </c>
+      <c r="V365" t="n">
+        <v>100</v>
+      </c>
+      <c r="W365" t="n">
+        <v>84.88</v>
+      </c>
+      <c r="X365" t="n">
+        <v>0.9896324222431668</v>
+      </c>
+      <c r="Y365" t="n">
+        <v>76.88</v>
+      </c>
+      <c r="Z365" t="n">
+        <v>109.261186264308</v>
+      </c>
+      <c r="AA365" t="n">
+        <v>1.196744853997128</v>
+      </c>
+      <c r="AB365" t="n">
+        <v>134.1201716738197</v>
+      </c>
+      <c r="AC365" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="AD365" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE365" t="n">
+        <v>0.456140350877193</v>
+      </c>
+      <c r="AF365" t="n">
+        <v>-24.8589854095117</v>
+      </c>
+      <c r="AG365" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="AH365" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="AI365" t="b">
         <v>1</v>
       </c>
     </row>

--- a/data/2FEB_25_26/players_25_26_2FEB_games.xlsx
+++ b/data/2FEB_25_26/players_25_26_2FEB_games.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI365"/>
+  <dimension ref="A1:AI323"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38921,5004 +38921,6 @@
       </c>
       <c r="AI323" t="b">
         <v>0</v>
-      </c>
-    </row>
-    <row r="324">
-      <c r="A324" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B324" t="n">
-        <v>24</v>
-      </c>
-      <c r="C324" t="inlineStr">
-        <is>
-          <t>BIELE ISB</t>
-        </is>
-      </c>
-      <c r="D324" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="E324" t="n">
-        <v>200</v>
-      </c>
-      <c r="F324" t="n">
-        <v>81</v>
-      </c>
-      <c r="G324" t="n">
-        <v>23</v>
-      </c>
-      <c r="H324" t="n">
-        <v>34</v>
-      </c>
-      <c r="I324" t="n">
-        <v>8</v>
-      </c>
-      <c r="J324" t="n">
-        <v>24</v>
-      </c>
-      <c r="K324" t="n">
-        <v>11</v>
-      </c>
-      <c r="L324" t="n">
-        <v>13</v>
-      </c>
-      <c r="M324" t="n">
-        <v>7</v>
-      </c>
-      <c r="N324" t="n">
-        <v>22</v>
-      </c>
-      <c r="O324" t="n">
-        <v>15</v>
-      </c>
-      <c r="P324" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q324" t="n">
-        <v>10</v>
-      </c>
-      <c r="R324" t="n">
-        <v>24</v>
-      </c>
-      <c r="S324" t="n">
-        <v>18</v>
-      </c>
-      <c r="T324" t="n">
-        <v>3</v>
-      </c>
-      <c r="U324" t="inlineStr">
-        <is>
-          <t>2487921</t>
-        </is>
-      </c>
-      <c r="V324" t="n">
-        <v>79</v>
-      </c>
-      <c r="W324" t="n">
-        <v>73.72</v>
-      </c>
-      <c r="X324" t="n">
-        <v>1.09875203472599</v>
-      </c>
-      <c r="Y324" t="n">
-        <v>66.72</v>
-      </c>
-      <c r="Z324" t="n">
-        <v>121.4028776978417</v>
-      </c>
-      <c r="AA324" t="n">
-        <v>0.9440726577437858</v>
-      </c>
-      <c r="AB324" t="n">
-        <v>107.2204125950054</v>
-      </c>
-      <c r="AC324" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="AD324" t="n">
-        <v>0.6875</v>
-      </c>
-      <c r="AE324" t="n">
-        <v>0.5087719298245614</v>
-      </c>
-      <c r="AF324" t="n">
-        <v>14.18246510283632</v>
-      </c>
-      <c r="AG324" t="inlineStr">
-        <is>
-          <t>BIELE ISB</t>
-        </is>
-      </c>
-      <c r="AH324" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="AI324" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="325">
-      <c r="A325" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B325" t="n">
-        <v>24</v>
-      </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>C.B. STARLABS MORÓN</t>
-        </is>
-      </c>
-      <c r="D325" t="inlineStr">
-        <is>
-          <t>CULTURAL Y DEPORTIVA LEONESA</t>
-        </is>
-      </c>
-      <c r="E325" t="n">
-        <v>200</v>
-      </c>
-      <c r="F325" t="n">
-        <v>93</v>
-      </c>
-      <c r="G325" t="n">
-        <v>18</v>
-      </c>
-      <c r="H325" t="n">
-        <v>34</v>
-      </c>
-      <c r="I325" t="n">
-        <v>13</v>
-      </c>
-      <c r="J325" t="n">
-        <v>19</v>
-      </c>
-      <c r="K325" t="n">
-        <v>18</v>
-      </c>
-      <c r="L325" t="n">
-        <v>28</v>
-      </c>
-      <c r="M325" t="n">
-        <v>7</v>
-      </c>
-      <c r="N325" t="n">
-        <v>23</v>
-      </c>
-      <c r="O325" t="n">
-        <v>24</v>
-      </c>
-      <c r="P325" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q325" t="n">
-        <v>15</v>
-      </c>
-      <c r="R325" t="n">
-        <v>16</v>
-      </c>
-      <c r="S325" t="n">
-        <v>23</v>
-      </c>
-      <c r="T325" t="n">
-        <v>1</v>
-      </c>
-      <c r="U325" t="inlineStr">
-        <is>
-          <t>2487923</t>
-        </is>
-      </c>
-      <c r="V325" t="n">
-        <v>83</v>
-      </c>
-      <c r="W325" t="n">
-        <v>80.31999999999999</v>
-      </c>
-      <c r="X325" t="n">
-        <v>1.157868525896415</v>
-      </c>
-      <c r="Y325" t="n">
-        <v>73.31999999999999</v>
-      </c>
-      <c r="Z325" t="n">
-        <v>126.8412438625205</v>
-      </c>
-      <c r="AA325" t="n">
-        <v>0.8257063270990848</v>
-      </c>
-      <c r="AB325" t="n">
-        <v>104.3762575452716</v>
-      </c>
-      <c r="AC325" t="n">
-        <v>0.2916666666666667</v>
-      </c>
-      <c r="AD325" t="n">
-        <v>0.5227272727272727</v>
-      </c>
-      <c r="AE325" t="n">
-        <v>0.4411764705882353</v>
-      </c>
-      <c r="AF325" t="n">
-        <v>22.46498631724883</v>
-      </c>
-      <c r="AG325" t="inlineStr">
-        <is>
-          <t>C.B. STARLABS MORÓN</t>
-        </is>
-      </c>
-      <c r="AH325" t="inlineStr">
-        <is>
-          <t>CULTURAL Y DEPORTIVA LEONESA</t>
-        </is>
-      </c>
-      <c r="AI325" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="326">
-      <c r="A326" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B326" t="n">
-        <v>24</v>
-      </c>
-      <c r="C326" t="inlineStr">
-        <is>
-          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
-        </is>
-      </c>
-      <c r="D326" t="inlineStr">
-        <is>
-          <t>COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-      <c r="E326" t="n">
-        <v>200</v>
-      </c>
-      <c r="F326" t="n">
-        <v>58</v>
-      </c>
-      <c r="G326" t="n">
-        <v>16</v>
-      </c>
-      <c r="H326" t="n">
-        <v>37</v>
-      </c>
-      <c r="I326" t="n">
-        <v>6</v>
-      </c>
-      <c r="J326" t="n">
-        <v>32</v>
-      </c>
-      <c r="K326" t="n">
-        <v>8</v>
-      </c>
-      <c r="L326" t="n">
-        <v>18</v>
-      </c>
-      <c r="M326" t="n">
-        <v>17</v>
-      </c>
-      <c r="N326" t="n">
-        <v>25</v>
-      </c>
-      <c r="O326" t="n">
-        <v>6</v>
-      </c>
-      <c r="P326" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q326" t="n">
-        <v>10</v>
-      </c>
-      <c r="R326" t="n">
-        <v>20</v>
-      </c>
-      <c r="S326" t="n">
-        <v>22</v>
-      </c>
-      <c r="T326" t="n">
-        <v>2</v>
-      </c>
-      <c r="U326" t="inlineStr">
-        <is>
-          <t>2487926</t>
-        </is>
-      </c>
-      <c r="V326" t="n">
-        <v>70</v>
-      </c>
-      <c r="W326" t="n">
-        <v>86.92</v>
-      </c>
-      <c r="X326" t="n">
-        <v>0.6672802577082374</v>
-      </c>
-      <c r="Y326" t="n">
-        <v>69.92</v>
-      </c>
-      <c r="Z326" t="n">
-        <v>82.95194508009153</v>
-      </c>
-      <c r="AA326" t="n">
-        <v>0.9039256198347108</v>
-      </c>
-      <c r="AB326" t="n">
-        <v>100.8064516129032</v>
-      </c>
-      <c r="AC326" t="n">
-        <v>0.3541666666666667</v>
-      </c>
-      <c r="AD326" t="n">
-        <v>0.7575757575757576</v>
-      </c>
-      <c r="AE326" t="n">
-        <v>0.5185185185185185</v>
-      </c>
-      <c r="AF326" t="n">
-        <v>-17.8545065328117</v>
-      </c>
-      <c r="AG326" t="inlineStr">
-        <is>
-          <t>COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-      <c r="AH326" t="inlineStr">
-        <is>
-          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
-        </is>
-      </c>
-      <c r="AI326" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="327">
-      <c r="A327" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B327" t="n">
-        <v>24</v>
-      </c>
-      <c r="C327" t="inlineStr">
-        <is>
-          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-      <c r="D327" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO</t>
-        </is>
-      </c>
-      <c r="E327" t="n">
-        <v>200</v>
-      </c>
-      <c r="F327" t="n">
-        <v>83</v>
-      </c>
-      <c r="G327" t="n">
-        <v>23</v>
-      </c>
-      <c r="H327" t="n">
-        <v>44</v>
-      </c>
-      <c r="I327" t="n">
-        <v>9</v>
-      </c>
-      <c r="J327" t="n">
-        <v>22</v>
-      </c>
-      <c r="K327" t="n">
-        <v>10</v>
-      </c>
-      <c r="L327" t="n">
-        <v>16</v>
-      </c>
-      <c r="M327" t="n">
-        <v>7</v>
-      </c>
-      <c r="N327" t="n">
-        <v>23</v>
-      </c>
-      <c r="O327" t="n">
-        <v>18</v>
-      </c>
-      <c r="P327" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q327" t="n">
-        <v>13</v>
-      </c>
-      <c r="R327" t="n">
-        <v>18</v>
-      </c>
-      <c r="S327" t="n">
-        <v>18</v>
-      </c>
-      <c r="T327" t="n">
-        <v>2</v>
-      </c>
-      <c r="U327" t="inlineStr">
-        <is>
-          <t>2487924</t>
-        </is>
-      </c>
-      <c r="V327" t="n">
-        <v>81</v>
-      </c>
-      <c r="W327" t="n">
-        <v>86.03999999999999</v>
-      </c>
-      <c r="X327" t="n">
-        <v>0.9646675964667597</v>
-      </c>
-      <c r="Y327" t="n">
-        <v>79.03999999999999</v>
-      </c>
-      <c r="Z327" t="n">
-        <v>105.0101214574899</v>
-      </c>
-      <c r="AA327" t="n">
-        <v>0.8996001776988006</v>
-      </c>
-      <c r="AB327" t="n">
-        <v>106.5228826933193</v>
-      </c>
-      <c r="AC327" t="n">
-        <v>0.21875</v>
-      </c>
-      <c r="AD327" t="n">
-        <v>0.6216216216216216</v>
-      </c>
-      <c r="AE327" t="n">
-        <v>0.4347826086956522</v>
-      </c>
-      <c r="AF327" t="n">
-        <v>-1.51276123582943</v>
-      </c>
-      <c r="AG327" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AH327" t="inlineStr">
-        <is>
-          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-      <c r="AI327" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="328">
-      <c r="A328" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B328" t="n">
-        <v>24</v>
-      </c>
-      <c r="C328" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="D328" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO</t>
-        </is>
-      </c>
-      <c r="E328" t="n">
-        <v>200</v>
-      </c>
-      <c r="F328" t="n">
-        <v>75</v>
-      </c>
-      <c r="G328" t="n">
-        <v>21</v>
-      </c>
-      <c r="H328" t="n">
-        <v>38</v>
-      </c>
-      <c r="I328" t="n">
-        <v>5</v>
-      </c>
-      <c r="J328" t="n">
-        <v>17</v>
-      </c>
-      <c r="K328" t="n">
-        <v>18</v>
-      </c>
-      <c r="L328" t="n">
-        <v>34</v>
-      </c>
-      <c r="M328" t="n">
-        <v>8</v>
-      </c>
-      <c r="N328" t="n">
-        <v>29</v>
-      </c>
-      <c r="O328" t="n">
-        <v>11</v>
-      </c>
-      <c r="P328" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q328" t="n">
-        <v>12</v>
-      </c>
-      <c r="R328" t="n">
-        <v>20</v>
-      </c>
-      <c r="S328" t="n">
-        <v>28</v>
-      </c>
-      <c r="T328" t="n">
-        <v>4</v>
-      </c>
-      <c r="U328" t="inlineStr">
-        <is>
-          <t>2487925</t>
-        </is>
-      </c>
-      <c r="V328" t="n">
-        <v>70</v>
-      </c>
-      <c r="W328" t="n">
-        <v>81.96000000000001</v>
-      </c>
-      <c r="X328" t="n">
-        <v>0.9150805270863835</v>
-      </c>
-      <c r="Y328" t="n">
-        <v>73.96000000000001</v>
-      </c>
-      <c r="Z328" t="n">
-        <v>101.4061654948621</v>
-      </c>
-      <c r="AA328" t="n">
-        <v>0.7651945780498469</v>
-      </c>
-      <c r="AB328" t="n">
-        <v>90.34589571502323</v>
-      </c>
-      <c r="AC328" t="n">
-        <v>0.2285714285714286</v>
-      </c>
-      <c r="AD328" t="n">
-        <v>0.6744186046511628</v>
-      </c>
-      <c r="AE328" t="n">
-        <v>0.4743589743589743</v>
-      </c>
-      <c r="AF328" t="n">
-        <v>11.06026977983885</v>
-      </c>
-      <c r="AG328" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO</t>
-        </is>
-      </c>
-      <c r="AH328" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="AI328" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="329">
-      <c r="A329" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B329" t="n">
-        <v>24</v>
-      </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-      <c r="D329" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="E329" t="n">
-        <v>225</v>
-      </c>
-      <c r="F329" t="n">
-        <v>86</v>
-      </c>
-      <c r="G329" t="n">
-        <v>18</v>
-      </c>
-      <c r="H329" t="n">
-        <v>33</v>
-      </c>
-      <c r="I329" t="n">
-        <v>9</v>
-      </c>
-      <c r="J329" t="n">
-        <v>25</v>
-      </c>
-      <c r="K329" t="n">
-        <v>23</v>
-      </c>
-      <c r="L329" t="n">
-        <v>31</v>
-      </c>
-      <c r="M329" t="n">
-        <v>7</v>
-      </c>
-      <c r="N329" t="n">
-        <v>21</v>
-      </c>
-      <c r="O329" t="n">
-        <v>12</v>
-      </c>
-      <c r="P329" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q329" t="n">
-        <v>13</v>
-      </c>
-      <c r="R329" t="n">
-        <v>22</v>
-      </c>
-      <c r="S329" t="n">
-        <v>25</v>
-      </c>
-      <c r="T329" t="n">
-        <v>0</v>
-      </c>
-      <c r="U329" t="inlineStr">
-        <is>
-          <t>2487922</t>
-        </is>
-      </c>
-      <c r="V329" t="n">
-        <v>84</v>
-      </c>
-      <c r="W329" t="n">
-        <v>84.64</v>
-      </c>
-      <c r="X329" t="n">
-        <v>1.016068052930057</v>
-      </c>
-      <c r="Y329" t="n">
-        <v>77.64</v>
-      </c>
-      <c r="Z329" t="n">
-        <v>110.7676455435343</v>
-      </c>
-      <c r="AA329" t="n">
-        <v>0.9740259740259739</v>
-      </c>
-      <c r="AB329" t="n">
-        <v>102.1400778210117</v>
-      </c>
-      <c r="AC329" t="n">
-        <v>0.2413793103448276</v>
-      </c>
-      <c r="AD329" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="AE329" t="n">
-        <v>0.5185185185185185</v>
-      </c>
-      <c r="AF329" t="n">
-        <v>8.627567722522599</v>
-      </c>
-      <c r="AG329" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="AH329" t="inlineStr">
-        <is>
-          <t>CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-      <c r="AI329" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="330">
-      <c r="A330" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B330" t="n">
-        <v>24</v>
-      </c>
-      <c r="C330" t="inlineStr">
-        <is>
-          <t>COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-      <c r="D330" t="inlineStr">
-        <is>
-          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
-        </is>
-      </c>
-      <c r="E330" t="n">
-        <v>200</v>
-      </c>
-      <c r="F330" t="n">
-        <v>70</v>
-      </c>
-      <c r="G330" t="n">
-        <v>16</v>
-      </c>
-      <c r="H330" t="n">
-        <v>29</v>
-      </c>
-      <c r="I330" t="n">
-        <v>7</v>
-      </c>
-      <c r="J330" t="n">
-        <v>26</v>
-      </c>
-      <c r="K330" t="n">
-        <v>17</v>
-      </c>
-      <c r="L330" t="n">
-        <v>26</v>
-      </c>
-      <c r="M330" t="n">
-        <v>8</v>
-      </c>
-      <c r="N330" t="n">
-        <v>31</v>
-      </c>
-      <c r="O330" t="n">
-        <v>11</v>
-      </c>
-      <c r="P330" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q330" t="n">
-        <v>11</v>
-      </c>
-      <c r="R330" t="n">
-        <v>22</v>
-      </c>
-      <c r="S330" t="n">
-        <v>19</v>
-      </c>
-      <c r="T330" t="n">
-        <v>4</v>
-      </c>
-      <c r="U330" t="inlineStr">
-        <is>
-          <t>2487926</t>
-        </is>
-      </c>
-      <c r="V330" t="n">
-        <v>58</v>
-      </c>
-      <c r="W330" t="n">
-        <v>77.44</v>
-      </c>
-      <c r="X330" t="n">
-        <v>0.9039256198347108</v>
-      </c>
-      <c r="Y330" t="n">
-        <v>69.44</v>
-      </c>
-      <c r="Z330" t="n">
-        <v>100.8064516129032</v>
-      </c>
-      <c r="AA330" t="n">
-        <v>0.6672802577082374</v>
-      </c>
-      <c r="AB330" t="n">
-        <v>82.95194508009153</v>
-      </c>
-      <c r="AC330" t="n">
-        <v>0.2424242424242424</v>
-      </c>
-      <c r="AD330" t="n">
-        <v>0.6458333333333334</v>
-      </c>
-      <c r="AE330" t="n">
-        <v>0.4814814814814815</v>
-      </c>
-      <c r="AF330" t="n">
-        <v>17.8545065328117</v>
-      </c>
-      <c r="AG330" t="inlineStr">
-        <is>
-          <t>COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-      <c r="AH330" t="inlineStr">
-        <is>
-          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
-        </is>
-      </c>
-      <c r="AI330" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="331">
-      <c r="A331" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B331" t="n">
-        <v>24</v>
-      </c>
-      <c r="C331" t="inlineStr">
-        <is>
-          <t>CULTURAL Y DEPORTIVA LEONESA</t>
-        </is>
-      </c>
-      <c r="D331" t="inlineStr">
-        <is>
-          <t>C.B. STARLABS MORÓN</t>
-        </is>
-      </c>
-      <c r="E331" t="n">
-        <v>200</v>
-      </c>
-      <c r="F331" t="n">
-        <v>83</v>
-      </c>
-      <c r="G331" t="n">
-        <v>26</v>
-      </c>
-      <c r="H331" t="n">
-        <v>62</v>
-      </c>
-      <c r="I331" t="n">
-        <v>8</v>
-      </c>
-      <c r="J331" t="n">
-        <v>25</v>
-      </c>
-      <c r="K331" t="n">
-        <v>7</v>
-      </c>
-      <c r="L331" t="n">
-        <v>8</v>
-      </c>
-      <c r="M331" t="n">
-        <v>21</v>
-      </c>
-      <c r="N331" t="n">
-        <v>17</v>
-      </c>
-      <c r="O331" t="n">
-        <v>22</v>
-      </c>
-      <c r="P331" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q331" t="n">
-        <v>10</v>
-      </c>
-      <c r="R331" t="n">
-        <v>23</v>
-      </c>
-      <c r="S331" t="n">
-        <v>16</v>
-      </c>
-      <c r="T331" t="n">
-        <v>2</v>
-      </c>
-      <c r="U331" t="inlineStr">
-        <is>
-          <t>2487923</t>
-        </is>
-      </c>
-      <c r="V331" t="n">
-        <v>93</v>
-      </c>
-      <c r="W331" t="n">
-        <v>100.52</v>
-      </c>
-      <c r="X331" t="n">
-        <v>0.8257063270990848</v>
-      </c>
-      <c r="Y331" t="n">
-        <v>79.52</v>
-      </c>
-      <c r="Z331" t="n">
-        <v>104.3762575452716</v>
-      </c>
-      <c r="AA331" t="n">
-        <v>1.157868525896415</v>
-      </c>
-      <c r="AB331" t="n">
-        <v>126.8412438625205</v>
-      </c>
-      <c r="AC331" t="n">
-        <v>0.4772727272727273</v>
-      </c>
-      <c r="AD331" t="n">
-        <v>0.7083333333333334</v>
-      </c>
-      <c r="AE331" t="n">
-        <v>0.5588235294117647</v>
-      </c>
-      <c r="AF331" t="n">
-        <v>-22.46498631724883</v>
-      </c>
-      <c r="AG331" t="inlineStr">
-        <is>
-          <t>C.B. STARLABS MORÓN</t>
-        </is>
-      </c>
-      <c r="AH331" t="inlineStr">
-        <is>
-          <t>CULTURAL Y DEPORTIVA LEONESA</t>
-        </is>
-      </c>
-      <c r="AI331" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="332">
-      <c r="A332" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B332" t="n">
-        <v>24</v>
-      </c>
-      <c r="C332" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO</t>
-        </is>
-      </c>
-      <c r="D332" t="inlineStr">
-        <is>
-          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-      <c r="E332" t="n">
-        <v>200</v>
-      </c>
-      <c r="F332" t="n">
-        <v>81</v>
-      </c>
-      <c r="G332" t="n">
-        <v>21</v>
-      </c>
-      <c r="H332" t="n">
-        <v>45</v>
-      </c>
-      <c r="I332" t="n">
-        <v>10</v>
-      </c>
-      <c r="J332" t="n">
-        <v>23</v>
-      </c>
-      <c r="K332" t="n">
-        <v>9</v>
-      </c>
-      <c r="L332" t="n">
-        <v>16</v>
-      </c>
-      <c r="M332" t="n">
-        <v>14</v>
-      </c>
-      <c r="N332" t="n">
-        <v>25</v>
-      </c>
-      <c r="O332" t="n">
-        <v>19</v>
-      </c>
-      <c r="P332" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q332" t="n">
-        <v>15</v>
-      </c>
-      <c r="R332" t="n">
-        <v>18</v>
-      </c>
-      <c r="S332" t="n">
-        <v>18</v>
-      </c>
-      <c r="T332" t="n">
-        <v>3</v>
-      </c>
-      <c r="U332" t="inlineStr">
-        <is>
-          <t>2487924</t>
-        </is>
-      </c>
-      <c r="V332" t="n">
-        <v>83</v>
-      </c>
-      <c r="W332" t="n">
-        <v>90.03999999999999</v>
-      </c>
-      <c r="X332" t="n">
-        <v>0.8996001776988006</v>
-      </c>
-      <c r="Y332" t="n">
-        <v>76.03999999999999</v>
-      </c>
-      <c r="Z332" t="n">
-        <v>106.5228826933193</v>
-      </c>
-      <c r="AA332" t="n">
-        <v>0.9646675964667597</v>
-      </c>
-      <c r="AB332" t="n">
-        <v>105.0101214574899</v>
-      </c>
-      <c r="AC332" t="n">
-        <v>0.3783783783783784</v>
-      </c>
-      <c r="AD332" t="n">
-        <v>0.78125</v>
-      </c>
-      <c r="AE332" t="n">
-        <v>0.5652173913043478</v>
-      </c>
-      <c r="AF332" t="n">
-        <v>1.51276123582943</v>
-      </c>
-      <c r="AG332" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AH332" t="inlineStr">
-        <is>
-          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-      <c r="AI332" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="333">
-      <c r="A333" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B333" t="n">
-        <v>24</v>
-      </c>
-      <c r="C333" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="D333" t="inlineStr">
-        <is>
-          <t>BIELE ISB</t>
-        </is>
-      </c>
-      <c r="E333" t="n">
-        <v>200</v>
-      </c>
-      <c r="F333" t="n">
-        <v>79</v>
-      </c>
-      <c r="G333" t="n">
-        <v>15</v>
-      </c>
-      <c r="H333" t="n">
-        <v>34</v>
-      </c>
-      <c r="I333" t="n">
-        <v>11</v>
-      </c>
-      <c r="J333" t="n">
-        <v>30</v>
-      </c>
-      <c r="K333" t="n">
-        <v>16</v>
-      </c>
-      <c r="L333" t="n">
-        <v>22</v>
-      </c>
-      <c r="M333" t="n">
-        <v>10</v>
-      </c>
-      <c r="N333" t="n">
-        <v>18</v>
-      </c>
-      <c r="O333" t="n">
-        <v>8</v>
-      </c>
-      <c r="P333" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q333" t="n">
-        <v>10</v>
-      </c>
-      <c r="R333" t="n">
-        <v>18</v>
-      </c>
-      <c r="S333" t="n">
-        <v>24</v>
-      </c>
-      <c r="T333" t="n">
-        <v>1</v>
-      </c>
-      <c r="U333" t="inlineStr">
-        <is>
-          <t>2487921</t>
-        </is>
-      </c>
-      <c r="V333" t="n">
-        <v>81</v>
-      </c>
-      <c r="W333" t="n">
-        <v>83.68000000000001</v>
-      </c>
-      <c r="X333" t="n">
-        <v>0.9440726577437858</v>
-      </c>
-      <c r="Y333" t="n">
-        <v>73.68000000000001</v>
-      </c>
-      <c r="Z333" t="n">
-        <v>107.2204125950054</v>
-      </c>
-      <c r="AA333" t="n">
-        <v>1.09875203472599</v>
-      </c>
-      <c r="AB333" t="n">
-        <v>121.4028776978417</v>
-      </c>
-      <c r="AC333" t="n">
-        <v>0.3125</v>
-      </c>
-      <c r="AD333" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="AE333" t="n">
-        <v>0.4912280701754386</v>
-      </c>
-      <c r="AF333" t="n">
-        <v>-14.18246510283632</v>
-      </c>
-      <c r="AG333" t="inlineStr">
-        <is>
-          <t>BIELE ISB</t>
-        </is>
-      </c>
-      <c r="AH333" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="AI333" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="334">
-      <c r="A334" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B334" t="n">
-        <v>24</v>
-      </c>
-      <c r="C334" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-      <c r="D334" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID</t>
-        </is>
-      </c>
-      <c r="E334" t="n">
-        <v>200</v>
-      </c>
-      <c r="F334" t="n">
-        <v>84</v>
-      </c>
-      <c r="G334" t="n">
-        <v>18</v>
-      </c>
-      <c r="H334" t="n">
-        <v>36</v>
-      </c>
-      <c r="I334" t="n">
-        <v>12</v>
-      </c>
-      <c r="J334" t="n">
-        <v>30</v>
-      </c>
-      <c r="K334" t="n">
-        <v>12</v>
-      </c>
-      <c r="L334" t="n">
-        <v>22</v>
-      </c>
-      <c r="M334" t="n">
-        <v>12</v>
-      </c>
-      <c r="N334" t="n">
-        <v>18</v>
-      </c>
-      <c r="O334" t="n">
-        <v>17</v>
-      </c>
-      <c r="P334" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q334" t="n">
-        <v>11</v>
-      </c>
-      <c r="R334" t="n">
-        <v>33</v>
-      </c>
-      <c r="S334" t="n">
-        <v>19</v>
-      </c>
-      <c r="T334" t="n">
-        <v>2</v>
-      </c>
-      <c r="U334" t="inlineStr">
-        <is>
-          <t>2487920</t>
-        </is>
-      </c>
-      <c r="V334" t="n">
-        <v>91</v>
-      </c>
-      <c r="W334" t="n">
-        <v>86.68000000000001</v>
-      </c>
-      <c r="X334" t="n">
-        <v>0.9690816797415781</v>
-      </c>
-      <c r="Y334" t="n">
-        <v>74.68000000000001</v>
-      </c>
-      <c r="Z334" t="n">
-        <v>112.4799143010177</v>
-      </c>
-      <c r="AA334" t="n">
-        <v>1.082817705854355</v>
-      </c>
-      <c r="AB334" t="n">
-        <v>122.9065370070232</v>
-      </c>
-      <c r="AC334" t="n">
-        <v>0.3428571428571429</v>
-      </c>
-      <c r="AD334" t="n">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="AE334" t="n">
-        <v>0.4761904761904762</v>
-      </c>
-      <c r="AF334" t="n">
-        <v>-10.42662270600557</v>
-      </c>
-      <c r="AG334" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID</t>
-        </is>
-      </c>
-      <c r="AH334" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-      <c r="AI334" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="335">
-      <c r="A335" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B335" t="n">
-        <v>24</v>
-      </c>
-      <c r="C335" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="D335" t="inlineStr">
-        <is>
-          <t>CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-      <c r="E335" t="n">
-        <v>225</v>
-      </c>
-      <c r="F335" t="n">
-        <v>84</v>
-      </c>
-      <c r="G335" t="n">
-        <v>14</v>
-      </c>
-      <c r="H335" t="n">
-        <v>31</v>
-      </c>
-      <c r="I335" t="n">
-        <v>13</v>
-      </c>
-      <c r="J335" t="n">
-        <v>26</v>
-      </c>
-      <c r="K335" t="n">
-        <v>17</v>
-      </c>
-      <c r="L335" t="n">
-        <v>21</v>
-      </c>
-      <c r="M335" t="n">
-        <v>4</v>
-      </c>
-      <c r="N335" t="n">
-        <v>22</v>
-      </c>
-      <c r="O335" t="n">
-        <v>16</v>
-      </c>
-      <c r="P335" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q335" t="n">
-        <v>20</v>
-      </c>
-      <c r="R335" t="n">
-        <v>25</v>
-      </c>
-      <c r="S335" t="n">
-        <v>22</v>
-      </c>
-      <c r="T335" t="n">
-        <v>1</v>
-      </c>
-      <c r="U335" t="inlineStr">
-        <is>
-          <t>2487922</t>
-        </is>
-      </c>
-      <c r="V335" t="n">
-        <v>86</v>
-      </c>
-      <c r="W335" t="n">
-        <v>86.24000000000001</v>
-      </c>
-      <c r="X335" t="n">
-        <v>0.9740259740259739</v>
-      </c>
-      <c r="Y335" t="n">
-        <v>82.24000000000001</v>
-      </c>
-      <c r="Z335" t="n">
-        <v>102.1400778210117</v>
-      </c>
-      <c r="AA335" t="n">
-        <v>1.016068052930057</v>
-      </c>
-      <c r="AB335" t="n">
-        <v>110.7676455435343</v>
-      </c>
-      <c r="AC335" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="AD335" t="n">
-        <v>0.7586206896551724</v>
-      </c>
-      <c r="AE335" t="n">
-        <v>0.4814814814814815</v>
-      </c>
-      <c r="AF335" t="n">
-        <v>-8.627567722522599</v>
-      </c>
-      <c r="AG335" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="AH335" t="inlineStr">
-        <is>
-          <t>CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-      <c r="AI335" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="336">
-      <c r="A336" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B336" t="n">
-        <v>24</v>
-      </c>
-      <c r="C336" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO</t>
-        </is>
-      </c>
-      <c r="D336" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="E336" t="n">
-        <v>200</v>
-      </c>
-      <c r="F336" t="n">
-        <v>70</v>
-      </c>
-      <c r="G336" t="n">
-        <v>15</v>
-      </c>
-      <c r="H336" t="n">
-        <v>38</v>
-      </c>
-      <c r="I336" t="n">
-        <v>10</v>
-      </c>
-      <c r="J336" t="n">
-        <v>32</v>
-      </c>
-      <c r="K336" t="n">
-        <v>10</v>
-      </c>
-      <c r="L336" t="n">
-        <v>17</v>
-      </c>
-      <c r="M336" t="n">
-        <v>14</v>
-      </c>
-      <c r="N336" t="n">
-        <v>27</v>
-      </c>
-      <c r="O336" t="n">
-        <v>9</v>
-      </c>
-      <c r="P336" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q336" t="n">
-        <v>14</v>
-      </c>
-      <c r="R336" t="n">
-        <v>28</v>
-      </c>
-      <c r="S336" t="n">
-        <v>20</v>
-      </c>
-      <c r="T336" t="n">
-        <v>3</v>
-      </c>
-      <c r="U336" t="inlineStr">
-        <is>
-          <t>2487925</t>
-        </is>
-      </c>
-      <c r="V336" t="n">
-        <v>75</v>
-      </c>
-      <c r="W336" t="n">
-        <v>91.48</v>
-      </c>
-      <c r="X336" t="n">
-        <v>0.7651945780498469</v>
-      </c>
-      <c r="Y336" t="n">
-        <v>77.48</v>
-      </c>
-      <c r="Z336" t="n">
-        <v>90.34589571502323</v>
-      </c>
-      <c r="AA336" t="n">
-        <v>0.9150805270863835</v>
-      </c>
-      <c r="AB336" t="n">
-        <v>101.4061654948621</v>
-      </c>
-      <c r="AC336" t="n">
-        <v>0.3255813953488372</v>
-      </c>
-      <c r="AD336" t="n">
-        <v>0.7714285714285715</v>
-      </c>
-      <c r="AE336" t="n">
-        <v>0.5256410256410257</v>
-      </c>
-      <c r="AF336" t="n">
-        <v>-11.06026977983885</v>
-      </c>
-      <c r="AG336" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO</t>
-        </is>
-      </c>
-      <c r="AH336" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="AI336" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="337">
-      <c r="A337" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B337" t="n">
-        <v>24</v>
-      </c>
-      <c r="C337" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID</t>
-        </is>
-      </c>
-      <c r="D337" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-      <c r="E337" t="n">
-        <v>200</v>
-      </c>
-      <c r="F337" t="n">
-        <v>91</v>
-      </c>
-      <c r="G337" t="n">
-        <v>15</v>
-      </c>
-      <c r="H337" t="n">
-        <v>28</v>
-      </c>
-      <c r="I337" t="n">
-        <v>10</v>
-      </c>
-      <c r="J337" t="n">
-        <v>28</v>
-      </c>
-      <c r="K337" t="n">
-        <v>31</v>
-      </c>
-      <c r="L337" t="n">
-        <v>41</v>
-      </c>
-      <c r="M337" t="n">
-        <v>10</v>
-      </c>
-      <c r="N337" t="n">
-        <v>23</v>
-      </c>
-      <c r="O337" t="n">
-        <v>15</v>
-      </c>
-      <c r="P337" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q337" t="n">
-        <v>10</v>
-      </c>
-      <c r="R337" t="n">
-        <v>19</v>
-      </c>
-      <c r="S337" t="n">
-        <v>31</v>
-      </c>
-      <c r="T337" t="n">
-        <v>3</v>
-      </c>
-      <c r="U337" t="inlineStr">
-        <is>
-          <t>2487920</t>
-        </is>
-      </c>
-      <c r="V337" t="n">
-        <v>84</v>
-      </c>
-      <c r="W337" t="n">
-        <v>84.03999999999999</v>
-      </c>
-      <c r="X337" t="n">
-        <v>1.082817705854355</v>
-      </c>
-      <c r="Y337" t="n">
-        <v>74.03999999999999</v>
-      </c>
-      <c r="Z337" t="n">
-        <v>122.9065370070232</v>
-      </c>
-      <c r="AA337" t="n">
-        <v>0.9690816797415781</v>
-      </c>
-      <c r="AB337" t="n">
-        <v>112.4799143010177</v>
-      </c>
-      <c r="AC337" t="n">
-        <v>0.3571428571428572</v>
-      </c>
-      <c r="AD337" t="n">
-        <v>0.6571428571428571</v>
-      </c>
-      <c r="AE337" t="n">
-        <v>0.5238095238095238</v>
-      </c>
-      <c r="AF337" t="n">
-        <v>10.42662270600557</v>
-      </c>
-      <c r="AG337" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID</t>
-        </is>
-      </c>
-      <c r="AH337" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-      <c r="AI337" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="338">
-      <c r="A338" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B338" t="n">
-        <v>25</v>
-      </c>
-      <c r="C338" t="inlineStr">
-        <is>
-          <t>BIELE ISB</t>
-        </is>
-      </c>
-      <c r="D338" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-      <c r="E338" t="n">
-        <v>200</v>
-      </c>
-      <c r="F338" t="n">
-        <v>102</v>
-      </c>
-      <c r="G338" t="n">
-        <v>22</v>
-      </c>
-      <c r="H338" t="n">
-        <v>29</v>
-      </c>
-      <c r="I338" t="n">
-        <v>17</v>
-      </c>
-      <c r="J338" t="n">
-        <v>38</v>
-      </c>
-      <c r="K338" t="n">
-        <v>7</v>
-      </c>
-      <c r="L338" t="n">
-        <v>9</v>
-      </c>
-      <c r="M338" t="n">
-        <v>8</v>
-      </c>
-      <c r="N338" t="n">
-        <v>26</v>
-      </c>
-      <c r="O338" t="n">
-        <v>19</v>
-      </c>
-      <c r="P338" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q338" t="n">
-        <v>10</v>
-      </c>
-      <c r="R338" t="n">
-        <v>21</v>
-      </c>
-      <c r="S338" t="n">
-        <v>11</v>
-      </c>
-      <c r="T338" t="n">
-        <v>2</v>
-      </c>
-      <c r="U338" t="inlineStr">
-        <is>
-          <t>2487933</t>
-        </is>
-      </c>
-      <c r="V338" t="n">
-        <v>71</v>
-      </c>
-      <c r="W338" t="n">
-        <v>80.96000000000001</v>
-      </c>
-      <c r="X338" t="n">
-        <v>1.259881422924901</v>
-      </c>
-      <c r="Y338" t="n">
-        <v>72.96000000000001</v>
-      </c>
-      <c r="Z338" t="n">
-        <v>139.8026315789473</v>
-      </c>
-      <c r="AA338" t="n">
-        <v>0.8919597989949749</v>
-      </c>
-      <c r="AB338" t="n">
-        <v>102.0114942528736</v>
-      </c>
-      <c r="AC338" t="n">
-        <v>0.3809523809523809</v>
-      </c>
-      <c r="AD338" t="n">
-        <v>0.7222222222222222</v>
-      </c>
-      <c r="AE338" t="n">
-        <v>0.5964912280701754</v>
-      </c>
-      <c r="AF338" t="n">
-        <v>37.79113732607377</v>
-      </c>
-      <c r="AG338" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-      <c r="AH338" t="inlineStr">
-        <is>
-          <t>BIELE ISB</t>
-        </is>
-      </c>
-      <c r="AI338" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="339">
-      <c r="A339" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B339" t="n">
-        <v>25</v>
-      </c>
-      <c r="C339" t="inlineStr">
-        <is>
-          <t>C.B. STARLABS MORÓN</t>
-        </is>
-      </c>
-      <c r="D339" t="inlineStr">
-        <is>
-          <t>CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-      <c r="E339" t="n">
-        <v>200</v>
-      </c>
-      <c r="F339" t="n">
-        <v>87</v>
-      </c>
-      <c r="G339" t="n">
-        <v>18</v>
-      </c>
-      <c r="H339" t="n">
-        <v>31</v>
-      </c>
-      <c r="I339" t="n">
-        <v>7</v>
-      </c>
-      <c r="J339" t="n">
-        <v>20</v>
-      </c>
-      <c r="K339" t="n">
-        <v>30</v>
-      </c>
-      <c r="L339" t="n">
-        <v>43</v>
-      </c>
-      <c r="M339" t="n">
-        <v>3</v>
-      </c>
-      <c r="N339" t="n">
-        <v>34</v>
-      </c>
-      <c r="O339" t="n">
-        <v>17</v>
-      </c>
-      <c r="P339" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q339" t="n">
-        <v>11</v>
-      </c>
-      <c r="R339" t="n">
-        <v>20</v>
-      </c>
-      <c r="S339" t="n">
-        <v>30</v>
-      </c>
-      <c r="T339" t="n">
-        <v>1</v>
-      </c>
-      <c r="U339" t="inlineStr">
-        <is>
-          <t>2487931</t>
-        </is>
-      </c>
-      <c r="V339" t="n">
-        <v>75</v>
-      </c>
-      <c r="W339" t="n">
-        <v>80.92</v>
-      </c>
-      <c r="X339" t="n">
-        <v>1.075135936727632</v>
-      </c>
-      <c r="Y339" t="n">
-        <v>77.92</v>
-      </c>
-      <c r="Z339" t="n">
-        <v>111.652977412731</v>
-      </c>
-      <c r="AA339" t="n">
-        <v>0.8971291866028709</v>
-      </c>
-      <c r="AB339" t="n">
-        <v>96.64948453608248</v>
-      </c>
-      <c r="AC339" t="n">
-        <v>0.125</v>
-      </c>
-      <c r="AD339" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="AE339" t="n">
-        <v>0.578125</v>
-      </c>
-      <c r="AF339" t="n">
-        <v>15.00349287664852</v>
-      </c>
-      <c r="AG339" t="inlineStr">
-        <is>
-          <t>CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-      <c r="AH339" t="inlineStr">
-        <is>
-          <t>C.B. STARLABS MORÓN</t>
-        </is>
-      </c>
-      <c r="AI339" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="340">
-      <c r="A340" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B340" t="n">
-        <v>25</v>
-      </c>
-      <c r="C340" t="inlineStr">
-        <is>
-          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
-        </is>
-      </c>
-      <c r="D340" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID</t>
-        </is>
-      </c>
-      <c r="E340" t="n">
-        <v>200</v>
-      </c>
-      <c r="F340" t="n">
-        <v>98</v>
-      </c>
-      <c r="G340" t="n">
-        <v>25</v>
-      </c>
-      <c r="H340" t="n">
-        <v>40</v>
-      </c>
-      <c r="I340" t="n">
-        <v>6</v>
-      </c>
-      <c r="J340" t="n">
-        <v>29</v>
-      </c>
-      <c r="K340" t="n">
-        <v>30</v>
-      </c>
-      <c r="L340" t="n">
-        <v>39</v>
-      </c>
-      <c r="M340" t="n">
-        <v>12</v>
-      </c>
-      <c r="N340" t="n">
-        <v>26</v>
-      </c>
-      <c r="O340" t="n">
-        <v>6</v>
-      </c>
-      <c r="P340" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q340" t="n">
-        <v>8</v>
-      </c>
-      <c r="R340" t="n">
-        <v>25</v>
-      </c>
-      <c r="S340" t="n">
-        <v>28</v>
-      </c>
-      <c r="T340" t="n">
-        <v>0</v>
-      </c>
-      <c r="U340" t="inlineStr">
-        <is>
-          <t>2487927</t>
-        </is>
-      </c>
-      <c r="V340" t="n">
-        <v>85</v>
-      </c>
-      <c r="W340" t="n">
-        <v>94.16</v>
-      </c>
-      <c r="X340" t="n">
-        <v>1.040781648258284</v>
-      </c>
-      <c r="Y340" t="n">
-        <v>82.16</v>
-      </c>
-      <c r="Z340" t="n">
-        <v>119.2794547224927</v>
-      </c>
-      <c r="AA340" t="n">
-        <v>0.9948501872659177</v>
-      </c>
-      <c r="AB340" t="n">
-        <v>106.9989929506546</v>
-      </c>
-      <c r="AC340" t="n">
-        <v>0.3243243243243243</v>
-      </c>
-      <c r="AD340" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="AE340" t="n">
-        <v>0.5507246376811594</v>
-      </c>
-      <c r="AF340" t="n">
-        <v>12.28046177183812</v>
-      </c>
-      <c r="AG340" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID</t>
-        </is>
-      </c>
-      <c r="AH340" t="inlineStr">
-        <is>
-          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
-        </is>
-      </c>
-      <c r="AI340" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="341">
-      <c r="A341" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B341" t="n">
-        <v>25</v>
-      </c>
-      <c r="C341" t="inlineStr">
-        <is>
-          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-      <c r="D341" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO</t>
-        </is>
-      </c>
-      <c r="E341" t="n">
-        <v>200</v>
-      </c>
-      <c r="F341" t="n">
-        <v>68</v>
-      </c>
-      <c r="G341" t="n">
-        <v>24</v>
-      </c>
-      <c r="H341" t="n">
-        <v>43</v>
-      </c>
-      <c r="I341" t="n">
-        <v>0</v>
-      </c>
-      <c r="J341" t="n">
-        <v>13</v>
-      </c>
-      <c r="K341" t="n">
-        <v>20</v>
-      </c>
-      <c r="L341" t="n">
-        <v>27</v>
-      </c>
-      <c r="M341" t="n">
-        <v>6</v>
-      </c>
-      <c r="N341" t="n">
-        <v>23</v>
-      </c>
-      <c r="O341" t="n">
-        <v>17</v>
-      </c>
-      <c r="P341" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q341" t="n">
-        <v>13</v>
-      </c>
-      <c r="R341" t="n">
-        <v>21</v>
-      </c>
-      <c r="S341" t="n">
-        <v>24</v>
-      </c>
-      <c r="T341" t="n">
-        <v>2</v>
-      </c>
-      <c r="U341" t="inlineStr">
-        <is>
-          <t>2487929</t>
-        </is>
-      </c>
-      <c r="V341" t="n">
-        <v>85</v>
-      </c>
-      <c r="W341" t="n">
-        <v>80.88</v>
-      </c>
-      <c r="X341" t="n">
-        <v>0.8407517309594461</v>
-      </c>
-      <c r="Y341" t="n">
-        <v>74.88</v>
-      </c>
-      <c r="Z341" t="n">
-        <v>90.81196581196582</v>
-      </c>
-      <c r="AA341" t="n">
-        <v>0.9792626728110599</v>
-      </c>
-      <c r="AB341" t="n">
-        <v>110.6770833333333</v>
-      </c>
-      <c r="AC341" t="n">
-        <v>0.1818181818181818</v>
-      </c>
-      <c r="AD341" t="n">
-        <v>0.696969696969697</v>
-      </c>
-      <c r="AE341" t="n">
-        <v>0.4393939393939394</v>
-      </c>
-      <c r="AF341" t="n">
-        <v>-19.86511752136752</v>
-      </c>
-      <c r="AG341" t="inlineStr">
-        <is>
-          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-      <c r="AH341" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO</t>
-        </is>
-      </c>
-      <c r="AI341" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="342">
-      <c r="A342" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B342" t="n">
-        <v>25</v>
-      </c>
-      <c r="C342" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="D342" t="inlineStr">
-        <is>
-          <t>COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-      <c r="E342" t="n">
-        <v>200</v>
-      </c>
-      <c r="F342" t="n">
-        <v>66</v>
-      </c>
-      <c r="G342" t="n">
-        <v>7</v>
-      </c>
-      <c r="H342" t="n">
-        <v>25</v>
-      </c>
-      <c r="I342" t="n">
-        <v>13</v>
-      </c>
-      <c r="J342" t="n">
-        <v>31</v>
-      </c>
-      <c r="K342" t="n">
-        <v>13</v>
-      </c>
-      <c r="L342" t="n">
-        <v>22</v>
-      </c>
-      <c r="M342" t="n">
-        <v>6</v>
-      </c>
-      <c r="N342" t="n">
-        <v>25</v>
-      </c>
-      <c r="O342" t="n">
-        <v>12</v>
-      </c>
-      <c r="P342" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q342" t="n">
-        <v>13</v>
-      </c>
-      <c r="R342" t="n">
-        <v>24</v>
-      </c>
-      <c r="S342" t="n">
-        <v>20</v>
-      </c>
-      <c r="T342" t="n">
-        <v>1</v>
-      </c>
-      <c r="U342" t="inlineStr">
-        <is>
-          <t>2487928</t>
-        </is>
-      </c>
-      <c r="V342" t="n">
-        <v>64</v>
-      </c>
-      <c r="W342" t="n">
-        <v>78.68000000000001</v>
-      </c>
-      <c r="X342" t="n">
-        <v>0.838840874428063</v>
-      </c>
-      <c r="Y342" t="n">
-        <v>72.68000000000001</v>
-      </c>
-      <c r="Z342" t="n">
-        <v>90.80902586681341</v>
-      </c>
-      <c r="AA342" t="n">
-        <v>0.7403979639055993</v>
-      </c>
-      <c r="AB342" t="n">
-        <v>83.7257980115123</v>
-      </c>
-      <c r="AC342" t="n">
-        <v>0.1875</v>
-      </c>
-      <c r="AD342" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="AE342" t="n">
-        <v>0.4626865671641791</v>
-      </c>
-      <c r="AF342" t="n">
-        <v>7.083227855301118</v>
-      </c>
-      <c r="AG342" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="AH342" t="inlineStr">
-        <is>
-          <t>COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-      <c r="AI342" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="343">
-      <c r="A343" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B343" t="n">
-        <v>25</v>
-      </c>
-      <c r="C343" t="inlineStr">
-        <is>
-          <t>CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-      <c r="D343" t="inlineStr">
-        <is>
-          <t>C.B. STARLABS MORÓN</t>
-        </is>
-      </c>
-      <c r="E343" t="n">
-        <v>200</v>
-      </c>
-      <c r="F343" t="n">
-        <v>75</v>
-      </c>
-      <c r="G343" t="n">
-        <v>16</v>
-      </c>
-      <c r="H343" t="n">
-        <v>31</v>
-      </c>
-      <c r="I343" t="n">
-        <v>11</v>
-      </c>
-      <c r="J343" t="n">
-        <v>37</v>
-      </c>
-      <c r="K343" t="n">
-        <v>10</v>
-      </c>
-      <c r="L343" t="n">
-        <v>15</v>
-      </c>
-      <c r="M343" t="n">
-        <v>6</v>
-      </c>
-      <c r="N343" t="n">
-        <v>21</v>
-      </c>
-      <c r="O343" t="n">
-        <v>11</v>
-      </c>
-      <c r="P343" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q343" t="n">
-        <v>9</v>
-      </c>
-      <c r="R343" t="n">
-        <v>31</v>
-      </c>
-      <c r="S343" t="n">
-        <v>20</v>
-      </c>
-      <c r="T343" t="n">
-        <v>2</v>
-      </c>
-      <c r="U343" t="inlineStr">
-        <is>
-          <t>2487931</t>
-        </is>
-      </c>
-      <c r="V343" t="n">
-        <v>87</v>
-      </c>
-      <c r="W343" t="n">
-        <v>83.59999999999999</v>
-      </c>
-      <c r="X343" t="n">
-        <v>0.8971291866028709</v>
-      </c>
-      <c r="Y343" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="Z343" t="n">
-        <v>96.64948453608248</v>
-      </c>
-      <c r="AA343" t="n">
-        <v>1.075135936727632</v>
-      </c>
-      <c r="AB343" t="n">
-        <v>111.652977412731</v>
-      </c>
-      <c r="AC343" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="AD343" t="n">
-        <v>0.875</v>
-      </c>
-      <c r="AE343" t="n">
-        <v>0.421875</v>
-      </c>
-      <c r="AF343" t="n">
-        <v>-15.00349287664852</v>
-      </c>
-      <c r="AG343" t="inlineStr">
-        <is>
-          <t>CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-      <c r="AH343" t="inlineStr">
-        <is>
-          <t>C.B. STARLABS MORÓN</t>
-        </is>
-      </c>
-      <c r="AI343" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="344">
-      <c r="A344" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B344" t="n">
-        <v>25</v>
-      </c>
-      <c r="C344" t="inlineStr">
-        <is>
-          <t>COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="E344" t="n">
-        <v>200</v>
-      </c>
-      <c r="F344" t="n">
-        <v>64</v>
-      </c>
-      <c r="G344" t="n">
-        <v>14</v>
-      </c>
-      <c r="H344" t="n">
-        <v>38</v>
-      </c>
-      <c r="I344" t="n">
-        <v>6</v>
-      </c>
-      <c r="J344" t="n">
-        <v>21</v>
-      </c>
-      <c r="K344" t="n">
-        <v>18</v>
-      </c>
-      <c r="L344" t="n">
-        <v>26</v>
-      </c>
-      <c r="M344" t="n">
-        <v>10</v>
-      </c>
-      <c r="N344" t="n">
-        <v>26</v>
-      </c>
-      <c r="O344" t="n">
-        <v>6</v>
-      </c>
-      <c r="P344" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q344" t="n">
-        <v>16</v>
-      </c>
-      <c r="R344" t="n">
-        <v>20</v>
-      </c>
-      <c r="S344" t="n">
-        <v>23</v>
-      </c>
-      <c r="T344" t="n">
-        <v>0</v>
-      </c>
-      <c r="U344" t="inlineStr">
-        <is>
-          <t>2487928</t>
-        </is>
-      </c>
-      <c r="V344" t="n">
-        <v>66</v>
-      </c>
-      <c r="W344" t="n">
-        <v>86.44</v>
-      </c>
-      <c r="X344" t="n">
-        <v>0.7403979639055993</v>
-      </c>
-      <c r="Y344" t="n">
-        <v>76.44</v>
-      </c>
-      <c r="Z344" t="n">
-        <v>83.7257980115123</v>
-      </c>
-      <c r="AA344" t="n">
-        <v>0.838840874428063</v>
-      </c>
-      <c r="AB344" t="n">
-        <v>90.80902586681341</v>
-      </c>
-      <c r="AC344" t="n">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="AD344" t="n">
-        <v>0.8125</v>
-      </c>
-      <c r="AE344" t="n">
-        <v>0.5373134328358209</v>
-      </c>
-      <c r="AF344" t="n">
-        <v>-7.083227855301118</v>
-      </c>
-      <c r="AG344" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="AH344" t="inlineStr">
-        <is>
-          <t>COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-      <c r="AI344" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="345">
-      <c r="A345" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B345" t="n">
-        <v>25</v>
-      </c>
-      <c r="C345" t="inlineStr">
-        <is>
-          <t>CULTURAL Y DEPORTIVA LEONESA</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO</t>
-        </is>
-      </c>
-      <c r="E345" t="n">
-        <v>200</v>
-      </c>
-      <c r="F345" t="n">
-        <v>85</v>
-      </c>
-      <c r="G345" t="n">
-        <v>26</v>
-      </c>
-      <c r="H345" t="n">
-        <v>45</v>
-      </c>
-      <c r="I345" t="n">
-        <v>8</v>
-      </c>
-      <c r="J345" t="n">
-        <v>24</v>
-      </c>
-      <c r="K345" t="n">
-        <v>9</v>
-      </c>
-      <c r="L345" t="n">
-        <v>17</v>
-      </c>
-      <c r="M345" t="n">
-        <v>16</v>
-      </c>
-      <c r="N345" t="n">
-        <v>29</v>
-      </c>
-      <c r="O345" t="n">
-        <v>18</v>
-      </c>
-      <c r="P345" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q345" t="n">
-        <v>22</v>
-      </c>
-      <c r="R345" t="n">
-        <v>22</v>
-      </c>
-      <c r="S345" t="n">
-        <v>17</v>
-      </c>
-      <c r="T345" t="n">
-        <v>4</v>
-      </c>
-      <c r="U345" t="inlineStr">
-        <is>
-          <t>2487930</t>
-        </is>
-      </c>
-      <c r="V345" t="n">
-        <v>73</v>
-      </c>
-      <c r="W345" t="n">
-        <v>98.48</v>
-      </c>
-      <c r="X345" t="n">
-        <v>0.8631194151096669</v>
-      </c>
-      <c r="Y345" t="n">
-        <v>82.48</v>
-      </c>
-      <c r="Z345" t="n">
-        <v>103.0552861299709</v>
-      </c>
-      <c r="AA345" t="n">
-        <v>0.7674516400336416</v>
-      </c>
-      <c r="AB345" t="n">
-        <v>85.76127819548871</v>
-      </c>
-      <c r="AC345" t="n">
-        <v>0.4705882352941176</v>
-      </c>
-      <c r="AD345" t="n">
-        <v>0.7435897435897436</v>
-      </c>
-      <c r="AE345" t="n">
-        <v>0.6164383561643836</v>
-      </c>
-      <c r="AF345" t="n">
-        <v>17.29400793448218</v>
-      </c>
-      <c r="AG345" t="inlineStr">
-        <is>
-          <t>CULTURAL Y DEPORTIVA LEONESA</t>
-        </is>
-      </c>
-      <c r="AH345" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AI345" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="346">
-      <c r="A346" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B346" t="n">
-        <v>25</v>
-      </c>
-      <c r="C346" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO</t>
-        </is>
-      </c>
-      <c r="D346" t="inlineStr">
-        <is>
-          <t>CULTURAL Y DEPORTIVA LEONESA</t>
-        </is>
-      </c>
-      <c r="E346" t="n">
-        <v>200</v>
-      </c>
-      <c r="F346" t="n">
-        <v>73</v>
-      </c>
-      <c r="G346" t="n">
-        <v>21</v>
-      </c>
-      <c r="H346" t="n">
-        <v>42</v>
-      </c>
-      <c r="I346" t="n">
-        <v>6</v>
-      </c>
-      <c r="J346" t="n">
-        <v>24</v>
-      </c>
-      <c r="K346" t="n">
-        <v>13</v>
-      </c>
-      <c r="L346" t="n">
-        <v>23</v>
-      </c>
-      <c r="M346" t="n">
-        <v>10</v>
-      </c>
-      <c r="N346" t="n">
-        <v>18</v>
-      </c>
-      <c r="O346" t="n">
-        <v>12</v>
-      </c>
-      <c r="P346" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q346" t="n">
-        <v>19</v>
-      </c>
-      <c r="R346" t="n">
-        <v>17</v>
-      </c>
-      <c r="S346" t="n">
-        <v>22</v>
-      </c>
-      <c r="T346" t="n">
-        <v>4</v>
-      </c>
-      <c r="U346" t="inlineStr">
-        <is>
-          <t>2487930</t>
-        </is>
-      </c>
-      <c r="V346" t="n">
-        <v>85</v>
-      </c>
-      <c r="W346" t="n">
-        <v>95.12</v>
-      </c>
-      <c r="X346" t="n">
-        <v>0.7674516400336416</v>
-      </c>
-      <c r="Y346" t="n">
-        <v>85.12</v>
-      </c>
-      <c r="Z346" t="n">
-        <v>85.76127819548871</v>
-      </c>
-      <c r="AA346" t="n">
-        <v>0.8631194151096669</v>
-      </c>
-      <c r="AB346" t="n">
-        <v>103.0552861299709</v>
-      </c>
-      <c r="AC346" t="n">
-        <v>0.2564102564102564</v>
-      </c>
-      <c r="AD346" t="n">
-        <v>0.5294117647058824</v>
-      </c>
-      <c r="AE346" t="n">
-        <v>0.3835616438356164</v>
-      </c>
-      <c r="AF346" t="n">
-        <v>-17.29400793448218</v>
-      </c>
-      <c r="AG346" t="inlineStr">
-        <is>
-          <t>CULTURAL Y DEPORTIVA LEONESA</t>
-        </is>
-      </c>
-      <c r="AH346" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AI346" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="347">
-      <c r="A347" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B347" t="n">
-        <v>25</v>
-      </c>
-      <c r="C347" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="D347" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="E347" t="n">
-        <v>200</v>
-      </c>
-      <c r="F347" t="n">
-        <v>70</v>
-      </c>
-      <c r="G347" t="n">
-        <v>18</v>
-      </c>
-      <c r="H347" t="n">
-        <v>40</v>
-      </c>
-      <c r="I347" t="n">
-        <v>9</v>
-      </c>
-      <c r="J347" t="n">
-        <v>25</v>
-      </c>
-      <c r="K347" t="n">
-        <v>7</v>
-      </c>
-      <c r="L347" t="n">
-        <v>7</v>
-      </c>
-      <c r="M347" t="n">
-        <v>11</v>
-      </c>
-      <c r="N347" t="n">
-        <v>21</v>
-      </c>
-      <c r="O347" t="n">
-        <v>18</v>
-      </c>
-      <c r="P347" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q347" t="n">
-        <v>10</v>
-      </c>
-      <c r="R347" t="n">
-        <v>16</v>
-      </c>
-      <c r="S347" t="n">
-        <v>16</v>
-      </c>
-      <c r="T347" t="n">
-        <v>0</v>
-      </c>
-      <c r="U347" t="inlineStr">
-        <is>
-          <t>2487932</t>
-        </is>
-      </c>
-      <c r="V347" t="n">
-        <v>68</v>
-      </c>
-      <c r="W347" t="n">
-        <v>78.08</v>
-      </c>
-      <c r="X347" t="n">
-        <v>0.896516393442623</v>
-      </c>
-      <c r="Y347" t="n">
-        <v>67.08</v>
-      </c>
-      <c r="Z347" t="n">
-        <v>104.3530113297555</v>
-      </c>
-      <c r="AA347" t="n">
-        <v>0.8966244725738396</v>
-      </c>
-      <c r="AB347" t="n">
-        <v>103.2806804374241</v>
-      </c>
-      <c r="AC347" t="n">
-        <v>0.3235294117647059</v>
-      </c>
-      <c r="AD347" t="n">
-        <v>0.6774193548387096</v>
-      </c>
-      <c r="AE347" t="n">
-        <v>0.4923076923076923</v>
-      </c>
-      <c r="AF347" t="n">
-        <v>1.072330892331465</v>
-      </c>
-      <c r="AG347" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="AH347" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="AI347" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="348">
-      <c r="A348" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B348" t="n">
-        <v>25</v>
-      </c>
-      <c r="C348" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-      <c r="D348" t="inlineStr">
-        <is>
-          <t>BIELE ISB</t>
-        </is>
-      </c>
-      <c r="E348" t="n">
-        <v>200</v>
-      </c>
-      <c r="F348" t="n">
-        <v>71</v>
-      </c>
-      <c r="G348" t="n">
-        <v>16</v>
-      </c>
-      <c r="H348" t="n">
-        <v>37</v>
-      </c>
-      <c r="I348" t="n">
-        <v>9</v>
-      </c>
-      <c r="J348" t="n">
-        <v>25</v>
-      </c>
-      <c r="K348" t="n">
-        <v>12</v>
-      </c>
-      <c r="L348" t="n">
-        <v>15</v>
-      </c>
-      <c r="M348" t="n">
-        <v>10</v>
-      </c>
-      <c r="N348" t="n">
-        <v>13</v>
-      </c>
-      <c r="O348" t="n">
-        <v>9</v>
-      </c>
-      <c r="P348" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q348" t="n">
-        <v>11</v>
-      </c>
-      <c r="R348" t="n">
-        <v>11</v>
-      </c>
-      <c r="S348" t="n">
-        <v>21</v>
-      </c>
-      <c r="T348" t="n">
-        <v>0</v>
-      </c>
-      <c r="U348" t="inlineStr">
-        <is>
-          <t>2487933</t>
-        </is>
-      </c>
-      <c r="V348" t="n">
-        <v>102</v>
-      </c>
-      <c r="W348" t="n">
-        <v>79.59999999999999</v>
-      </c>
-      <c r="X348" t="n">
-        <v>0.8919597989949749</v>
-      </c>
-      <c r="Y348" t="n">
-        <v>69.59999999999999</v>
-      </c>
-      <c r="Z348" t="n">
-        <v>102.0114942528736</v>
-      </c>
-      <c r="AA348" t="n">
-        <v>1.259881422924901</v>
-      </c>
-      <c r="AB348" t="n">
-        <v>139.8026315789473</v>
-      </c>
-      <c r="AC348" t="n">
-        <v>0.2777777777777778</v>
-      </c>
-      <c r="AD348" t="n">
-        <v>0.6190476190476191</v>
-      </c>
-      <c r="AE348" t="n">
-        <v>0.4035087719298245</v>
-      </c>
-      <c r="AF348" t="n">
-        <v>-37.79113732607377</v>
-      </c>
-      <c r="AG348" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-      <c r="AH348" t="inlineStr">
-        <is>
-          <t>BIELE ISB</t>
-        </is>
-      </c>
-      <c r="AI348" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="349">
-      <c r="A349" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B349" t="n">
-        <v>25</v>
-      </c>
-      <c r="C349" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="E349" t="n">
-        <v>200</v>
-      </c>
-      <c r="F349" t="n">
-        <v>68</v>
-      </c>
-      <c r="G349" t="n">
-        <v>20</v>
-      </c>
-      <c r="H349" t="n">
-        <v>37</v>
-      </c>
-      <c r="I349" t="n">
-        <v>7</v>
-      </c>
-      <c r="J349" t="n">
-        <v>24</v>
-      </c>
-      <c r="K349" t="n">
-        <v>7</v>
-      </c>
-      <c r="L349" t="n">
-        <v>11</v>
-      </c>
-      <c r="M349" t="n">
-        <v>10</v>
-      </c>
-      <c r="N349" t="n">
-        <v>23</v>
-      </c>
-      <c r="O349" t="n">
-        <v>15</v>
-      </c>
-      <c r="P349" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q349" t="n">
-        <v>10</v>
-      </c>
-      <c r="R349" t="n">
-        <v>16</v>
-      </c>
-      <c r="S349" t="n">
-        <v>16</v>
-      </c>
-      <c r="T349" t="n">
-        <v>4</v>
-      </c>
-      <c r="U349" t="inlineStr">
-        <is>
-          <t>2487932</t>
-        </is>
-      </c>
-      <c r="V349" t="n">
-        <v>70</v>
-      </c>
-      <c r="W349" t="n">
-        <v>75.84</v>
-      </c>
-      <c r="X349" t="n">
-        <v>0.8966244725738396</v>
-      </c>
-      <c r="Y349" t="n">
-        <v>65.84</v>
-      </c>
-      <c r="Z349" t="n">
-        <v>103.2806804374241</v>
-      </c>
-      <c r="AA349" t="n">
-        <v>0.896516393442623</v>
-      </c>
-      <c r="AB349" t="n">
-        <v>104.3530113297555</v>
-      </c>
-      <c r="AC349" t="n">
-        <v>0.3225806451612903</v>
-      </c>
-      <c r="AD349" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="AE349" t="n">
-        <v>0.5076923076923077</v>
-      </c>
-      <c r="AF349" t="n">
-        <v>-1.072330892331465</v>
-      </c>
-      <c r="AG349" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="AH349" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="AI349" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="350">
-      <c r="A350" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B350" t="n">
-        <v>25</v>
-      </c>
-      <c r="C350" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO</t>
-        </is>
-      </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-      <c r="E350" t="n">
-        <v>200</v>
-      </c>
-      <c r="F350" t="n">
-        <v>85</v>
-      </c>
-      <c r="G350" t="n">
-        <v>24</v>
-      </c>
-      <c r="H350" t="n">
-        <v>35</v>
-      </c>
-      <c r="I350" t="n">
-        <v>8</v>
-      </c>
-      <c r="J350" t="n">
-        <v>31</v>
-      </c>
-      <c r="K350" t="n">
-        <v>13</v>
-      </c>
-      <c r="L350" t="n">
-        <v>20</v>
-      </c>
-      <c r="M350" t="n">
-        <v>10</v>
-      </c>
-      <c r="N350" t="n">
-        <v>27</v>
-      </c>
-      <c r="O350" t="n">
-        <v>22</v>
-      </c>
-      <c r="P350" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q350" t="n">
-        <v>12</v>
-      </c>
-      <c r="R350" t="n">
-        <v>24</v>
-      </c>
-      <c r="S350" t="n">
-        <v>21</v>
-      </c>
-      <c r="T350" t="n">
-        <v>0</v>
-      </c>
-      <c r="U350" t="inlineStr">
-        <is>
-          <t>2487929</t>
-        </is>
-      </c>
-      <c r="V350" t="n">
-        <v>68</v>
-      </c>
-      <c r="W350" t="n">
-        <v>86.8</v>
-      </c>
-      <c r="X350" t="n">
-        <v>0.9792626728110599</v>
-      </c>
-      <c r="Y350" t="n">
-        <v>76.8</v>
-      </c>
-      <c r="Z350" t="n">
-        <v>110.6770833333333</v>
-      </c>
-      <c r="AA350" t="n">
-        <v>0.8407517309594461</v>
-      </c>
-      <c r="AB350" t="n">
-        <v>90.81196581196582</v>
-      </c>
-      <c r="AC350" t="n">
-        <v>0.303030303030303</v>
-      </c>
-      <c r="AD350" t="n">
-        <v>0.8181818181818182</v>
-      </c>
-      <c r="AE350" t="n">
-        <v>0.5606060606060606</v>
-      </c>
-      <c r="AF350" t="n">
-        <v>19.86511752136752</v>
-      </c>
-      <c r="AG350" t="inlineStr">
-        <is>
-          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-      <c r="AH350" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO</t>
-        </is>
-      </c>
-      <c r="AI350" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="351">
-      <c r="A351" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B351" t="n">
-        <v>25</v>
-      </c>
-      <c r="C351" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
-        </is>
-      </c>
-      <c r="E351" t="n">
-        <v>200</v>
-      </c>
-      <c r="F351" t="n">
-        <v>85</v>
-      </c>
-      <c r="G351" t="n">
-        <v>22</v>
-      </c>
-      <c r="H351" t="n">
-        <v>44</v>
-      </c>
-      <c r="I351" t="n">
-        <v>7</v>
-      </c>
-      <c r="J351" t="n">
-        <v>19</v>
-      </c>
-      <c r="K351" t="n">
-        <v>20</v>
-      </c>
-      <c r="L351" t="n">
-        <v>26</v>
-      </c>
-      <c r="M351" t="n">
-        <v>6</v>
-      </c>
-      <c r="N351" t="n">
-        <v>25</v>
-      </c>
-      <c r="O351" t="n">
-        <v>19</v>
-      </c>
-      <c r="P351" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q351" t="n">
-        <v>11</v>
-      </c>
-      <c r="R351" t="n">
-        <v>30</v>
-      </c>
-      <c r="S351" t="n">
-        <v>25</v>
-      </c>
-      <c r="T351" t="n">
-        <v>0</v>
-      </c>
-      <c r="U351" t="inlineStr">
-        <is>
-          <t>2487927</t>
-        </is>
-      </c>
-      <c r="V351" t="n">
-        <v>98</v>
-      </c>
-      <c r="W351" t="n">
-        <v>85.44</v>
-      </c>
-      <c r="X351" t="n">
-        <v>0.9948501872659177</v>
-      </c>
-      <c r="Y351" t="n">
-        <v>79.44</v>
-      </c>
-      <c r="Z351" t="n">
-        <v>106.9989929506546</v>
-      </c>
-      <c r="AA351" t="n">
-        <v>1.040781648258284</v>
-      </c>
-      <c r="AB351" t="n">
-        <v>119.2794547224927</v>
-      </c>
-      <c r="AC351" t="n">
-        <v>0.1875</v>
-      </c>
-      <c r="AD351" t="n">
-        <v>0.6756756756756757</v>
-      </c>
-      <c r="AE351" t="n">
-        <v>0.4492753623188406</v>
-      </c>
-      <c r="AF351" t="n">
-        <v>-12.28046177183812</v>
-      </c>
-      <c r="AG351" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID</t>
-        </is>
-      </c>
-      <c r="AH351" t="inlineStr">
-        <is>
-          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
-        </is>
-      </c>
-      <c r="AI351" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="352">
-      <c r="A352" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B352" t="n">
-        <v>26</v>
-      </c>
-      <c r="C352" t="inlineStr">
-        <is>
-          <t>BIELE ISB</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID</t>
-        </is>
-      </c>
-      <c r="E352" t="n">
-        <v>200</v>
-      </c>
-      <c r="F352" t="n">
-        <v>100</v>
-      </c>
-      <c r="G352" t="n">
-        <v>26</v>
-      </c>
-      <c r="H352" t="n">
-        <v>42</v>
-      </c>
-      <c r="I352" t="n">
-        <v>9</v>
-      </c>
-      <c r="J352" t="n">
-        <v>21</v>
-      </c>
-      <c r="K352" t="n">
-        <v>21</v>
-      </c>
-      <c r="L352" t="n">
-        <v>24</v>
-      </c>
-      <c r="M352" t="n">
-        <v>9</v>
-      </c>
-      <c r="N352" t="n">
-        <v>22</v>
-      </c>
-      <c r="O352" t="n">
-        <v>18</v>
-      </c>
-      <c r="P352" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q352" t="n">
-        <v>10</v>
-      </c>
-      <c r="R352" t="n">
-        <v>23</v>
-      </c>
-      <c r="S352" t="n">
-        <v>24</v>
-      </c>
-      <c r="T352" t="n">
-        <v>1</v>
-      </c>
-      <c r="U352" t="inlineStr">
-        <is>
-          <t>2487934</t>
-        </is>
-      </c>
-      <c r="V352" t="n">
-        <v>84</v>
-      </c>
-      <c r="W352" t="n">
-        <v>83.56</v>
-      </c>
-      <c r="X352" t="n">
-        <v>1.196744853997128</v>
-      </c>
-      <c r="Y352" t="n">
-        <v>74.56</v>
-      </c>
-      <c r="Z352" t="n">
-        <v>134.1201716738197</v>
-      </c>
-      <c r="AA352" t="n">
-        <v>0.9896324222431668</v>
-      </c>
-      <c r="AB352" t="n">
-        <v>109.261186264308</v>
-      </c>
-      <c r="AC352" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AD352" t="n">
-        <v>0.7333333333333333</v>
-      </c>
-      <c r="AE352" t="n">
-        <v>0.543859649122807</v>
-      </c>
-      <c r="AF352" t="n">
-        <v>24.8589854095117</v>
-      </c>
-      <c r="AG352" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID</t>
-        </is>
-      </c>
-      <c r="AH352" t="inlineStr">
-        <is>
-          <t>BIELE ISB</t>
-        </is>
-      </c>
-      <c r="AI352" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="353">
-      <c r="A353" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B353" t="n">
-        <v>26</v>
-      </c>
-      <c r="C353" t="inlineStr">
-        <is>
-          <t>C.B. STARLABS MORÓN</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="E353" t="n">
-        <v>200</v>
-      </c>
-      <c r="F353" t="n">
-        <v>75</v>
-      </c>
-      <c r="G353" t="n">
-        <v>22</v>
-      </c>
-      <c r="H353" t="n">
-        <v>42</v>
-      </c>
-      <c r="I353" t="n">
-        <v>7</v>
-      </c>
-      <c r="J353" t="n">
-        <v>17</v>
-      </c>
-      <c r="K353" t="n">
-        <v>10</v>
-      </c>
-      <c r="L353" t="n">
-        <v>17</v>
-      </c>
-      <c r="M353" t="n">
-        <v>6</v>
-      </c>
-      <c r="N353" t="n">
-        <v>20</v>
-      </c>
-      <c r="O353" t="n">
-        <v>18</v>
-      </c>
-      <c r="P353" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q353" t="n">
-        <v>15</v>
-      </c>
-      <c r="R353" t="n">
-        <v>22</v>
-      </c>
-      <c r="S353" t="n">
-        <v>19</v>
-      </c>
-      <c r="T353" t="n">
-        <v>0</v>
-      </c>
-      <c r="U353" t="inlineStr">
-        <is>
-          <t>2487936</t>
-        </is>
-      </c>
-      <c r="V353" t="n">
-        <v>84</v>
-      </c>
-      <c r="W353" t="n">
-        <v>81.48</v>
-      </c>
-      <c r="X353" t="n">
-        <v>0.9204712812960235</v>
-      </c>
-      <c r="Y353" t="n">
-        <v>75.48</v>
-      </c>
-      <c r="Z353" t="n">
-        <v>99.36406995230524</v>
-      </c>
-      <c r="AA353" t="n">
-        <v>0.9726725335803613</v>
-      </c>
-      <c r="AB353" t="n">
-        <v>111.4649681528662</v>
-      </c>
-      <c r="AC353" t="n">
-        <v>0.2068965517241379</v>
-      </c>
-      <c r="AD353" t="n">
-        <v>0.6451612903225806</v>
-      </c>
-      <c r="AE353" t="n">
-        <v>0.4333333333333333</v>
-      </c>
-      <c r="AF353" t="n">
-        <v>-12.10089820056101</v>
-      </c>
-      <c r="AG353" t="inlineStr">
-        <is>
-          <t>C.B. STARLABS MORÓN</t>
-        </is>
-      </c>
-      <c r="AH353" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="AI353" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="354">
-      <c r="A354" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B354" t="n">
-        <v>26</v>
-      </c>
-      <c r="C354" t="inlineStr">
-        <is>
-          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
-        </is>
-      </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="E354" t="n">
-        <v>200</v>
-      </c>
-      <c r="F354" t="n">
-        <v>77</v>
-      </c>
-      <c r="G354" t="n">
-        <v>16</v>
-      </c>
-      <c r="H354" t="n">
-        <v>36</v>
-      </c>
-      <c r="I354" t="n">
-        <v>10</v>
-      </c>
-      <c r="J354" t="n">
-        <v>29</v>
-      </c>
-      <c r="K354" t="n">
-        <v>15</v>
-      </c>
-      <c r="L354" t="n">
-        <v>24</v>
-      </c>
-      <c r="M354" t="n">
-        <v>13</v>
-      </c>
-      <c r="N354" t="n">
-        <v>18</v>
-      </c>
-      <c r="O354" t="n">
-        <v>9</v>
-      </c>
-      <c r="P354" t="n">
-        <v>5</v>
-      </c>
-      <c r="Q354" t="n">
-        <v>10</v>
-      </c>
-      <c r="R354" t="n">
-        <v>21</v>
-      </c>
-      <c r="S354" t="n">
-        <v>24</v>
-      </c>
-      <c r="T354" t="n">
-        <v>2</v>
-      </c>
-      <c r="U354" t="inlineStr">
-        <is>
-          <t>2487940</t>
-        </is>
-      </c>
-      <c r="V354" t="n">
-        <v>75</v>
-      </c>
-      <c r="W354" t="n">
-        <v>85.56</v>
-      </c>
-      <c r="X354" t="n">
-        <v>0.8999532491818607</v>
-      </c>
-      <c r="Y354" t="n">
-        <v>72.56</v>
-      </c>
-      <c r="Z354" t="n">
-        <v>106.1190738699008</v>
-      </c>
-      <c r="AA354" t="n">
-        <v>0.8449752140603877</v>
-      </c>
-      <c r="AB354" t="n">
-        <v>103.0786146234195</v>
-      </c>
-      <c r="AC354" t="n">
-        <v>0.325</v>
-      </c>
-      <c r="AD354" t="n">
-        <v>0.5294117647058824</v>
-      </c>
-      <c r="AE354" t="n">
-        <v>0.4189189189189189</v>
-      </c>
-      <c r="AF354" t="n">
-        <v>3.040459246481305</v>
-      </c>
-      <c r="AG354" t="inlineStr">
-        <is>
-          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
-        </is>
-      </c>
-      <c r="AH354" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="AI354" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="355">
-      <c r="A355" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B355" t="n">
-        <v>26</v>
-      </c>
-      <c r="C355" t="inlineStr">
-        <is>
-          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-      <c r="E355" t="n">
-        <v>200</v>
-      </c>
-      <c r="F355" t="n">
-        <v>69</v>
-      </c>
-      <c r="G355" t="n">
-        <v>13</v>
-      </c>
-      <c r="H355" t="n">
-        <v>31</v>
-      </c>
-      <c r="I355" t="n">
-        <v>9</v>
-      </c>
-      <c r="J355" t="n">
-        <v>25</v>
-      </c>
-      <c r="K355" t="n">
-        <v>16</v>
-      </c>
-      <c r="L355" t="n">
-        <v>30</v>
-      </c>
-      <c r="M355" t="n">
-        <v>11</v>
-      </c>
-      <c r="N355" t="n">
-        <v>25</v>
-      </c>
-      <c r="O355" t="n">
-        <v>14</v>
-      </c>
-      <c r="P355" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q355" t="n">
-        <v>18</v>
-      </c>
-      <c r="R355" t="n">
-        <v>22</v>
-      </c>
-      <c r="S355" t="n">
-        <v>23</v>
-      </c>
-      <c r="T355" t="n">
-        <v>2</v>
-      </c>
-      <c r="U355" t="inlineStr">
-        <is>
-          <t>2487939</t>
-        </is>
-      </c>
-      <c r="V355" t="n">
-        <v>80</v>
-      </c>
-      <c r="W355" t="n">
-        <v>87.2</v>
-      </c>
-      <c r="X355" t="n">
-        <v>0.7912844036697247</v>
-      </c>
-      <c r="Y355" t="n">
-        <v>76.2</v>
-      </c>
-      <c r="Z355" t="n">
-        <v>90.55118110236221</v>
-      </c>
-      <c r="AA355" t="n">
-        <v>0.9000900090009001</v>
-      </c>
-      <c r="AB355" t="n">
-        <v>108.283703302653</v>
-      </c>
-      <c r="AC355" t="n">
-        <v>0.3055555555555556</v>
-      </c>
-      <c r="AD355" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="AE355" t="n">
-        <v>0.4736842105263158</v>
-      </c>
-      <c r="AF355" t="n">
-        <v>-17.73252220029075</v>
-      </c>
-      <c r="AG355" t="inlineStr">
-        <is>
-          <t>COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-      <c r="AH355" t="inlineStr">
-        <is>
-          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-      <c r="AI355" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="356">
-      <c r="A356" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B356" t="n">
-        <v>26</v>
-      </c>
-      <c r="C356" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="D356" t="inlineStr">
-        <is>
-          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
-        </is>
-      </c>
-      <c r="E356" t="n">
-        <v>200</v>
-      </c>
-      <c r="F356" t="n">
-        <v>75</v>
-      </c>
-      <c r="G356" t="n">
-        <v>17</v>
-      </c>
-      <c r="H356" t="n">
-        <v>35</v>
-      </c>
-      <c r="I356" t="n">
-        <v>7</v>
-      </c>
-      <c r="J356" t="n">
-        <v>25</v>
-      </c>
-      <c r="K356" t="n">
-        <v>20</v>
-      </c>
-      <c r="L356" t="n">
-        <v>29</v>
-      </c>
-      <c r="M356" t="n">
-        <v>16</v>
-      </c>
-      <c r="N356" t="n">
-        <v>27</v>
-      </c>
-      <c r="O356" t="n">
-        <v>17</v>
-      </c>
-      <c r="P356" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q356" t="n">
-        <v>16</v>
-      </c>
-      <c r="R356" t="n">
-        <v>24</v>
-      </c>
-      <c r="S356" t="n">
-        <v>21</v>
-      </c>
-      <c r="T356" t="n">
-        <v>1</v>
-      </c>
-      <c r="U356" t="inlineStr">
-        <is>
-          <t>2487940</t>
-        </is>
-      </c>
-      <c r="V356" t="n">
-        <v>77</v>
-      </c>
-      <c r="W356" t="n">
-        <v>88.75999999999999</v>
-      </c>
-      <c r="X356" t="n">
-        <v>0.8449752140603877</v>
-      </c>
-      <c r="Y356" t="n">
-        <v>72.75999999999999</v>
-      </c>
-      <c r="Z356" t="n">
-        <v>103.0786146234195</v>
-      </c>
-      <c r="AA356" t="n">
-        <v>0.8999532491818607</v>
-      </c>
-      <c r="AB356" t="n">
-        <v>106.1190738699008</v>
-      </c>
-      <c r="AC356" t="n">
-        <v>0.4705882352941176</v>
-      </c>
-      <c r="AD356" t="n">
-        <v>0.675</v>
-      </c>
-      <c r="AE356" t="n">
-        <v>0.581081081081081</v>
-      </c>
-      <c r="AF356" t="n">
-        <v>-3.040459246481305</v>
-      </c>
-      <c r="AG356" t="inlineStr">
-        <is>
-          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
-        </is>
-      </c>
-      <c r="AH356" t="inlineStr">
-        <is>
-          <t>CLUB BALONCESTO TOLEDO BASKET</t>
-        </is>
-      </c>
-      <c r="AI356" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="357">
-      <c r="A357" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B357" t="n">
-        <v>26</v>
-      </c>
-      <c r="C357" t="inlineStr">
-        <is>
-          <t>CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-      <c r="D357" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO</t>
-        </is>
-      </c>
-      <c r="E357" t="n">
-        <v>200</v>
-      </c>
-      <c r="F357" t="n">
-        <v>83</v>
-      </c>
-      <c r="G357" t="n">
-        <v>21</v>
-      </c>
-      <c r="H357" t="n">
-        <v>36</v>
-      </c>
-      <c r="I357" t="n">
-        <v>11</v>
-      </c>
-      <c r="J357" t="n">
-        <v>32</v>
-      </c>
-      <c r="K357" t="n">
-        <v>8</v>
-      </c>
-      <c r="L357" t="n">
-        <v>8</v>
-      </c>
-      <c r="M357" t="n">
-        <v>11</v>
-      </c>
-      <c r="N357" t="n">
-        <v>31</v>
-      </c>
-      <c r="O357" t="n">
-        <v>19</v>
-      </c>
-      <c r="P357" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q357" t="n">
-        <v>18</v>
-      </c>
-      <c r="R357" t="n">
-        <v>18</v>
-      </c>
-      <c r="S357" t="n">
-        <v>15</v>
-      </c>
-      <c r="T357" t="n">
-        <v>1</v>
-      </c>
-      <c r="U357" t="inlineStr">
-        <is>
-          <t>2487937</t>
-        </is>
-      </c>
-      <c r="V357" t="n">
-        <v>54</v>
-      </c>
-      <c r="W357" t="n">
-        <v>89.52000000000001</v>
-      </c>
-      <c r="X357" t="n">
-        <v>0.9271671134941911</v>
-      </c>
-      <c r="Y357" t="n">
-        <v>78.52000000000001</v>
-      </c>
-      <c r="Z357" t="n">
-        <v>105.7055527254203</v>
-      </c>
-      <c r="AA357" t="n">
-        <v>0.6493506493506493</v>
-      </c>
-      <c r="AB357" t="n">
-        <v>69.98444790046656</v>
-      </c>
-      <c r="AC357" t="n">
-        <v>0.3235294117647059</v>
-      </c>
-      <c r="AD357" t="n">
-        <v>0.8378378378378378</v>
-      </c>
-      <c r="AE357" t="n">
-        <v>0.5915492957746479</v>
-      </c>
-      <c r="AF357" t="n">
-        <v>35.7211048249537</v>
-      </c>
-      <c r="AG357" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AH357" t="inlineStr">
-        <is>
-          <t>CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-      <c r="AI357" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="358">
-      <c r="A358" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B358" t="n">
-        <v>26</v>
-      </c>
-      <c r="C358" t="inlineStr">
-        <is>
-          <t>COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-      <c r="D358" t="inlineStr">
-        <is>
-          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-      <c r="E358" t="n">
-        <v>200</v>
-      </c>
-      <c r="F358" t="n">
-        <v>80</v>
-      </c>
-      <c r="G358" t="n">
-        <v>15</v>
-      </c>
-      <c r="H358" t="n">
-        <v>29</v>
-      </c>
-      <c r="I358" t="n">
-        <v>11</v>
-      </c>
-      <c r="J358" t="n">
-        <v>33</v>
-      </c>
-      <c r="K358" t="n">
-        <v>17</v>
-      </c>
-      <c r="L358" t="n">
-        <v>27</v>
-      </c>
-      <c r="M358" t="n">
-        <v>15</v>
-      </c>
-      <c r="N358" t="n">
-        <v>25</v>
-      </c>
-      <c r="O358" t="n">
-        <v>16</v>
-      </c>
-      <c r="P358" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q358" t="n">
-        <v>15</v>
-      </c>
-      <c r="R358" t="n">
-        <v>24</v>
-      </c>
-      <c r="S358" t="n">
-        <v>22</v>
-      </c>
-      <c r="T358" t="n">
-        <v>2</v>
-      </c>
-      <c r="U358" t="inlineStr">
-        <is>
-          <t>2487939</t>
-        </is>
-      </c>
-      <c r="V358" t="n">
-        <v>69</v>
-      </c>
-      <c r="W358" t="n">
-        <v>88.88</v>
-      </c>
-      <c r="X358" t="n">
-        <v>0.9000900090009001</v>
-      </c>
-      <c r="Y358" t="n">
-        <v>73.88</v>
-      </c>
-      <c r="Z358" t="n">
-        <v>108.283703302653</v>
-      </c>
-      <c r="AA358" t="n">
-        <v>0.7912844036697247</v>
-      </c>
-      <c r="AB358" t="n">
-        <v>90.55118110236221</v>
-      </c>
-      <c r="AC358" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="AD358" t="n">
-        <v>0.6944444444444444</v>
-      </c>
-      <c r="AE358" t="n">
-        <v>0.5263157894736842</v>
-      </c>
-      <c r="AF358" t="n">
-        <v>17.73252220029075</v>
-      </c>
-      <c r="AG358" t="inlineStr">
-        <is>
-          <t>COTO CÓRDOBA CB</t>
-        </is>
-      </c>
-      <c r="AH358" t="inlineStr">
-        <is>
-          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
-        </is>
-      </c>
-      <c r="AI358" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="359">
-      <c r="A359" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B359" t="n">
-        <v>26</v>
-      </c>
-      <c r="C359" t="inlineStr">
-        <is>
-          <t>CULTURAL Y DEPORTIVA LEONESA</t>
-        </is>
-      </c>
-      <c r="D359" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO</t>
-        </is>
-      </c>
-      <c r="E359" t="n">
-        <v>200</v>
-      </c>
-      <c r="F359" t="n">
-        <v>88</v>
-      </c>
-      <c r="G359" t="n">
-        <v>31</v>
-      </c>
-      <c r="H359" t="n">
-        <v>53</v>
-      </c>
-      <c r="I359" t="n">
-        <v>5</v>
-      </c>
-      <c r="J359" t="n">
-        <v>12</v>
-      </c>
-      <c r="K359" t="n">
-        <v>11</v>
-      </c>
-      <c r="L359" t="n">
-        <v>19</v>
-      </c>
-      <c r="M359" t="n">
-        <v>7</v>
-      </c>
-      <c r="N359" t="n">
-        <v>24</v>
-      </c>
-      <c r="O359" t="n">
-        <v>18</v>
-      </c>
-      <c r="P359" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q359" t="n">
-        <v>12</v>
-      </c>
-      <c r="R359" t="n">
-        <v>25</v>
-      </c>
-      <c r="S359" t="n">
-        <v>21</v>
-      </c>
-      <c r="T359" t="n">
-        <v>3</v>
-      </c>
-      <c r="U359" t="inlineStr">
-        <is>
-          <t>2487938</t>
-        </is>
-      </c>
-      <c r="V359" t="n">
-        <v>91</v>
-      </c>
-      <c r="W359" t="n">
-        <v>85.36</v>
-      </c>
-      <c r="X359" t="n">
-        <v>1.030927835051547</v>
-      </c>
-      <c r="Y359" t="n">
-        <v>78.36</v>
-      </c>
-      <c r="Z359" t="n">
-        <v>112.3021949974477</v>
-      </c>
-      <c r="AA359" t="n">
-        <v>0.9964958388085853</v>
-      </c>
-      <c r="AB359" t="n">
-        <v>114.7251638930913</v>
-      </c>
-      <c r="AC359" t="n">
-        <v>0.2333333333333333</v>
-      </c>
-      <c r="AD359" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AE359" t="n">
-        <v>0.4696969696969697</v>
-      </c>
-      <c r="AF359" t="n">
-        <v>-2.422968895643621</v>
-      </c>
-      <c r="AG359" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO</t>
-        </is>
-      </c>
-      <c r="AH359" t="inlineStr">
-        <is>
-          <t>CULTURAL Y DEPORTIVA LEONESA</t>
-        </is>
-      </c>
-      <c r="AI359" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="360">
-      <c r="A360" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B360" t="n">
-        <v>26</v>
-      </c>
-      <c r="C360" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO</t>
-        </is>
-      </c>
-      <c r="D360" t="inlineStr">
-        <is>
-          <t>CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-      <c r="E360" t="n">
-        <v>200</v>
-      </c>
-      <c r="F360" t="n">
-        <v>54</v>
-      </c>
-      <c r="G360" t="n">
-        <v>14</v>
-      </c>
-      <c r="H360" t="n">
-        <v>39</v>
-      </c>
-      <c r="I360" t="n">
-        <v>5</v>
-      </c>
-      <c r="J360" t="n">
-        <v>22</v>
-      </c>
-      <c r="K360" t="n">
-        <v>11</v>
-      </c>
-      <c r="L360" t="n">
-        <v>14</v>
-      </c>
-      <c r="M360" t="n">
-        <v>6</v>
-      </c>
-      <c r="N360" t="n">
-        <v>23</v>
-      </c>
-      <c r="O360" t="n">
-        <v>8</v>
-      </c>
-      <c r="P360" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q360" t="n">
-        <v>16</v>
-      </c>
-      <c r="R360" t="n">
-        <v>15</v>
-      </c>
-      <c r="S360" t="n">
-        <v>18</v>
-      </c>
-      <c r="T360" t="n">
-        <v>1</v>
-      </c>
-      <c r="U360" t="inlineStr">
-        <is>
-          <t>2487937</t>
-        </is>
-      </c>
-      <c r="V360" t="n">
-        <v>83</v>
-      </c>
-      <c r="W360" t="n">
-        <v>83.16</v>
-      </c>
-      <c r="X360" t="n">
-        <v>0.6493506493506493</v>
-      </c>
-      <c r="Y360" t="n">
-        <v>77.16</v>
-      </c>
-      <c r="Z360" t="n">
-        <v>69.98444790046656</v>
-      </c>
-      <c r="AA360" t="n">
-        <v>0.9271671134941911</v>
-      </c>
-      <c r="AB360" t="n">
-        <v>105.7055527254203</v>
-      </c>
-      <c r="AC360" t="n">
-        <v>0.1621621621621622</v>
-      </c>
-      <c r="AD360" t="n">
-        <v>0.6764705882352942</v>
-      </c>
-      <c r="AE360" t="n">
-        <v>0.4084507042253521</v>
-      </c>
-      <c r="AF360" t="n">
-        <v>-35.7211048249537</v>
-      </c>
-      <c r="AG360" t="inlineStr">
-        <is>
-          <t>CÍRCULO GIJÓN BALONCESTO</t>
-        </is>
-      </c>
-      <c r="AH360" t="inlineStr">
-        <is>
-          <t>CLÍNICA PONFERRADA SDP</t>
-        </is>
-      </c>
-      <c r="AI360" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="361">
-      <c r="A361" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B361" t="n">
-        <v>26</v>
-      </c>
-      <c r="C361" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>C.B. STARLABS MORÓN</t>
-        </is>
-      </c>
-      <c r="E361" t="n">
-        <v>200</v>
-      </c>
-      <c r="F361" t="n">
-        <v>84</v>
-      </c>
-      <c r="G361" t="n">
-        <v>26</v>
-      </c>
-      <c r="H361" t="n">
-        <v>37</v>
-      </c>
-      <c r="I361" t="n">
-        <v>6</v>
-      </c>
-      <c r="J361" t="n">
-        <v>29</v>
-      </c>
-      <c r="K361" t="n">
-        <v>14</v>
-      </c>
-      <c r="L361" t="n">
-        <v>19</v>
-      </c>
-      <c r="M361" t="n">
-        <v>11</v>
-      </c>
-      <c r="N361" t="n">
-        <v>23</v>
-      </c>
-      <c r="O361" t="n">
-        <v>18</v>
-      </c>
-      <c r="P361" t="n">
-        <v>8</v>
-      </c>
-      <c r="Q361" t="n">
-        <v>12</v>
-      </c>
-      <c r="R361" t="n">
-        <v>19</v>
-      </c>
-      <c r="S361" t="n">
-        <v>21</v>
-      </c>
-      <c r="T361" t="n">
-        <v>4</v>
-      </c>
-      <c r="U361" t="inlineStr">
-        <is>
-          <t>2487936</t>
-        </is>
-      </c>
-      <c r="V361" t="n">
-        <v>75</v>
-      </c>
-      <c r="W361" t="n">
-        <v>86.36</v>
-      </c>
-      <c r="X361" t="n">
-        <v>0.9726725335803613</v>
-      </c>
-      <c r="Y361" t="n">
-        <v>75.36</v>
-      </c>
-      <c r="Z361" t="n">
-        <v>111.4649681528662</v>
-      </c>
-      <c r="AA361" t="n">
-        <v>0.9204712812960235</v>
-      </c>
-      <c r="AB361" t="n">
-        <v>99.36406995230524</v>
-      </c>
-      <c r="AC361" t="n">
-        <v>0.3548387096774194</v>
-      </c>
-      <c r="AD361" t="n">
-        <v>0.7931034482758621</v>
-      </c>
-      <c r="AE361" t="n">
-        <v>0.5666666666666667</v>
-      </c>
-      <c r="AF361" t="n">
-        <v>12.10089820056101</v>
-      </c>
-      <c r="AG361" t="inlineStr">
-        <is>
-          <t>C.B. STARLABS MORÓN</t>
-        </is>
-      </c>
-      <c r="AH361" t="inlineStr">
-        <is>
-          <t>INSOLAC CAJA 87</t>
-        </is>
-      </c>
-      <c r="AI361" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="362">
-      <c r="A362" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B362" t="n">
-        <v>26</v>
-      </c>
-      <c r="C362" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="E362" t="n">
-        <v>200</v>
-      </c>
-      <c r="F362" t="n">
-        <v>73</v>
-      </c>
-      <c r="G362" t="n">
-        <v>10</v>
-      </c>
-      <c r="H362" t="n">
-        <v>29</v>
-      </c>
-      <c r="I362" t="n">
-        <v>12</v>
-      </c>
-      <c r="J362" t="n">
-        <v>30</v>
-      </c>
-      <c r="K362" t="n">
-        <v>17</v>
-      </c>
-      <c r="L362" t="n">
-        <v>20</v>
-      </c>
-      <c r="M362" t="n">
-        <v>10</v>
-      </c>
-      <c r="N362" t="n">
-        <v>18</v>
-      </c>
-      <c r="O362" t="n">
-        <v>13</v>
-      </c>
-      <c r="P362" t="n">
-        <v>10</v>
-      </c>
-      <c r="Q362" t="n">
-        <v>13</v>
-      </c>
-      <c r="R362" t="n">
-        <v>29</v>
-      </c>
-      <c r="S362" t="n">
-        <v>20</v>
-      </c>
-      <c r="T362" t="n">
-        <v>1</v>
-      </c>
-      <c r="U362" t="inlineStr">
-        <is>
-          <t>2487935</t>
-        </is>
-      </c>
-      <c r="V362" t="n">
-        <v>69</v>
-      </c>
-      <c r="W362" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="X362" t="n">
-        <v>0.9034653465346535</v>
-      </c>
-      <c r="Y362" t="n">
-        <v>70.8</v>
-      </c>
-      <c r="Z362" t="n">
-        <v>103.1073446327684</v>
-      </c>
-      <c r="AA362" t="n">
-        <v>0.7649667405764966</v>
-      </c>
-      <c r="AB362" t="n">
-        <v>88.23529411764706</v>
-      </c>
-      <c r="AC362" t="n">
-        <v>0.2941176470588235</v>
-      </c>
-      <c r="AD362" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AE362" t="n">
-        <v>0.4375</v>
-      </c>
-      <c r="AF362" t="n">
-        <v>14.8720505151213</v>
-      </c>
-      <c r="AG362" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="AH362" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-      <c r="AI362" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="363">
-      <c r="A363" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B363" t="n">
-        <v>26</v>
-      </c>
-      <c r="C363" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-      <c r="E363" t="n">
-        <v>200</v>
-      </c>
-      <c r="F363" t="n">
-        <v>69</v>
-      </c>
-      <c r="G363" t="n">
-        <v>14</v>
-      </c>
-      <c r="H363" t="n">
-        <v>28</v>
-      </c>
-      <c r="I363" t="n">
-        <v>8</v>
-      </c>
-      <c r="J363" t="n">
-        <v>29</v>
-      </c>
-      <c r="K363" t="n">
-        <v>17</v>
-      </c>
-      <c r="L363" t="n">
-        <v>30</v>
-      </c>
-      <c r="M363" t="n">
-        <v>12</v>
-      </c>
-      <c r="N363" t="n">
-        <v>24</v>
-      </c>
-      <c r="O363" t="n">
-        <v>13</v>
-      </c>
-      <c r="P363" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q363" t="n">
-        <v>20</v>
-      </c>
-      <c r="R363" t="n">
-        <v>20</v>
-      </c>
-      <c r="S363" t="n">
-        <v>29</v>
-      </c>
-      <c r="T363" t="n">
-        <v>3</v>
-      </c>
-      <c r="U363" t="inlineStr">
-        <is>
-          <t>2487935</t>
-        </is>
-      </c>
-      <c r="V363" t="n">
-        <v>73</v>
-      </c>
-      <c r="W363" t="n">
-        <v>90.2</v>
-      </c>
-      <c r="X363" t="n">
-        <v>0.7649667405764966</v>
-      </c>
-      <c r="Y363" t="n">
-        <v>78.2</v>
-      </c>
-      <c r="Z363" t="n">
-        <v>88.23529411764706</v>
-      </c>
-      <c r="AA363" t="n">
-        <v>0.9034653465346535</v>
-      </c>
-      <c r="AB363" t="n">
-        <v>103.1073446327684</v>
-      </c>
-      <c r="AC363" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AD363" t="n">
-        <v>0.7058823529411765</v>
-      </c>
-      <c r="AE363" t="n">
-        <v>0.5625</v>
-      </c>
-      <c r="AF363" t="n">
-        <v>-14.8720505151213</v>
-      </c>
-      <c r="AG363" t="inlineStr">
-        <is>
-          <t>LOGROBASKET LOGI7</t>
-        </is>
-      </c>
-      <c r="AH363" t="inlineStr">
-        <is>
-          <t>JAEN PARAÍSO INTERIOR CB</t>
-        </is>
-      </c>
-      <c r="AI363" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="364">
-      <c r="A364" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B364" t="n">
-        <v>26</v>
-      </c>
-      <c r="C364" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO</t>
-        </is>
-      </c>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>CULTURAL Y DEPORTIVA LEONESA</t>
-        </is>
-      </c>
-      <c r="E364" t="n">
-        <v>200</v>
-      </c>
-      <c r="F364" t="n">
-        <v>91</v>
-      </c>
-      <c r="G364" t="n">
-        <v>18</v>
-      </c>
-      <c r="H364" t="n">
-        <v>38</v>
-      </c>
-      <c r="I364" t="n">
-        <v>14</v>
-      </c>
-      <c r="J364" t="n">
-        <v>27</v>
-      </c>
-      <c r="K364" t="n">
-        <v>13</v>
-      </c>
-      <c r="L364" t="n">
-        <v>28</v>
-      </c>
-      <c r="M364" t="n">
-        <v>12</v>
-      </c>
-      <c r="N364" t="n">
-        <v>23</v>
-      </c>
-      <c r="O364" t="n">
-        <v>17</v>
-      </c>
-      <c r="P364" t="n">
-        <v>6</v>
-      </c>
-      <c r="Q364" t="n">
-        <v>14</v>
-      </c>
-      <c r="R364" t="n">
-        <v>22</v>
-      </c>
-      <c r="S364" t="n">
-        <v>25</v>
-      </c>
-      <c r="T364" t="n">
-        <v>3</v>
-      </c>
-      <c r="U364" t="inlineStr">
-        <is>
-          <t>2487938</t>
-        </is>
-      </c>
-      <c r="V364" t="n">
-        <v>88</v>
-      </c>
-      <c r="W364" t="n">
-        <v>91.31999999999999</v>
-      </c>
-      <c r="X364" t="n">
-        <v>0.9964958388085853</v>
-      </c>
-      <c r="Y364" t="n">
-        <v>79.31999999999999</v>
-      </c>
-      <c r="Z364" t="n">
-        <v>114.7251638930913</v>
-      </c>
-      <c r="AA364" t="n">
-        <v>1.030927835051547</v>
-      </c>
-      <c r="AB364" t="n">
-        <v>112.3021949974477</v>
-      </c>
-      <c r="AC364" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-      <c r="AD364" t="n">
-        <v>0.7666666666666667</v>
-      </c>
-      <c r="AE364" t="n">
-        <v>0.5303030303030303</v>
-      </c>
-      <c r="AF364" t="n">
-        <v>2.422968895643621</v>
-      </c>
-      <c r="AG364" t="inlineStr">
-        <is>
-          <t>REINA PROTEÍNAS CLAVIJO</t>
-        </is>
-      </c>
-      <c r="AH364" t="inlineStr">
-        <is>
-          <t>CULTURAL Y DEPORTIVA LEONESA</t>
-        </is>
-      </c>
-      <c r="AI364" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="365">
-      <c r="A365" t="inlineStr">
-        <is>
-          <t>Liga Regular "OESTE"</t>
-        </is>
-      </c>
-      <c r="B365" t="n">
-        <v>26</v>
-      </c>
-      <c r="C365" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID</t>
-        </is>
-      </c>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>BIELE ISB</t>
-        </is>
-      </c>
-      <c r="E365" t="n">
-        <v>200</v>
-      </c>
-      <c r="F365" t="n">
-        <v>84</v>
-      </c>
-      <c r="G365" t="n">
-        <v>25</v>
-      </c>
-      <c r="H365" t="n">
-        <v>45</v>
-      </c>
-      <c r="I365" t="n">
-        <v>5</v>
-      </c>
-      <c r="J365" t="n">
-        <v>16</v>
-      </c>
-      <c r="K365" t="n">
-        <v>19</v>
-      </c>
-      <c r="L365" t="n">
-        <v>27</v>
-      </c>
-      <c r="M365" t="n">
-        <v>8</v>
-      </c>
-      <c r="N365" t="n">
-        <v>18</v>
-      </c>
-      <c r="O365" t="n">
-        <v>12</v>
-      </c>
-      <c r="P365" t="n">
-        <v>7</v>
-      </c>
-      <c r="Q365" t="n">
-        <v>12</v>
-      </c>
-      <c r="R365" t="n">
-        <v>24</v>
-      </c>
-      <c r="S365" t="n">
-        <v>23</v>
-      </c>
-      <c r="T365" t="n">
-        <v>2</v>
-      </c>
-      <c r="U365" t="inlineStr">
-        <is>
-          <t>2487934</t>
-        </is>
-      </c>
-      <c r="V365" t="n">
-        <v>100</v>
-      </c>
-      <c r="W365" t="n">
-        <v>84.88</v>
-      </c>
-      <c r="X365" t="n">
-        <v>0.9896324222431668</v>
-      </c>
-      <c r="Y365" t="n">
-        <v>76.88</v>
-      </c>
-      <c r="Z365" t="n">
-        <v>109.261186264308</v>
-      </c>
-      <c r="AA365" t="n">
-        <v>1.196744853997128</v>
-      </c>
-      <c r="AB365" t="n">
-        <v>134.1201716738197</v>
-      </c>
-      <c r="AC365" t="n">
-        <v>0.2666666666666667</v>
-      </c>
-      <c r="AD365" t="n">
-        <v>0.6666666666666666</v>
-      </c>
-      <c r="AE365" t="n">
-        <v>0.456140350877193</v>
-      </c>
-      <c r="AF365" t="n">
-        <v>-24.8589854095117</v>
-      </c>
-      <c r="AG365" t="inlineStr">
-        <is>
-          <t>UEMC BALONCESTO VALLADOLID</t>
-        </is>
-      </c>
-      <c r="AH365" t="inlineStr">
-        <is>
-          <t>BIELE ISB</t>
-        </is>
-      </c>
-      <c r="AI365" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/2FEB_25_26/players_25_26_2FEB_games.xlsx
+++ b/data/2FEB_25_26/players_25_26_2FEB_games.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI323"/>
+  <dimension ref="A1:AI365"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38921,6 +38921,5004 @@
       </c>
       <c r="AI323" t="b">
         <v>0</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>24</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E324" t="n">
+        <v>200</v>
+      </c>
+      <c r="F324" t="n">
+        <v>81</v>
+      </c>
+      <c r="G324" t="n">
+        <v>23</v>
+      </c>
+      <c r="H324" t="n">
+        <v>34</v>
+      </c>
+      <c r="I324" t="n">
+        <v>8</v>
+      </c>
+      <c r="J324" t="n">
+        <v>24</v>
+      </c>
+      <c r="K324" t="n">
+        <v>11</v>
+      </c>
+      <c r="L324" t="n">
+        <v>13</v>
+      </c>
+      <c r="M324" t="n">
+        <v>7</v>
+      </c>
+      <c r="N324" t="n">
+        <v>22</v>
+      </c>
+      <c r="O324" t="n">
+        <v>15</v>
+      </c>
+      <c r="P324" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q324" t="n">
+        <v>10</v>
+      </c>
+      <c r="R324" t="n">
+        <v>24</v>
+      </c>
+      <c r="S324" t="n">
+        <v>18</v>
+      </c>
+      <c r="T324" t="n">
+        <v>3</v>
+      </c>
+      <c r="U324" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="V324" t="n">
+        <v>79</v>
+      </c>
+      <c r="W324" t="n">
+        <v>73.72</v>
+      </c>
+      <c r="X324" t="n">
+        <v>1.09875203472599</v>
+      </c>
+      <c r="Y324" t="n">
+        <v>66.72</v>
+      </c>
+      <c r="Z324" t="n">
+        <v>121.4028776978417</v>
+      </c>
+      <c r="AA324" t="n">
+        <v>0.9440726577437858</v>
+      </c>
+      <c r="AB324" t="n">
+        <v>107.2204125950054</v>
+      </c>
+      <c r="AC324" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AD324" t="n">
+        <v>0.6875</v>
+      </c>
+      <c r="AE324" t="n">
+        <v>0.5087719298245614</v>
+      </c>
+      <c r="AF324" t="n">
+        <v>14.18246510283632</v>
+      </c>
+      <c r="AG324" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="AH324" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="AI324" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>24</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="E325" t="n">
+        <v>200</v>
+      </c>
+      <c r="F325" t="n">
+        <v>93</v>
+      </c>
+      <c r="G325" t="n">
+        <v>18</v>
+      </c>
+      <c r="H325" t="n">
+        <v>34</v>
+      </c>
+      <c r="I325" t="n">
+        <v>13</v>
+      </c>
+      <c r="J325" t="n">
+        <v>19</v>
+      </c>
+      <c r="K325" t="n">
+        <v>18</v>
+      </c>
+      <c r="L325" t="n">
+        <v>28</v>
+      </c>
+      <c r="M325" t="n">
+        <v>7</v>
+      </c>
+      <c r="N325" t="n">
+        <v>23</v>
+      </c>
+      <c r="O325" t="n">
+        <v>24</v>
+      </c>
+      <c r="P325" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q325" t="n">
+        <v>15</v>
+      </c>
+      <c r="R325" t="n">
+        <v>16</v>
+      </c>
+      <c r="S325" t="n">
+        <v>23</v>
+      </c>
+      <c r="T325" t="n">
+        <v>1</v>
+      </c>
+      <c r="U325" t="inlineStr">
+        <is>
+          <t>2487923</t>
+        </is>
+      </c>
+      <c r="V325" t="n">
+        <v>83</v>
+      </c>
+      <c r="W325" t="n">
+        <v>80.31999999999999</v>
+      </c>
+      <c r="X325" t="n">
+        <v>1.157868525896415</v>
+      </c>
+      <c r="Y325" t="n">
+        <v>73.31999999999999</v>
+      </c>
+      <c r="Z325" t="n">
+        <v>126.8412438625205</v>
+      </c>
+      <c r="AA325" t="n">
+        <v>0.8257063270990848</v>
+      </c>
+      <c r="AB325" t="n">
+        <v>104.3762575452716</v>
+      </c>
+      <c r="AC325" t="n">
+        <v>0.2916666666666667</v>
+      </c>
+      <c r="AD325" t="n">
+        <v>0.5227272727272727</v>
+      </c>
+      <c r="AE325" t="n">
+        <v>0.4411764705882353</v>
+      </c>
+      <c r="AF325" t="n">
+        <v>22.46498631724883</v>
+      </c>
+      <c r="AG325" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="AH325" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="AI325" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>24</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="E326" t="n">
+        <v>200</v>
+      </c>
+      <c r="F326" t="n">
+        <v>58</v>
+      </c>
+      <c r="G326" t="n">
+        <v>16</v>
+      </c>
+      <c r="H326" t="n">
+        <v>37</v>
+      </c>
+      <c r="I326" t="n">
+        <v>6</v>
+      </c>
+      <c r="J326" t="n">
+        <v>32</v>
+      </c>
+      <c r="K326" t="n">
+        <v>8</v>
+      </c>
+      <c r="L326" t="n">
+        <v>18</v>
+      </c>
+      <c r="M326" t="n">
+        <v>17</v>
+      </c>
+      <c r="N326" t="n">
+        <v>25</v>
+      </c>
+      <c r="O326" t="n">
+        <v>6</v>
+      </c>
+      <c r="P326" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q326" t="n">
+        <v>10</v>
+      </c>
+      <c r="R326" t="n">
+        <v>20</v>
+      </c>
+      <c r="S326" t="n">
+        <v>22</v>
+      </c>
+      <c r="T326" t="n">
+        <v>2</v>
+      </c>
+      <c r="U326" t="inlineStr">
+        <is>
+          <t>2487926</t>
+        </is>
+      </c>
+      <c r="V326" t="n">
+        <v>70</v>
+      </c>
+      <c r="W326" t="n">
+        <v>86.92</v>
+      </c>
+      <c r="X326" t="n">
+        <v>0.6672802577082374</v>
+      </c>
+      <c r="Y326" t="n">
+        <v>69.92</v>
+      </c>
+      <c r="Z326" t="n">
+        <v>82.95194508009153</v>
+      </c>
+      <c r="AA326" t="n">
+        <v>0.9039256198347108</v>
+      </c>
+      <c r="AB326" t="n">
+        <v>100.8064516129032</v>
+      </c>
+      <c r="AC326" t="n">
+        <v>0.3541666666666667</v>
+      </c>
+      <c r="AD326" t="n">
+        <v>0.7575757575757576</v>
+      </c>
+      <c r="AE326" t="n">
+        <v>0.5185185185185185</v>
+      </c>
+      <c r="AF326" t="n">
+        <v>-17.8545065328117</v>
+      </c>
+      <c r="AG326" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="AH326" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="AI326" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>24</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E327" t="n">
+        <v>200</v>
+      </c>
+      <c r="F327" t="n">
+        <v>83</v>
+      </c>
+      <c r="G327" t="n">
+        <v>23</v>
+      </c>
+      <c r="H327" t="n">
+        <v>44</v>
+      </c>
+      <c r="I327" t="n">
+        <v>9</v>
+      </c>
+      <c r="J327" t="n">
+        <v>22</v>
+      </c>
+      <c r="K327" t="n">
+        <v>10</v>
+      </c>
+      <c r="L327" t="n">
+        <v>16</v>
+      </c>
+      <c r="M327" t="n">
+        <v>7</v>
+      </c>
+      <c r="N327" t="n">
+        <v>23</v>
+      </c>
+      <c r="O327" t="n">
+        <v>18</v>
+      </c>
+      <c r="P327" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q327" t="n">
+        <v>13</v>
+      </c>
+      <c r="R327" t="n">
+        <v>18</v>
+      </c>
+      <c r="S327" t="n">
+        <v>18</v>
+      </c>
+      <c r="T327" t="n">
+        <v>2</v>
+      </c>
+      <c r="U327" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="V327" t="n">
+        <v>81</v>
+      </c>
+      <c r="W327" t="n">
+        <v>86.03999999999999</v>
+      </c>
+      <c r="X327" t="n">
+        <v>0.9646675964667597</v>
+      </c>
+      <c r="Y327" t="n">
+        <v>79.03999999999999</v>
+      </c>
+      <c r="Z327" t="n">
+        <v>105.0101214574899</v>
+      </c>
+      <c r="AA327" t="n">
+        <v>0.8996001776988006</v>
+      </c>
+      <c r="AB327" t="n">
+        <v>106.5228826933193</v>
+      </c>
+      <c r="AC327" t="n">
+        <v>0.21875</v>
+      </c>
+      <c r="AD327" t="n">
+        <v>0.6216216216216216</v>
+      </c>
+      <c r="AE327" t="n">
+        <v>0.4347826086956522</v>
+      </c>
+      <c r="AF327" t="n">
+        <v>-1.51276123582943</v>
+      </c>
+      <c r="AG327" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH327" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="AI327" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>24</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="E328" t="n">
+        <v>200</v>
+      </c>
+      <c r="F328" t="n">
+        <v>75</v>
+      </c>
+      <c r="G328" t="n">
+        <v>21</v>
+      </c>
+      <c r="H328" t="n">
+        <v>38</v>
+      </c>
+      <c r="I328" t="n">
+        <v>5</v>
+      </c>
+      <c r="J328" t="n">
+        <v>17</v>
+      </c>
+      <c r="K328" t="n">
+        <v>18</v>
+      </c>
+      <c r="L328" t="n">
+        <v>34</v>
+      </c>
+      <c r="M328" t="n">
+        <v>8</v>
+      </c>
+      <c r="N328" t="n">
+        <v>29</v>
+      </c>
+      <c r="O328" t="n">
+        <v>11</v>
+      </c>
+      <c r="P328" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q328" t="n">
+        <v>12</v>
+      </c>
+      <c r="R328" t="n">
+        <v>20</v>
+      </c>
+      <c r="S328" t="n">
+        <v>28</v>
+      </c>
+      <c r="T328" t="n">
+        <v>4</v>
+      </c>
+      <c r="U328" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="V328" t="n">
+        <v>70</v>
+      </c>
+      <c r="W328" t="n">
+        <v>81.96000000000001</v>
+      </c>
+      <c r="X328" t="n">
+        <v>0.9150805270863835</v>
+      </c>
+      <c r="Y328" t="n">
+        <v>73.96000000000001</v>
+      </c>
+      <c r="Z328" t="n">
+        <v>101.4061654948621</v>
+      </c>
+      <c r="AA328" t="n">
+        <v>0.7651945780498469</v>
+      </c>
+      <c r="AB328" t="n">
+        <v>90.34589571502323</v>
+      </c>
+      <c r="AC328" t="n">
+        <v>0.2285714285714286</v>
+      </c>
+      <c r="AD328" t="n">
+        <v>0.6744186046511628</v>
+      </c>
+      <c r="AE328" t="n">
+        <v>0.4743589743589743</v>
+      </c>
+      <c r="AF328" t="n">
+        <v>11.06026977983885</v>
+      </c>
+      <c r="AG328" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="AH328" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="AI328" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>24</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="E329" t="n">
+        <v>225</v>
+      </c>
+      <c r="F329" t="n">
+        <v>86</v>
+      </c>
+      <c r="G329" t="n">
+        <v>18</v>
+      </c>
+      <c r="H329" t="n">
+        <v>33</v>
+      </c>
+      <c r="I329" t="n">
+        <v>9</v>
+      </c>
+      <c r="J329" t="n">
+        <v>25</v>
+      </c>
+      <c r="K329" t="n">
+        <v>23</v>
+      </c>
+      <c r="L329" t="n">
+        <v>31</v>
+      </c>
+      <c r="M329" t="n">
+        <v>7</v>
+      </c>
+      <c r="N329" t="n">
+        <v>21</v>
+      </c>
+      <c r="O329" t="n">
+        <v>12</v>
+      </c>
+      <c r="P329" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q329" t="n">
+        <v>13</v>
+      </c>
+      <c r="R329" t="n">
+        <v>22</v>
+      </c>
+      <c r="S329" t="n">
+        <v>25</v>
+      </c>
+      <c r="T329" t="n">
+        <v>0</v>
+      </c>
+      <c r="U329" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="V329" t="n">
+        <v>84</v>
+      </c>
+      <c r="W329" t="n">
+        <v>84.64</v>
+      </c>
+      <c r="X329" t="n">
+        <v>1.016068052930057</v>
+      </c>
+      <c r="Y329" t="n">
+        <v>77.64</v>
+      </c>
+      <c r="Z329" t="n">
+        <v>110.7676455435343</v>
+      </c>
+      <c r="AA329" t="n">
+        <v>0.9740259740259739</v>
+      </c>
+      <c r="AB329" t="n">
+        <v>102.1400778210117</v>
+      </c>
+      <c r="AC329" t="n">
+        <v>0.2413793103448276</v>
+      </c>
+      <c r="AD329" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="AE329" t="n">
+        <v>0.5185185185185185</v>
+      </c>
+      <c r="AF329" t="n">
+        <v>8.627567722522599</v>
+      </c>
+      <c r="AG329" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="AH329" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="AI329" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>24</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="E330" t="n">
+        <v>200</v>
+      </c>
+      <c r="F330" t="n">
+        <v>70</v>
+      </c>
+      <c r="G330" t="n">
+        <v>16</v>
+      </c>
+      <c r="H330" t="n">
+        <v>29</v>
+      </c>
+      <c r="I330" t="n">
+        <v>7</v>
+      </c>
+      <c r="J330" t="n">
+        <v>26</v>
+      </c>
+      <c r="K330" t="n">
+        <v>17</v>
+      </c>
+      <c r="L330" t="n">
+        <v>26</v>
+      </c>
+      <c r="M330" t="n">
+        <v>8</v>
+      </c>
+      <c r="N330" t="n">
+        <v>31</v>
+      </c>
+      <c r="O330" t="n">
+        <v>11</v>
+      </c>
+      <c r="P330" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q330" t="n">
+        <v>11</v>
+      </c>
+      <c r="R330" t="n">
+        <v>22</v>
+      </c>
+      <c r="S330" t="n">
+        <v>19</v>
+      </c>
+      <c r="T330" t="n">
+        <v>4</v>
+      </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>2487926</t>
+        </is>
+      </c>
+      <c r="V330" t="n">
+        <v>58</v>
+      </c>
+      <c r="W330" t="n">
+        <v>77.44</v>
+      </c>
+      <c r="X330" t="n">
+        <v>0.9039256198347108</v>
+      </c>
+      <c r="Y330" t="n">
+        <v>69.44</v>
+      </c>
+      <c r="Z330" t="n">
+        <v>100.8064516129032</v>
+      </c>
+      <c r="AA330" t="n">
+        <v>0.6672802577082374</v>
+      </c>
+      <c r="AB330" t="n">
+        <v>82.95194508009153</v>
+      </c>
+      <c r="AC330" t="n">
+        <v>0.2424242424242424</v>
+      </c>
+      <c r="AD330" t="n">
+        <v>0.6458333333333334</v>
+      </c>
+      <c r="AE330" t="n">
+        <v>0.4814814814814815</v>
+      </c>
+      <c r="AF330" t="n">
+        <v>17.8545065328117</v>
+      </c>
+      <c r="AG330" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="AH330" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="AI330" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>24</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="E331" t="n">
+        <v>200</v>
+      </c>
+      <c r="F331" t="n">
+        <v>83</v>
+      </c>
+      <c r="G331" t="n">
+        <v>26</v>
+      </c>
+      <c r="H331" t="n">
+        <v>62</v>
+      </c>
+      <c r="I331" t="n">
+        <v>8</v>
+      </c>
+      <c r="J331" t="n">
+        <v>25</v>
+      </c>
+      <c r="K331" t="n">
+        <v>7</v>
+      </c>
+      <c r="L331" t="n">
+        <v>8</v>
+      </c>
+      <c r="M331" t="n">
+        <v>21</v>
+      </c>
+      <c r="N331" t="n">
+        <v>17</v>
+      </c>
+      <c r="O331" t="n">
+        <v>22</v>
+      </c>
+      <c r="P331" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q331" t="n">
+        <v>10</v>
+      </c>
+      <c r="R331" t="n">
+        <v>23</v>
+      </c>
+      <c r="S331" t="n">
+        <v>16</v>
+      </c>
+      <c r="T331" t="n">
+        <v>2</v>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>2487923</t>
+        </is>
+      </c>
+      <c r="V331" t="n">
+        <v>93</v>
+      </c>
+      <c r="W331" t="n">
+        <v>100.52</v>
+      </c>
+      <c r="X331" t="n">
+        <v>0.8257063270990848</v>
+      </c>
+      <c r="Y331" t="n">
+        <v>79.52</v>
+      </c>
+      <c r="Z331" t="n">
+        <v>104.3762575452716</v>
+      </c>
+      <c r="AA331" t="n">
+        <v>1.157868525896415</v>
+      </c>
+      <c r="AB331" t="n">
+        <v>126.8412438625205</v>
+      </c>
+      <c r="AC331" t="n">
+        <v>0.4772727272727273</v>
+      </c>
+      <c r="AD331" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="AE331" t="n">
+        <v>0.5588235294117647</v>
+      </c>
+      <c r="AF331" t="n">
+        <v>-22.46498631724883</v>
+      </c>
+      <c r="AG331" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="AH331" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="AI331" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B332" t="n">
+        <v>24</v>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="E332" t="n">
+        <v>200</v>
+      </c>
+      <c r="F332" t="n">
+        <v>81</v>
+      </c>
+      <c r="G332" t="n">
+        <v>21</v>
+      </c>
+      <c r="H332" t="n">
+        <v>45</v>
+      </c>
+      <c r="I332" t="n">
+        <v>10</v>
+      </c>
+      <c r="J332" t="n">
+        <v>23</v>
+      </c>
+      <c r="K332" t="n">
+        <v>9</v>
+      </c>
+      <c r="L332" t="n">
+        <v>16</v>
+      </c>
+      <c r="M332" t="n">
+        <v>14</v>
+      </c>
+      <c r="N332" t="n">
+        <v>25</v>
+      </c>
+      <c r="O332" t="n">
+        <v>19</v>
+      </c>
+      <c r="P332" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q332" t="n">
+        <v>15</v>
+      </c>
+      <c r="R332" t="n">
+        <v>18</v>
+      </c>
+      <c r="S332" t="n">
+        <v>18</v>
+      </c>
+      <c r="T332" t="n">
+        <v>3</v>
+      </c>
+      <c r="U332" t="inlineStr">
+        <is>
+          <t>2487924</t>
+        </is>
+      </c>
+      <c r="V332" t="n">
+        <v>83</v>
+      </c>
+      <c r="W332" t="n">
+        <v>90.03999999999999</v>
+      </c>
+      <c r="X332" t="n">
+        <v>0.8996001776988006</v>
+      </c>
+      <c r="Y332" t="n">
+        <v>76.03999999999999</v>
+      </c>
+      <c r="Z332" t="n">
+        <v>106.5228826933193</v>
+      </c>
+      <c r="AA332" t="n">
+        <v>0.9646675964667597</v>
+      </c>
+      <c r="AB332" t="n">
+        <v>105.0101214574899</v>
+      </c>
+      <c r="AC332" t="n">
+        <v>0.3783783783783784</v>
+      </c>
+      <c r="AD332" t="n">
+        <v>0.78125</v>
+      </c>
+      <c r="AE332" t="n">
+        <v>0.5652173913043478</v>
+      </c>
+      <c r="AF332" t="n">
+        <v>1.51276123582943</v>
+      </c>
+      <c r="AG332" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH332" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="AI332" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B333" t="n">
+        <v>24</v>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="E333" t="n">
+        <v>200</v>
+      </c>
+      <c r="F333" t="n">
+        <v>79</v>
+      </c>
+      <c r="G333" t="n">
+        <v>15</v>
+      </c>
+      <c r="H333" t="n">
+        <v>34</v>
+      </c>
+      <c r="I333" t="n">
+        <v>11</v>
+      </c>
+      <c r="J333" t="n">
+        <v>30</v>
+      </c>
+      <c r="K333" t="n">
+        <v>16</v>
+      </c>
+      <c r="L333" t="n">
+        <v>22</v>
+      </c>
+      <c r="M333" t="n">
+        <v>10</v>
+      </c>
+      <c r="N333" t="n">
+        <v>18</v>
+      </c>
+      <c r="O333" t="n">
+        <v>8</v>
+      </c>
+      <c r="P333" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q333" t="n">
+        <v>10</v>
+      </c>
+      <c r="R333" t="n">
+        <v>18</v>
+      </c>
+      <c r="S333" t="n">
+        <v>24</v>
+      </c>
+      <c r="T333" t="n">
+        <v>1</v>
+      </c>
+      <c r="U333" t="inlineStr">
+        <is>
+          <t>2487921</t>
+        </is>
+      </c>
+      <c r="V333" t="n">
+        <v>81</v>
+      </c>
+      <c r="W333" t="n">
+        <v>83.68000000000001</v>
+      </c>
+      <c r="X333" t="n">
+        <v>0.9440726577437858</v>
+      </c>
+      <c r="Y333" t="n">
+        <v>73.68000000000001</v>
+      </c>
+      <c r="Z333" t="n">
+        <v>107.2204125950054</v>
+      </c>
+      <c r="AA333" t="n">
+        <v>1.09875203472599</v>
+      </c>
+      <c r="AB333" t="n">
+        <v>121.4028776978417</v>
+      </c>
+      <c r="AC333" t="n">
+        <v>0.3125</v>
+      </c>
+      <c r="AD333" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="AE333" t="n">
+        <v>0.4912280701754386</v>
+      </c>
+      <c r="AF333" t="n">
+        <v>-14.18246510283632</v>
+      </c>
+      <c r="AG333" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="AH333" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="AI333" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B334" t="n">
+        <v>24</v>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="E334" t="n">
+        <v>200</v>
+      </c>
+      <c r="F334" t="n">
+        <v>84</v>
+      </c>
+      <c r="G334" t="n">
+        <v>18</v>
+      </c>
+      <c r="H334" t="n">
+        <v>36</v>
+      </c>
+      <c r="I334" t="n">
+        <v>12</v>
+      </c>
+      <c r="J334" t="n">
+        <v>30</v>
+      </c>
+      <c r="K334" t="n">
+        <v>12</v>
+      </c>
+      <c r="L334" t="n">
+        <v>22</v>
+      </c>
+      <c r="M334" t="n">
+        <v>12</v>
+      </c>
+      <c r="N334" t="n">
+        <v>18</v>
+      </c>
+      <c r="O334" t="n">
+        <v>17</v>
+      </c>
+      <c r="P334" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q334" t="n">
+        <v>11</v>
+      </c>
+      <c r="R334" t="n">
+        <v>33</v>
+      </c>
+      <c r="S334" t="n">
+        <v>19</v>
+      </c>
+      <c r="T334" t="n">
+        <v>2</v>
+      </c>
+      <c r="U334" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="V334" t="n">
+        <v>91</v>
+      </c>
+      <c r="W334" t="n">
+        <v>86.68000000000001</v>
+      </c>
+      <c r="X334" t="n">
+        <v>0.9690816797415781</v>
+      </c>
+      <c r="Y334" t="n">
+        <v>74.68000000000001</v>
+      </c>
+      <c r="Z334" t="n">
+        <v>112.4799143010177</v>
+      </c>
+      <c r="AA334" t="n">
+        <v>1.082817705854355</v>
+      </c>
+      <c r="AB334" t="n">
+        <v>122.9065370070232</v>
+      </c>
+      <c r="AC334" t="n">
+        <v>0.3428571428571429</v>
+      </c>
+      <c r="AD334" t="n">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="AE334" t="n">
+        <v>0.4761904761904762</v>
+      </c>
+      <c r="AF334" t="n">
+        <v>-10.42662270600557</v>
+      </c>
+      <c r="AG334" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="AH334" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="AI334" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B335" t="n">
+        <v>24</v>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E335" t="n">
+        <v>225</v>
+      </c>
+      <c r="F335" t="n">
+        <v>84</v>
+      </c>
+      <c r="G335" t="n">
+        <v>14</v>
+      </c>
+      <c r="H335" t="n">
+        <v>31</v>
+      </c>
+      <c r="I335" t="n">
+        <v>13</v>
+      </c>
+      <c r="J335" t="n">
+        <v>26</v>
+      </c>
+      <c r="K335" t="n">
+        <v>17</v>
+      </c>
+      <c r="L335" t="n">
+        <v>21</v>
+      </c>
+      <c r="M335" t="n">
+        <v>4</v>
+      </c>
+      <c r="N335" t="n">
+        <v>22</v>
+      </c>
+      <c r="O335" t="n">
+        <v>16</v>
+      </c>
+      <c r="P335" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q335" t="n">
+        <v>20</v>
+      </c>
+      <c r="R335" t="n">
+        <v>25</v>
+      </c>
+      <c r="S335" t="n">
+        <v>22</v>
+      </c>
+      <c r="T335" t="n">
+        <v>1</v>
+      </c>
+      <c r="U335" t="inlineStr">
+        <is>
+          <t>2487922</t>
+        </is>
+      </c>
+      <c r="V335" t="n">
+        <v>86</v>
+      </c>
+      <c r="W335" t="n">
+        <v>86.24000000000001</v>
+      </c>
+      <c r="X335" t="n">
+        <v>0.9740259740259739</v>
+      </c>
+      <c r="Y335" t="n">
+        <v>82.24000000000001</v>
+      </c>
+      <c r="Z335" t="n">
+        <v>102.1400778210117</v>
+      </c>
+      <c r="AA335" t="n">
+        <v>1.016068052930057</v>
+      </c>
+      <c r="AB335" t="n">
+        <v>110.7676455435343</v>
+      </c>
+      <c r="AC335" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="AD335" t="n">
+        <v>0.7586206896551724</v>
+      </c>
+      <c r="AE335" t="n">
+        <v>0.4814814814814815</v>
+      </c>
+      <c r="AF335" t="n">
+        <v>-8.627567722522599</v>
+      </c>
+      <c r="AG335" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="AH335" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="AI335" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B336" t="n">
+        <v>24</v>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="E336" t="n">
+        <v>200</v>
+      </c>
+      <c r="F336" t="n">
+        <v>70</v>
+      </c>
+      <c r="G336" t="n">
+        <v>15</v>
+      </c>
+      <c r="H336" t="n">
+        <v>38</v>
+      </c>
+      <c r="I336" t="n">
+        <v>10</v>
+      </c>
+      <c r="J336" t="n">
+        <v>32</v>
+      </c>
+      <c r="K336" t="n">
+        <v>10</v>
+      </c>
+      <c r="L336" t="n">
+        <v>17</v>
+      </c>
+      <c r="M336" t="n">
+        <v>14</v>
+      </c>
+      <c r="N336" t="n">
+        <v>27</v>
+      </c>
+      <c r="O336" t="n">
+        <v>9</v>
+      </c>
+      <c r="P336" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q336" t="n">
+        <v>14</v>
+      </c>
+      <c r="R336" t="n">
+        <v>28</v>
+      </c>
+      <c r="S336" t="n">
+        <v>20</v>
+      </c>
+      <c r="T336" t="n">
+        <v>3</v>
+      </c>
+      <c r="U336" t="inlineStr">
+        <is>
+          <t>2487925</t>
+        </is>
+      </c>
+      <c r="V336" t="n">
+        <v>75</v>
+      </c>
+      <c r="W336" t="n">
+        <v>91.48</v>
+      </c>
+      <c r="X336" t="n">
+        <v>0.7651945780498469</v>
+      </c>
+      <c r="Y336" t="n">
+        <v>77.48</v>
+      </c>
+      <c r="Z336" t="n">
+        <v>90.34589571502323</v>
+      </c>
+      <c r="AA336" t="n">
+        <v>0.9150805270863835</v>
+      </c>
+      <c r="AB336" t="n">
+        <v>101.4061654948621</v>
+      </c>
+      <c r="AC336" t="n">
+        <v>0.3255813953488372</v>
+      </c>
+      <c r="AD336" t="n">
+        <v>0.7714285714285715</v>
+      </c>
+      <c r="AE336" t="n">
+        <v>0.5256410256410257</v>
+      </c>
+      <c r="AF336" t="n">
+        <v>-11.06026977983885</v>
+      </c>
+      <c r="AG336" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="AH336" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="AI336" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B337" t="n">
+        <v>24</v>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="E337" t="n">
+        <v>200</v>
+      </c>
+      <c r="F337" t="n">
+        <v>91</v>
+      </c>
+      <c r="G337" t="n">
+        <v>15</v>
+      </c>
+      <c r="H337" t="n">
+        <v>28</v>
+      </c>
+      <c r="I337" t="n">
+        <v>10</v>
+      </c>
+      <c r="J337" t="n">
+        <v>28</v>
+      </c>
+      <c r="K337" t="n">
+        <v>31</v>
+      </c>
+      <c r="L337" t="n">
+        <v>41</v>
+      </c>
+      <c r="M337" t="n">
+        <v>10</v>
+      </c>
+      <c r="N337" t="n">
+        <v>23</v>
+      </c>
+      <c r="O337" t="n">
+        <v>15</v>
+      </c>
+      <c r="P337" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q337" t="n">
+        <v>10</v>
+      </c>
+      <c r="R337" t="n">
+        <v>19</v>
+      </c>
+      <c r="S337" t="n">
+        <v>31</v>
+      </c>
+      <c r="T337" t="n">
+        <v>3</v>
+      </c>
+      <c r="U337" t="inlineStr">
+        <is>
+          <t>2487920</t>
+        </is>
+      </c>
+      <c r="V337" t="n">
+        <v>84</v>
+      </c>
+      <c r="W337" t="n">
+        <v>84.03999999999999</v>
+      </c>
+      <c r="X337" t="n">
+        <v>1.082817705854355</v>
+      </c>
+      <c r="Y337" t="n">
+        <v>74.03999999999999</v>
+      </c>
+      <c r="Z337" t="n">
+        <v>122.9065370070232</v>
+      </c>
+      <c r="AA337" t="n">
+        <v>0.9690816797415781</v>
+      </c>
+      <c r="AB337" t="n">
+        <v>112.4799143010177</v>
+      </c>
+      <c r="AC337" t="n">
+        <v>0.3571428571428572</v>
+      </c>
+      <c r="AD337" t="n">
+        <v>0.6571428571428571</v>
+      </c>
+      <c r="AE337" t="n">
+        <v>0.5238095238095238</v>
+      </c>
+      <c r="AF337" t="n">
+        <v>10.42662270600557</v>
+      </c>
+      <c r="AG337" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="AH337" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="AI337" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B338" t="n">
+        <v>25</v>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="E338" t="n">
+        <v>200</v>
+      </c>
+      <c r="F338" t="n">
+        <v>102</v>
+      </c>
+      <c r="G338" t="n">
+        <v>22</v>
+      </c>
+      <c r="H338" t="n">
+        <v>29</v>
+      </c>
+      <c r="I338" t="n">
+        <v>17</v>
+      </c>
+      <c r="J338" t="n">
+        <v>38</v>
+      </c>
+      <c r="K338" t="n">
+        <v>7</v>
+      </c>
+      <c r="L338" t="n">
+        <v>9</v>
+      </c>
+      <c r="M338" t="n">
+        <v>8</v>
+      </c>
+      <c r="N338" t="n">
+        <v>26</v>
+      </c>
+      <c r="O338" t="n">
+        <v>19</v>
+      </c>
+      <c r="P338" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q338" t="n">
+        <v>10</v>
+      </c>
+      <c r="R338" t="n">
+        <v>21</v>
+      </c>
+      <c r="S338" t="n">
+        <v>11</v>
+      </c>
+      <c r="T338" t="n">
+        <v>2</v>
+      </c>
+      <c r="U338" t="inlineStr">
+        <is>
+          <t>2487933</t>
+        </is>
+      </c>
+      <c r="V338" t="n">
+        <v>71</v>
+      </c>
+      <c r="W338" t="n">
+        <v>80.96000000000001</v>
+      </c>
+      <c r="X338" t="n">
+        <v>1.259881422924901</v>
+      </c>
+      <c r="Y338" t="n">
+        <v>72.96000000000001</v>
+      </c>
+      <c r="Z338" t="n">
+        <v>139.8026315789473</v>
+      </c>
+      <c r="AA338" t="n">
+        <v>0.8919597989949749</v>
+      </c>
+      <c r="AB338" t="n">
+        <v>102.0114942528736</v>
+      </c>
+      <c r="AC338" t="n">
+        <v>0.3809523809523809</v>
+      </c>
+      <c r="AD338" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="AE338" t="n">
+        <v>0.5964912280701754</v>
+      </c>
+      <c r="AF338" t="n">
+        <v>37.79113732607377</v>
+      </c>
+      <c r="AG338" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="AH338" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="AI338" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B339" t="n">
+        <v>25</v>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E339" t="n">
+        <v>200</v>
+      </c>
+      <c r="F339" t="n">
+        <v>87</v>
+      </c>
+      <c r="G339" t="n">
+        <v>18</v>
+      </c>
+      <c r="H339" t="n">
+        <v>31</v>
+      </c>
+      <c r="I339" t="n">
+        <v>7</v>
+      </c>
+      <c r="J339" t="n">
+        <v>20</v>
+      </c>
+      <c r="K339" t="n">
+        <v>30</v>
+      </c>
+      <c r="L339" t="n">
+        <v>43</v>
+      </c>
+      <c r="M339" t="n">
+        <v>3</v>
+      </c>
+      <c r="N339" t="n">
+        <v>34</v>
+      </c>
+      <c r="O339" t="n">
+        <v>17</v>
+      </c>
+      <c r="P339" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q339" t="n">
+        <v>11</v>
+      </c>
+      <c r="R339" t="n">
+        <v>20</v>
+      </c>
+      <c r="S339" t="n">
+        <v>30</v>
+      </c>
+      <c r="T339" t="n">
+        <v>1</v>
+      </c>
+      <c r="U339" t="inlineStr">
+        <is>
+          <t>2487931</t>
+        </is>
+      </c>
+      <c r="V339" t="n">
+        <v>75</v>
+      </c>
+      <c r="W339" t="n">
+        <v>80.92</v>
+      </c>
+      <c r="X339" t="n">
+        <v>1.075135936727632</v>
+      </c>
+      <c r="Y339" t="n">
+        <v>77.92</v>
+      </c>
+      <c r="Z339" t="n">
+        <v>111.652977412731</v>
+      </c>
+      <c r="AA339" t="n">
+        <v>0.8971291866028709</v>
+      </c>
+      <c r="AB339" t="n">
+        <v>96.64948453608248</v>
+      </c>
+      <c r="AC339" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="AD339" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="AE339" t="n">
+        <v>0.578125</v>
+      </c>
+      <c r="AF339" t="n">
+        <v>15.00349287664852</v>
+      </c>
+      <c r="AG339" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="AH339" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="AI339" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B340" t="n">
+        <v>25</v>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="E340" t="n">
+        <v>200</v>
+      </c>
+      <c r="F340" t="n">
+        <v>98</v>
+      </c>
+      <c r="G340" t="n">
+        <v>25</v>
+      </c>
+      <c r="H340" t="n">
+        <v>40</v>
+      </c>
+      <c r="I340" t="n">
+        <v>6</v>
+      </c>
+      <c r="J340" t="n">
+        <v>29</v>
+      </c>
+      <c r="K340" t="n">
+        <v>30</v>
+      </c>
+      <c r="L340" t="n">
+        <v>39</v>
+      </c>
+      <c r="M340" t="n">
+        <v>12</v>
+      </c>
+      <c r="N340" t="n">
+        <v>26</v>
+      </c>
+      <c r="O340" t="n">
+        <v>6</v>
+      </c>
+      <c r="P340" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q340" t="n">
+        <v>8</v>
+      </c>
+      <c r="R340" t="n">
+        <v>25</v>
+      </c>
+      <c r="S340" t="n">
+        <v>28</v>
+      </c>
+      <c r="T340" t="n">
+        <v>0</v>
+      </c>
+      <c r="U340" t="inlineStr">
+        <is>
+          <t>2487927</t>
+        </is>
+      </c>
+      <c r="V340" t="n">
+        <v>85</v>
+      </c>
+      <c r="W340" t="n">
+        <v>94.16</v>
+      </c>
+      <c r="X340" t="n">
+        <v>1.040781648258284</v>
+      </c>
+      <c r="Y340" t="n">
+        <v>82.16</v>
+      </c>
+      <c r="Z340" t="n">
+        <v>119.2794547224927</v>
+      </c>
+      <c r="AA340" t="n">
+        <v>0.9948501872659177</v>
+      </c>
+      <c r="AB340" t="n">
+        <v>106.9989929506546</v>
+      </c>
+      <c r="AC340" t="n">
+        <v>0.3243243243243243</v>
+      </c>
+      <c r="AD340" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AE340" t="n">
+        <v>0.5507246376811594</v>
+      </c>
+      <c r="AF340" t="n">
+        <v>12.28046177183812</v>
+      </c>
+      <c r="AG340" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="AH340" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="AI340" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B341" t="n">
+        <v>25</v>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="E341" t="n">
+        <v>200</v>
+      </c>
+      <c r="F341" t="n">
+        <v>68</v>
+      </c>
+      <c r="G341" t="n">
+        <v>24</v>
+      </c>
+      <c r="H341" t="n">
+        <v>43</v>
+      </c>
+      <c r="I341" t="n">
+        <v>0</v>
+      </c>
+      <c r="J341" t="n">
+        <v>13</v>
+      </c>
+      <c r="K341" t="n">
+        <v>20</v>
+      </c>
+      <c r="L341" t="n">
+        <v>27</v>
+      </c>
+      <c r="M341" t="n">
+        <v>6</v>
+      </c>
+      <c r="N341" t="n">
+        <v>23</v>
+      </c>
+      <c r="O341" t="n">
+        <v>17</v>
+      </c>
+      <c r="P341" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q341" t="n">
+        <v>13</v>
+      </c>
+      <c r="R341" t="n">
+        <v>21</v>
+      </c>
+      <c r="S341" t="n">
+        <v>24</v>
+      </c>
+      <c r="T341" t="n">
+        <v>2</v>
+      </c>
+      <c r="U341" t="inlineStr">
+        <is>
+          <t>2487929</t>
+        </is>
+      </c>
+      <c r="V341" t="n">
+        <v>85</v>
+      </c>
+      <c r="W341" t="n">
+        <v>80.88</v>
+      </c>
+      <c r="X341" t="n">
+        <v>0.8407517309594461</v>
+      </c>
+      <c r="Y341" t="n">
+        <v>74.88</v>
+      </c>
+      <c r="Z341" t="n">
+        <v>90.81196581196582</v>
+      </c>
+      <c r="AA341" t="n">
+        <v>0.9792626728110599</v>
+      </c>
+      <c r="AB341" t="n">
+        <v>110.6770833333333</v>
+      </c>
+      <c r="AC341" t="n">
+        <v>0.1818181818181818</v>
+      </c>
+      <c r="AD341" t="n">
+        <v>0.696969696969697</v>
+      </c>
+      <c r="AE341" t="n">
+        <v>0.4393939393939394</v>
+      </c>
+      <c r="AF341" t="n">
+        <v>-19.86511752136752</v>
+      </c>
+      <c r="AG341" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="AH341" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="AI341" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B342" t="n">
+        <v>25</v>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="E342" t="n">
+        <v>200</v>
+      </c>
+      <c r="F342" t="n">
+        <v>66</v>
+      </c>
+      <c r="G342" t="n">
+        <v>7</v>
+      </c>
+      <c r="H342" t="n">
+        <v>25</v>
+      </c>
+      <c r="I342" t="n">
+        <v>13</v>
+      </c>
+      <c r="J342" t="n">
+        <v>31</v>
+      </c>
+      <c r="K342" t="n">
+        <v>13</v>
+      </c>
+      <c r="L342" t="n">
+        <v>22</v>
+      </c>
+      <c r="M342" t="n">
+        <v>6</v>
+      </c>
+      <c r="N342" t="n">
+        <v>25</v>
+      </c>
+      <c r="O342" t="n">
+        <v>12</v>
+      </c>
+      <c r="P342" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q342" t="n">
+        <v>13</v>
+      </c>
+      <c r="R342" t="n">
+        <v>24</v>
+      </c>
+      <c r="S342" t="n">
+        <v>20</v>
+      </c>
+      <c r="T342" t="n">
+        <v>1</v>
+      </c>
+      <c r="U342" t="inlineStr">
+        <is>
+          <t>2487928</t>
+        </is>
+      </c>
+      <c r="V342" t="n">
+        <v>64</v>
+      </c>
+      <c r="W342" t="n">
+        <v>78.68000000000001</v>
+      </c>
+      <c r="X342" t="n">
+        <v>0.838840874428063</v>
+      </c>
+      <c r="Y342" t="n">
+        <v>72.68000000000001</v>
+      </c>
+      <c r="Z342" t="n">
+        <v>90.80902586681341</v>
+      </c>
+      <c r="AA342" t="n">
+        <v>0.7403979639055993</v>
+      </c>
+      <c r="AB342" t="n">
+        <v>83.7257980115123</v>
+      </c>
+      <c r="AC342" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="AD342" t="n">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="AE342" t="n">
+        <v>0.4626865671641791</v>
+      </c>
+      <c r="AF342" t="n">
+        <v>7.083227855301118</v>
+      </c>
+      <c r="AG342" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="AH342" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="AI342" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B343" t="n">
+        <v>25</v>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="E343" t="n">
+        <v>200</v>
+      </c>
+      <c r="F343" t="n">
+        <v>75</v>
+      </c>
+      <c r="G343" t="n">
+        <v>16</v>
+      </c>
+      <c r="H343" t="n">
+        <v>31</v>
+      </c>
+      <c r="I343" t="n">
+        <v>11</v>
+      </c>
+      <c r="J343" t="n">
+        <v>37</v>
+      </c>
+      <c r="K343" t="n">
+        <v>10</v>
+      </c>
+      <c r="L343" t="n">
+        <v>15</v>
+      </c>
+      <c r="M343" t="n">
+        <v>6</v>
+      </c>
+      <c r="N343" t="n">
+        <v>21</v>
+      </c>
+      <c r="O343" t="n">
+        <v>11</v>
+      </c>
+      <c r="P343" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q343" t="n">
+        <v>9</v>
+      </c>
+      <c r="R343" t="n">
+        <v>31</v>
+      </c>
+      <c r="S343" t="n">
+        <v>20</v>
+      </c>
+      <c r="T343" t="n">
+        <v>2</v>
+      </c>
+      <c r="U343" t="inlineStr">
+        <is>
+          <t>2487931</t>
+        </is>
+      </c>
+      <c r="V343" t="n">
+        <v>87</v>
+      </c>
+      <c r="W343" t="n">
+        <v>83.59999999999999</v>
+      </c>
+      <c r="X343" t="n">
+        <v>0.8971291866028709</v>
+      </c>
+      <c r="Y343" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="Z343" t="n">
+        <v>96.64948453608248</v>
+      </c>
+      <c r="AA343" t="n">
+        <v>1.075135936727632</v>
+      </c>
+      <c r="AB343" t="n">
+        <v>111.652977412731</v>
+      </c>
+      <c r="AC343" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AD343" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="AE343" t="n">
+        <v>0.421875</v>
+      </c>
+      <c r="AF343" t="n">
+        <v>-15.00349287664852</v>
+      </c>
+      <c r="AG343" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="AH343" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="AI343" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B344" t="n">
+        <v>25</v>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="E344" t="n">
+        <v>200</v>
+      </c>
+      <c r="F344" t="n">
+        <v>64</v>
+      </c>
+      <c r="G344" t="n">
+        <v>14</v>
+      </c>
+      <c r="H344" t="n">
+        <v>38</v>
+      </c>
+      <c r="I344" t="n">
+        <v>6</v>
+      </c>
+      <c r="J344" t="n">
+        <v>21</v>
+      </c>
+      <c r="K344" t="n">
+        <v>18</v>
+      </c>
+      <c r="L344" t="n">
+        <v>26</v>
+      </c>
+      <c r="M344" t="n">
+        <v>10</v>
+      </c>
+      <c r="N344" t="n">
+        <v>26</v>
+      </c>
+      <c r="O344" t="n">
+        <v>6</v>
+      </c>
+      <c r="P344" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q344" t="n">
+        <v>16</v>
+      </c>
+      <c r="R344" t="n">
+        <v>20</v>
+      </c>
+      <c r="S344" t="n">
+        <v>23</v>
+      </c>
+      <c r="T344" t="n">
+        <v>0</v>
+      </c>
+      <c r="U344" t="inlineStr">
+        <is>
+          <t>2487928</t>
+        </is>
+      </c>
+      <c r="V344" t="n">
+        <v>66</v>
+      </c>
+      <c r="W344" t="n">
+        <v>86.44</v>
+      </c>
+      <c r="X344" t="n">
+        <v>0.7403979639055993</v>
+      </c>
+      <c r="Y344" t="n">
+        <v>76.44</v>
+      </c>
+      <c r="Z344" t="n">
+        <v>83.7257980115123</v>
+      </c>
+      <c r="AA344" t="n">
+        <v>0.838840874428063</v>
+      </c>
+      <c r="AB344" t="n">
+        <v>90.80902586681341</v>
+      </c>
+      <c r="AC344" t="n">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="AD344" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="AE344" t="n">
+        <v>0.5373134328358209</v>
+      </c>
+      <c r="AF344" t="n">
+        <v>-7.083227855301118</v>
+      </c>
+      <c r="AG344" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="AH344" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="AI344" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B345" t="n">
+        <v>25</v>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E345" t="n">
+        <v>200</v>
+      </c>
+      <c r="F345" t="n">
+        <v>85</v>
+      </c>
+      <c r="G345" t="n">
+        <v>26</v>
+      </c>
+      <c r="H345" t="n">
+        <v>45</v>
+      </c>
+      <c r="I345" t="n">
+        <v>8</v>
+      </c>
+      <c r="J345" t="n">
+        <v>24</v>
+      </c>
+      <c r="K345" t="n">
+        <v>9</v>
+      </c>
+      <c r="L345" t="n">
+        <v>17</v>
+      </c>
+      <c r="M345" t="n">
+        <v>16</v>
+      </c>
+      <c r="N345" t="n">
+        <v>29</v>
+      </c>
+      <c r="O345" t="n">
+        <v>18</v>
+      </c>
+      <c r="P345" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q345" t="n">
+        <v>22</v>
+      </c>
+      <c r="R345" t="n">
+        <v>22</v>
+      </c>
+      <c r="S345" t="n">
+        <v>17</v>
+      </c>
+      <c r="T345" t="n">
+        <v>4</v>
+      </c>
+      <c r="U345" t="inlineStr">
+        <is>
+          <t>2487930</t>
+        </is>
+      </c>
+      <c r="V345" t="n">
+        <v>73</v>
+      </c>
+      <c r="W345" t="n">
+        <v>98.48</v>
+      </c>
+      <c r="X345" t="n">
+        <v>0.8631194151096669</v>
+      </c>
+      <c r="Y345" t="n">
+        <v>82.48</v>
+      </c>
+      <c r="Z345" t="n">
+        <v>103.0552861299709</v>
+      </c>
+      <c r="AA345" t="n">
+        <v>0.7674516400336416</v>
+      </c>
+      <c r="AB345" t="n">
+        <v>85.76127819548871</v>
+      </c>
+      <c r="AC345" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="AD345" t="n">
+        <v>0.7435897435897436</v>
+      </c>
+      <c r="AE345" t="n">
+        <v>0.6164383561643836</v>
+      </c>
+      <c r="AF345" t="n">
+        <v>17.29400793448218</v>
+      </c>
+      <c r="AG345" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="AH345" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI345" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B346" t="n">
+        <v>25</v>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="E346" t="n">
+        <v>200</v>
+      </c>
+      <c r="F346" t="n">
+        <v>73</v>
+      </c>
+      <c r="G346" t="n">
+        <v>21</v>
+      </c>
+      <c r="H346" t="n">
+        <v>42</v>
+      </c>
+      <c r="I346" t="n">
+        <v>6</v>
+      </c>
+      <c r="J346" t="n">
+        <v>24</v>
+      </c>
+      <c r="K346" t="n">
+        <v>13</v>
+      </c>
+      <c r="L346" t="n">
+        <v>23</v>
+      </c>
+      <c r="M346" t="n">
+        <v>10</v>
+      </c>
+      <c r="N346" t="n">
+        <v>18</v>
+      </c>
+      <c r="O346" t="n">
+        <v>12</v>
+      </c>
+      <c r="P346" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q346" t="n">
+        <v>19</v>
+      </c>
+      <c r="R346" t="n">
+        <v>17</v>
+      </c>
+      <c r="S346" t="n">
+        <v>22</v>
+      </c>
+      <c r="T346" t="n">
+        <v>4</v>
+      </c>
+      <c r="U346" t="inlineStr">
+        <is>
+          <t>2487930</t>
+        </is>
+      </c>
+      <c r="V346" t="n">
+        <v>85</v>
+      </c>
+      <c r="W346" t="n">
+        <v>95.12</v>
+      </c>
+      <c r="X346" t="n">
+        <v>0.7674516400336416</v>
+      </c>
+      <c r="Y346" t="n">
+        <v>85.12</v>
+      </c>
+      <c r="Z346" t="n">
+        <v>85.76127819548871</v>
+      </c>
+      <c r="AA346" t="n">
+        <v>0.8631194151096669</v>
+      </c>
+      <c r="AB346" t="n">
+        <v>103.0552861299709</v>
+      </c>
+      <c r="AC346" t="n">
+        <v>0.2564102564102564</v>
+      </c>
+      <c r="AD346" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="AE346" t="n">
+        <v>0.3835616438356164</v>
+      </c>
+      <c r="AF346" t="n">
+        <v>-17.29400793448218</v>
+      </c>
+      <c r="AG346" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="AH346" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AI346" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B347" t="n">
+        <v>25</v>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="E347" t="n">
+        <v>200</v>
+      </c>
+      <c r="F347" t="n">
+        <v>70</v>
+      </c>
+      <c r="G347" t="n">
+        <v>18</v>
+      </c>
+      <c r="H347" t="n">
+        <v>40</v>
+      </c>
+      <c r="I347" t="n">
+        <v>9</v>
+      </c>
+      <c r="J347" t="n">
+        <v>25</v>
+      </c>
+      <c r="K347" t="n">
+        <v>7</v>
+      </c>
+      <c r="L347" t="n">
+        <v>7</v>
+      </c>
+      <c r="M347" t="n">
+        <v>11</v>
+      </c>
+      <c r="N347" t="n">
+        <v>21</v>
+      </c>
+      <c r="O347" t="n">
+        <v>18</v>
+      </c>
+      <c r="P347" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q347" t="n">
+        <v>10</v>
+      </c>
+      <c r="R347" t="n">
+        <v>16</v>
+      </c>
+      <c r="S347" t="n">
+        <v>16</v>
+      </c>
+      <c r="T347" t="n">
+        <v>0</v>
+      </c>
+      <c r="U347" t="inlineStr">
+        <is>
+          <t>2487932</t>
+        </is>
+      </c>
+      <c r="V347" t="n">
+        <v>68</v>
+      </c>
+      <c r="W347" t="n">
+        <v>78.08</v>
+      </c>
+      <c r="X347" t="n">
+        <v>0.896516393442623</v>
+      </c>
+      <c r="Y347" t="n">
+        <v>67.08</v>
+      </c>
+      <c r="Z347" t="n">
+        <v>104.3530113297555</v>
+      </c>
+      <c r="AA347" t="n">
+        <v>0.8966244725738396</v>
+      </c>
+      <c r="AB347" t="n">
+        <v>103.2806804374241</v>
+      </c>
+      <c r="AC347" t="n">
+        <v>0.3235294117647059</v>
+      </c>
+      <c r="AD347" t="n">
+        <v>0.6774193548387096</v>
+      </c>
+      <c r="AE347" t="n">
+        <v>0.4923076923076923</v>
+      </c>
+      <c r="AF347" t="n">
+        <v>1.072330892331465</v>
+      </c>
+      <c r="AG347" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="AH347" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="AI347" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B348" t="n">
+        <v>25</v>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="E348" t="n">
+        <v>200</v>
+      </c>
+      <c r="F348" t="n">
+        <v>71</v>
+      </c>
+      <c r="G348" t="n">
+        <v>16</v>
+      </c>
+      <c r="H348" t="n">
+        <v>37</v>
+      </c>
+      <c r="I348" t="n">
+        <v>9</v>
+      </c>
+      <c r="J348" t="n">
+        <v>25</v>
+      </c>
+      <c r="K348" t="n">
+        <v>12</v>
+      </c>
+      <c r="L348" t="n">
+        <v>15</v>
+      </c>
+      <c r="M348" t="n">
+        <v>10</v>
+      </c>
+      <c r="N348" t="n">
+        <v>13</v>
+      </c>
+      <c r="O348" t="n">
+        <v>9</v>
+      </c>
+      <c r="P348" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q348" t="n">
+        <v>11</v>
+      </c>
+      <c r="R348" t="n">
+        <v>11</v>
+      </c>
+      <c r="S348" t="n">
+        <v>21</v>
+      </c>
+      <c r="T348" t="n">
+        <v>0</v>
+      </c>
+      <c r="U348" t="inlineStr">
+        <is>
+          <t>2487933</t>
+        </is>
+      </c>
+      <c r="V348" t="n">
+        <v>102</v>
+      </c>
+      <c r="W348" t="n">
+        <v>79.59999999999999</v>
+      </c>
+      <c r="X348" t="n">
+        <v>0.8919597989949749</v>
+      </c>
+      <c r="Y348" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="Z348" t="n">
+        <v>102.0114942528736</v>
+      </c>
+      <c r="AA348" t="n">
+        <v>1.259881422924901</v>
+      </c>
+      <c r="AB348" t="n">
+        <v>139.8026315789473</v>
+      </c>
+      <c r="AC348" t="n">
+        <v>0.2777777777777778</v>
+      </c>
+      <c r="AD348" t="n">
+        <v>0.6190476190476191</v>
+      </c>
+      <c r="AE348" t="n">
+        <v>0.4035087719298245</v>
+      </c>
+      <c r="AF348" t="n">
+        <v>-37.79113732607377</v>
+      </c>
+      <c r="AG348" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="AH348" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="AI348" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B349" t="n">
+        <v>25</v>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E349" t="n">
+        <v>200</v>
+      </c>
+      <c r="F349" t="n">
+        <v>68</v>
+      </c>
+      <c r="G349" t="n">
+        <v>20</v>
+      </c>
+      <c r="H349" t="n">
+        <v>37</v>
+      </c>
+      <c r="I349" t="n">
+        <v>7</v>
+      </c>
+      <c r="J349" t="n">
+        <v>24</v>
+      </c>
+      <c r="K349" t="n">
+        <v>7</v>
+      </c>
+      <c r="L349" t="n">
+        <v>11</v>
+      </c>
+      <c r="M349" t="n">
+        <v>10</v>
+      </c>
+      <c r="N349" t="n">
+        <v>23</v>
+      </c>
+      <c r="O349" t="n">
+        <v>15</v>
+      </c>
+      <c r="P349" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q349" t="n">
+        <v>10</v>
+      </c>
+      <c r="R349" t="n">
+        <v>16</v>
+      </c>
+      <c r="S349" t="n">
+        <v>16</v>
+      </c>
+      <c r="T349" t="n">
+        <v>4</v>
+      </c>
+      <c r="U349" t="inlineStr">
+        <is>
+          <t>2487932</t>
+        </is>
+      </c>
+      <c r="V349" t="n">
+        <v>70</v>
+      </c>
+      <c r="W349" t="n">
+        <v>75.84</v>
+      </c>
+      <c r="X349" t="n">
+        <v>0.8966244725738396</v>
+      </c>
+      <c r="Y349" t="n">
+        <v>65.84</v>
+      </c>
+      <c r="Z349" t="n">
+        <v>103.2806804374241</v>
+      </c>
+      <c r="AA349" t="n">
+        <v>0.896516393442623</v>
+      </c>
+      <c r="AB349" t="n">
+        <v>104.3530113297555</v>
+      </c>
+      <c r="AC349" t="n">
+        <v>0.3225806451612903</v>
+      </c>
+      <c r="AD349" t="n">
+        <v>0.6764705882352942</v>
+      </c>
+      <c r="AE349" t="n">
+        <v>0.5076923076923077</v>
+      </c>
+      <c r="AF349" t="n">
+        <v>-1.072330892331465</v>
+      </c>
+      <c r="AG349" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="AH349" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="AI349" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B350" t="n">
+        <v>25</v>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="E350" t="n">
+        <v>200</v>
+      </c>
+      <c r="F350" t="n">
+        <v>85</v>
+      </c>
+      <c r="G350" t="n">
+        <v>24</v>
+      </c>
+      <c r="H350" t="n">
+        <v>35</v>
+      </c>
+      <c r="I350" t="n">
+        <v>8</v>
+      </c>
+      <c r="J350" t="n">
+        <v>31</v>
+      </c>
+      <c r="K350" t="n">
+        <v>13</v>
+      </c>
+      <c r="L350" t="n">
+        <v>20</v>
+      </c>
+      <c r="M350" t="n">
+        <v>10</v>
+      </c>
+      <c r="N350" t="n">
+        <v>27</v>
+      </c>
+      <c r="O350" t="n">
+        <v>22</v>
+      </c>
+      <c r="P350" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q350" t="n">
+        <v>12</v>
+      </c>
+      <c r="R350" t="n">
+        <v>24</v>
+      </c>
+      <c r="S350" t="n">
+        <v>21</v>
+      </c>
+      <c r="T350" t="n">
+        <v>0</v>
+      </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>2487929</t>
+        </is>
+      </c>
+      <c r="V350" t="n">
+        <v>68</v>
+      </c>
+      <c r="W350" t="n">
+        <v>86.8</v>
+      </c>
+      <c r="X350" t="n">
+        <v>0.9792626728110599</v>
+      </c>
+      <c r="Y350" t="n">
+        <v>76.8</v>
+      </c>
+      <c r="Z350" t="n">
+        <v>110.6770833333333</v>
+      </c>
+      <c r="AA350" t="n">
+        <v>0.8407517309594461</v>
+      </c>
+      <c r="AB350" t="n">
+        <v>90.81196581196582</v>
+      </c>
+      <c r="AC350" t="n">
+        <v>0.303030303030303</v>
+      </c>
+      <c r="AD350" t="n">
+        <v>0.8181818181818182</v>
+      </c>
+      <c r="AE350" t="n">
+        <v>0.5606060606060606</v>
+      </c>
+      <c r="AF350" t="n">
+        <v>19.86511752136752</v>
+      </c>
+      <c r="AG350" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="AH350" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="AI350" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B351" t="n">
+        <v>25</v>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="E351" t="n">
+        <v>200</v>
+      </c>
+      <c r="F351" t="n">
+        <v>85</v>
+      </c>
+      <c r="G351" t="n">
+        <v>22</v>
+      </c>
+      <c r="H351" t="n">
+        <v>44</v>
+      </c>
+      <c r="I351" t="n">
+        <v>7</v>
+      </c>
+      <c r="J351" t="n">
+        <v>19</v>
+      </c>
+      <c r="K351" t="n">
+        <v>20</v>
+      </c>
+      <c r="L351" t="n">
+        <v>26</v>
+      </c>
+      <c r="M351" t="n">
+        <v>6</v>
+      </c>
+      <c r="N351" t="n">
+        <v>25</v>
+      </c>
+      <c r="O351" t="n">
+        <v>19</v>
+      </c>
+      <c r="P351" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q351" t="n">
+        <v>11</v>
+      </c>
+      <c r="R351" t="n">
+        <v>30</v>
+      </c>
+      <c r="S351" t="n">
+        <v>25</v>
+      </c>
+      <c r="T351" t="n">
+        <v>0</v>
+      </c>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>2487927</t>
+        </is>
+      </c>
+      <c r="V351" t="n">
+        <v>98</v>
+      </c>
+      <c r="W351" t="n">
+        <v>85.44</v>
+      </c>
+      <c r="X351" t="n">
+        <v>0.9948501872659177</v>
+      </c>
+      <c r="Y351" t="n">
+        <v>79.44</v>
+      </c>
+      <c r="Z351" t="n">
+        <v>106.9989929506546</v>
+      </c>
+      <c r="AA351" t="n">
+        <v>1.040781648258284</v>
+      </c>
+      <c r="AB351" t="n">
+        <v>119.2794547224927</v>
+      </c>
+      <c r="AC351" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="AD351" t="n">
+        <v>0.6756756756756757</v>
+      </c>
+      <c r="AE351" t="n">
+        <v>0.4492753623188406</v>
+      </c>
+      <c r="AF351" t="n">
+        <v>-12.28046177183812</v>
+      </c>
+      <c r="AG351" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="AH351" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="AI351" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B352" t="n">
+        <v>26</v>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="E352" t="n">
+        <v>200</v>
+      </c>
+      <c r="F352" t="n">
+        <v>100</v>
+      </c>
+      <c r="G352" t="n">
+        <v>26</v>
+      </c>
+      <c r="H352" t="n">
+        <v>42</v>
+      </c>
+      <c r="I352" t="n">
+        <v>9</v>
+      </c>
+      <c r="J352" t="n">
+        <v>21</v>
+      </c>
+      <c r="K352" t="n">
+        <v>21</v>
+      </c>
+      <c r="L352" t="n">
+        <v>24</v>
+      </c>
+      <c r="M352" t="n">
+        <v>9</v>
+      </c>
+      <c r="N352" t="n">
+        <v>22</v>
+      </c>
+      <c r="O352" t="n">
+        <v>18</v>
+      </c>
+      <c r="P352" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q352" t="n">
+        <v>10</v>
+      </c>
+      <c r="R352" t="n">
+        <v>23</v>
+      </c>
+      <c r="S352" t="n">
+        <v>24</v>
+      </c>
+      <c r="T352" t="n">
+        <v>1</v>
+      </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>2487934</t>
+        </is>
+      </c>
+      <c r="V352" t="n">
+        <v>84</v>
+      </c>
+      <c r="W352" t="n">
+        <v>83.56</v>
+      </c>
+      <c r="X352" t="n">
+        <v>1.196744853997128</v>
+      </c>
+      <c r="Y352" t="n">
+        <v>74.56</v>
+      </c>
+      <c r="Z352" t="n">
+        <v>134.1201716738197</v>
+      </c>
+      <c r="AA352" t="n">
+        <v>0.9896324222431668</v>
+      </c>
+      <c r="AB352" t="n">
+        <v>109.261186264308</v>
+      </c>
+      <c r="AC352" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD352" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="AE352" t="n">
+        <v>0.543859649122807</v>
+      </c>
+      <c r="AF352" t="n">
+        <v>24.8589854095117</v>
+      </c>
+      <c r="AG352" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="AH352" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="AI352" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B353" t="n">
+        <v>26</v>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="E353" t="n">
+        <v>200</v>
+      </c>
+      <c r="F353" t="n">
+        <v>75</v>
+      </c>
+      <c r="G353" t="n">
+        <v>22</v>
+      </c>
+      <c r="H353" t="n">
+        <v>42</v>
+      </c>
+      <c r="I353" t="n">
+        <v>7</v>
+      </c>
+      <c r="J353" t="n">
+        <v>17</v>
+      </c>
+      <c r="K353" t="n">
+        <v>10</v>
+      </c>
+      <c r="L353" t="n">
+        <v>17</v>
+      </c>
+      <c r="M353" t="n">
+        <v>6</v>
+      </c>
+      <c r="N353" t="n">
+        <v>20</v>
+      </c>
+      <c r="O353" t="n">
+        <v>18</v>
+      </c>
+      <c r="P353" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q353" t="n">
+        <v>15</v>
+      </c>
+      <c r="R353" t="n">
+        <v>22</v>
+      </c>
+      <c r="S353" t="n">
+        <v>19</v>
+      </c>
+      <c r="T353" t="n">
+        <v>0</v>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>2487936</t>
+        </is>
+      </c>
+      <c r="V353" t="n">
+        <v>84</v>
+      </c>
+      <c r="W353" t="n">
+        <v>81.48</v>
+      </c>
+      <c r="X353" t="n">
+        <v>0.9204712812960235</v>
+      </c>
+      <c r="Y353" t="n">
+        <v>75.48</v>
+      </c>
+      <c r="Z353" t="n">
+        <v>99.36406995230524</v>
+      </c>
+      <c r="AA353" t="n">
+        <v>0.9726725335803613</v>
+      </c>
+      <c r="AB353" t="n">
+        <v>111.4649681528662</v>
+      </c>
+      <c r="AC353" t="n">
+        <v>0.2068965517241379</v>
+      </c>
+      <c r="AD353" t="n">
+        <v>0.6451612903225806</v>
+      </c>
+      <c r="AE353" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="AF353" t="n">
+        <v>-12.10089820056101</v>
+      </c>
+      <c r="AG353" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="AH353" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="AI353" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B354" t="n">
+        <v>26</v>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="E354" t="n">
+        <v>200</v>
+      </c>
+      <c r="F354" t="n">
+        <v>77</v>
+      </c>
+      <c r="G354" t="n">
+        <v>16</v>
+      </c>
+      <c r="H354" t="n">
+        <v>36</v>
+      </c>
+      <c r="I354" t="n">
+        <v>10</v>
+      </c>
+      <c r="J354" t="n">
+        <v>29</v>
+      </c>
+      <c r="K354" t="n">
+        <v>15</v>
+      </c>
+      <c r="L354" t="n">
+        <v>24</v>
+      </c>
+      <c r="M354" t="n">
+        <v>13</v>
+      </c>
+      <c r="N354" t="n">
+        <v>18</v>
+      </c>
+      <c r="O354" t="n">
+        <v>9</v>
+      </c>
+      <c r="P354" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q354" t="n">
+        <v>10</v>
+      </c>
+      <c r="R354" t="n">
+        <v>21</v>
+      </c>
+      <c r="S354" t="n">
+        <v>24</v>
+      </c>
+      <c r="T354" t="n">
+        <v>2</v>
+      </c>
+      <c r="U354" t="inlineStr">
+        <is>
+          <t>2487940</t>
+        </is>
+      </c>
+      <c r="V354" t="n">
+        <v>75</v>
+      </c>
+      <c r="W354" t="n">
+        <v>85.56</v>
+      </c>
+      <c r="X354" t="n">
+        <v>0.8999532491818607</v>
+      </c>
+      <c r="Y354" t="n">
+        <v>72.56</v>
+      </c>
+      <c r="Z354" t="n">
+        <v>106.1190738699008</v>
+      </c>
+      <c r="AA354" t="n">
+        <v>0.8449752140603877</v>
+      </c>
+      <c r="AB354" t="n">
+        <v>103.0786146234195</v>
+      </c>
+      <c r="AC354" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="AD354" t="n">
+        <v>0.5294117647058824</v>
+      </c>
+      <c r="AE354" t="n">
+        <v>0.4189189189189189</v>
+      </c>
+      <c r="AF354" t="n">
+        <v>3.040459246481305</v>
+      </c>
+      <c r="AG354" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="AH354" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="AI354" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B355" t="n">
+        <v>26</v>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="E355" t="n">
+        <v>200</v>
+      </c>
+      <c r="F355" t="n">
+        <v>69</v>
+      </c>
+      <c r="G355" t="n">
+        <v>13</v>
+      </c>
+      <c r="H355" t="n">
+        <v>31</v>
+      </c>
+      <c r="I355" t="n">
+        <v>9</v>
+      </c>
+      <c r="J355" t="n">
+        <v>25</v>
+      </c>
+      <c r="K355" t="n">
+        <v>16</v>
+      </c>
+      <c r="L355" t="n">
+        <v>30</v>
+      </c>
+      <c r="M355" t="n">
+        <v>11</v>
+      </c>
+      <c r="N355" t="n">
+        <v>25</v>
+      </c>
+      <c r="O355" t="n">
+        <v>14</v>
+      </c>
+      <c r="P355" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q355" t="n">
+        <v>18</v>
+      </c>
+      <c r="R355" t="n">
+        <v>22</v>
+      </c>
+      <c r="S355" t="n">
+        <v>23</v>
+      </c>
+      <c r="T355" t="n">
+        <v>2</v>
+      </c>
+      <c r="U355" t="inlineStr">
+        <is>
+          <t>2487939</t>
+        </is>
+      </c>
+      <c r="V355" t="n">
+        <v>80</v>
+      </c>
+      <c r="W355" t="n">
+        <v>87.2</v>
+      </c>
+      <c r="X355" t="n">
+        <v>0.7912844036697247</v>
+      </c>
+      <c r="Y355" t="n">
+        <v>76.2</v>
+      </c>
+      <c r="Z355" t="n">
+        <v>90.55118110236221</v>
+      </c>
+      <c r="AA355" t="n">
+        <v>0.9000900090009001</v>
+      </c>
+      <c r="AB355" t="n">
+        <v>108.283703302653</v>
+      </c>
+      <c r="AC355" t="n">
+        <v>0.3055555555555556</v>
+      </c>
+      <c r="AD355" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="AE355" t="n">
+        <v>0.4736842105263158</v>
+      </c>
+      <c r="AF355" t="n">
+        <v>-17.73252220029075</v>
+      </c>
+      <c r="AG355" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="AH355" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="AI355" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B356" t="n">
+        <v>26</v>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="E356" t="n">
+        <v>200</v>
+      </c>
+      <c r="F356" t="n">
+        <v>75</v>
+      </c>
+      <c r="G356" t="n">
+        <v>17</v>
+      </c>
+      <c r="H356" t="n">
+        <v>35</v>
+      </c>
+      <c r="I356" t="n">
+        <v>7</v>
+      </c>
+      <c r="J356" t="n">
+        <v>25</v>
+      </c>
+      <c r="K356" t="n">
+        <v>20</v>
+      </c>
+      <c r="L356" t="n">
+        <v>29</v>
+      </c>
+      <c r="M356" t="n">
+        <v>16</v>
+      </c>
+      <c r="N356" t="n">
+        <v>27</v>
+      </c>
+      <c r="O356" t="n">
+        <v>17</v>
+      </c>
+      <c r="P356" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q356" t="n">
+        <v>16</v>
+      </c>
+      <c r="R356" t="n">
+        <v>24</v>
+      </c>
+      <c r="S356" t="n">
+        <v>21</v>
+      </c>
+      <c r="T356" t="n">
+        <v>1</v>
+      </c>
+      <c r="U356" t="inlineStr">
+        <is>
+          <t>2487940</t>
+        </is>
+      </c>
+      <c r="V356" t="n">
+        <v>77</v>
+      </c>
+      <c r="W356" t="n">
+        <v>88.75999999999999</v>
+      </c>
+      <c r="X356" t="n">
+        <v>0.8449752140603877</v>
+      </c>
+      <c r="Y356" t="n">
+        <v>72.75999999999999</v>
+      </c>
+      <c r="Z356" t="n">
+        <v>103.0786146234195</v>
+      </c>
+      <c r="AA356" t="n">
+        <v>0.8999532491818607</v>
+      </c>
+      <c r="AB356" t="n">
+        <v>106.1190738699008</v>
+      </c>
+      <c r="AC356" t="n">
+        <v>0.4705882352941176</v>
+      </c>
+      <c r="AD356" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="AE356" t="n">
+        <v>0.581081081081081</v>
+      </c>
+      <c r="AF356" t="n">
+        <v>-3.040459246481305</v>
+      </c>
+      <c r="AG356" t="inlineStr">
+        <is>
+          <t>CACERES PATRIMONIO DE LA HUMANIDAD</t>
+        </is>
+      </c>
+      <c r="AH356" t="inlineStr">
+        <is>
+          <t>CLUB BALONCESTO TOLEDO BASKET</t>
+        </is>
+      </c>
+      <c r="AI356" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B357" t="n">
+        <v>26</v>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="E357" t="n">
+        <v>200</v>
+      </c>
+      <c r="F357" t="n">
+        <v>83</v>
+      </c>
+      <c r="G357" t="n">
+        <v>21</v>
+      </c>
+      <c r="H357" t="n">
+        <v>36</v>
+      </c>
+      <c r="I357" t="n">
+        <v>11</v>
+      </c>
+      <c r="J357" t="n">
+        <v>32</v>
+      </c>
+      <c r="K357" t="n">
+        <v>8</v>
+      </c>
+      <c r="L357" t="n">
+        <v>8</v>
+      </c>
+      <c r="M357" t="n">
+        <v>11</v>
+      </c>
+      <c r="N357" t="n">
+        <v>31</v>
+      </c>
+      <c r="O357" t="n">
+        <v>19</v>
+      </c>
+      <c r="P357" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q357" t="n">
+        <v>18</v>
+      </c>
+      <c r="R357" t="n">
+        <v>18</v>
+      </c>
+      <c r="S357" t="n">
+        <v>15</v>
+      </c>
+      <c r="T357" t="n">
+        <v>1</v>
+      </c>
+      <c r="U357" t="inlineStr">
+        <is>
+          <t>2487937</t>
+        </is>
+      </c>
+      <c r="V357" t="n">
+        <v>54</v>
+      </c>
+      <c r="W357" t="n">
+        <v>89.52000000000001</v>
+      </c>
+      <c r="X357" t="n">
+        <v>0.9271671134941911</v>
+      </c>
+      <c r="Y357" t="n">
+        <v>78.52000000000001</v>
+      </c>
+      <c r="Z357" t="n">
+        <v>105.7055527254203</v>
+      </c>
+      <c r="AA357" t="n">
+        <v>0.6493506493506493</v>
+      </c>
+      <c r="AB357" t="n">
+        <v>69.98444790046656</v>
+      </c>
+      <c r="AC357" t="n">
+        <v>0.3235294117647059</v>
+      </c>
+      <c r="AD357" t="n">
+        <v>0.8378378378378378</v>
+      </c>
+      <c r="AE357" t="n">
+        <v>0.5915492957746479</v>
+      </c>
+      <c r="AF357" t="n">
+        <v>35.7211048249537</v>
+      </c>
+      <c r="AG357" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH357" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="AI357" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B358" t="n">
+        <v>26</v>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="E358" t="n">
+        <v>200</v>
+      </c>
+      <c r="F358" t="n">
+        <v>80</v>
+      </c>
+      <c r="G358" t="n">
+        <v>15</v>
+      </c>
+      <c r="H358" t="n">
+        <v>29</v>
+      </c>
+      <c r="I358" t="n">
+        <v>11</v>
+      </c>
+      <c r="J358" t="n">
+        <v>33</v>
+      </c>
+      <c r="K358" t="n">
+        <v>17</v>
+      </c>
+      <c r="L358" t="n">
+        <v>27</v>
+      </c>
+      <c r="M358" t="n">
+        <v>15</v>
+      </c>
+      <c r="N358" t="n">
+        <v>25</v>
+      </c>
+      <c r="O358" t="n">
+        <v>16</v>
+      </c>
+      <c r="P358" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q358" t="n">
+        <v>15</v>
+      </c>
+      <c r="R358" t="n">
+        <v>24</v>
+      </c>
+      <c r="S358" t="n">
+        <v>22</v>
+      </c>
+      <c r="T358" t="n">
+        <v>2</v>
+      </c>
+      <c r="U358" t="inlineStr">
+        <is>
+          <t>2487939</t>
+        </is>
+      </c>
+      <c r="V358" t="n">
+        <v>69</v>
+      </c>
+      <c r="W358" t="n">
+        <v>88.88</v>
+      </c>
+      <c r="X358" t="n">
+        <v>0.9000900090009001</v>
+      </c>
+      <c r="Y358" t="n">
+        <v>73.88</v>
+      </c>
+      <c r="Z358" t="n">
+        <v>108.283703302653</v>
+      </c>
+      <c r="AA358" t="n">
+        <v>0.7912844036697247</v>
+      </c>
+      <c r="AB358" t="n">
+        <v>90.55118110236221</v>
+      </c>
+      <c r="AC358" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AD358" t="n">
+        <v>0.6944444444444444</v>
+      </c>
+      <c r="AE358" t="n">
+        <v>0.5263157894736842</v>
+      </c>
+      <c r="AF358" t="n">
+        <v>17.73252220029075</v>
+      </c>
+      <c r="AG358" t="inlineStr">
+        <is>
+          <t>COTO CÓRDOBA CB</t>
+        </is>
+      </c>
+      <c r="AH358" t="inlineStr">
+        <is>
+          <t>CASTILLO DE GORRAIZ VALLE DE EGÜES</t>
+        </is>
+      </c>
+      <c r="AI358" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B359" t="n">
+        <v>26</v>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="E359" t="n">
+        <v>200</v>
+      </c>
+      <c r="F359" t="n">
+        <v>88</v>
+      </c>
+      <c r="G359" t="n">
+        <v>31</v>
+      </c>
+      <c r="H359" t="n">
+        <v>53</v>
+      </c>
+      <c r="I359" t="n">
+        <v>5</v>
+      </c>
+      <c r="J359" t="n">
+        <v>12</v>
+      </c>
+      <c r="K359" t="n">
+        <v>11</v>
+      </c>
+      <c r="L359" t="n">
+        <v>19</v>
+      </c>
+      <c r="M359" t="n">
+        <v>7</v>
+      </c>
+      <c r="N359" t="n">
+        <v>24</v>
+      </c>
+      <c r="O359" t="n">
+        <v>18</v>
+      </c>
+      <c r="P359" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q359" t="n">
+        <v>12</v>
+      </c>
+      <c r="R359" t="n">
+        <v>25</v>
+      </c>
+      <c r="S359" t="n">
+        <v>21</v>
+      </c>
+      <c r="T359" t="n">
+        <v>3</v>
+      </c>
+      <c r="U359" t="inlineStr">
+        <is>
+          <t>2487938</t>
+        </is>
+      </c>
+      <c r="V359" t="n">
+        <v>91</v>
+      </c>
+      <c r="W359" t="n">
+        <v>85.36</v>
+      </c>
+      <c r="X359" t="n">
+        <v>1.030927835051547</v>
+      </c>
+      <c r="Y359" t="n">
+        <v>78.36</v>
+      </c>
+      <c r="Z359" t="n">
+        <v>112.3021949974477</v>
+      </c>
+      <c r="AA359" t="n">
+        <v>0.9964958388085853</v>
+      </c>
+      <c r="AB359" t="n">
+        <v>114.7251638930913</v>
+      </c>
+      <c r="AC359" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="AD359" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE359" t="n">
+        <v>0.4696969696969697</v>
+      </c>
+      <c r="AF359" t="n">
+        <v>-2.422968895643621</v>
+      </c>
+      <c r="AG359" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="AH359" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="AI359" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B360" t="n">
+        <v>26</v>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="E360" t="n">
+        <v>200</v>
+      </c>
+      <c r="F360" t="n">
+        <v>54</v>
+      </c>
+      <c r="G360" t="n">
+        <v>14</v>
+      </c>
+      <c r="H360" t="n">
+        <v>39</v>
+      </c>
+      <c r="I360" t="n">
+        <v>5</v>
+      </c>
+      <c r="J360" t="n">
+        <v>22</v>
+      </c>
+      <c r="K360" t="n">
+        <v>11</v>
+      </c>
+      <c r="L360" t="n">
+        <v>14</v>
+      </c>
+      <c r="M360" t="n">
+        <v>6</v>
+      </c>
+      <c r="N360" t="n">
+        <v>23</v>
+      </c>
+      <c r="O360" t="n">
+        <v>8</v>
+      </c>
+      <c r="P360" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q360" t="n">
+        <v>16</v>
+      </c>
+      <c r="R360" t="n">
+        <v>15</v>
+      </c>
+      <c r="S360" t="n">
+        <v>18</v>
+      </c>
+      <c r="T360" t="n">
+        <v>1</v>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>2487937</t>
+        </is>
+      </c>
+      <c r="V360" t="n">
+        <v>83</v>
+      </c>
+      <c r="W360" t="n">
+        <v>83.16</v>
+      </c>
+      <c r="X360" t="n">
+        <v>0.6493506493506493</v>
+      </c>
+      <c r="Y360" t="n">
+        <v>77.16</v>
+      </c>
+      <c r="Z360" t="n">
+        <v>69.98444790046656</v>
+      </c>
+      <c r="AA360" t="n">
+        <v>0.9271671134941911</v>
+      </c>
+      <c r="AB360" t="n">
+        <v>105.7055527254203</v>
+      </c>
+      <c r="AC360" t="n">
+        <v>0.1621621621621622</v>
+      </c>
+      <c r="AD360" t="n">
+        <v>0.6764705882352942</v>
+      </c>
+      <c r="AE360" t="n">
+        <v>0.4084507042253521</v>
+      </c>
+      <c r="AF360" t="n">
+        <v>-35.7211048249537</v>
+      </c>
+      <c r="AG360" t="inlineStr">
+        <is>
+          <t>CÍRCULO GIJÓN BALONCESTO</t>
+        </is>
+      </c>
+      <c r="AH360" t="inlineStr">
+        <is>
+          <t>CLÍNICA PONFERRADA SDP</t>
+        </is>
+      </c>
+      <c r="AI360" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B361" t="n">
+        <v>26</v>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="E361" t="n">
+        <v>200</v>
+      </c>
+      <c r="F361" t="n">
+        <v>84</v>
+      </c>
+      <c r="G361" t="n">
+        <v>26</v>
+      </c>
+      <c r="H361" t="n">
+        <v>37</v>
+      </c>
+      <c r="I361" t="n">
+        <v>6</v>
+      </c>
+      <c r="J361" t="n">
+        <v>29</v>
+      </c>
+      <c r="K361" t="n">
+        <v>14</v>
+      </c>
+      <c r="L361" t="n">
+        <v>19</v>
+      </c>
+      <c r="M361" t="n">
+        <v>11</v>
+      </c>
+      <c r="N361" t="n">
+        <v>23</v>
+      </c>
+      <c r="O361" t="n">
+        <v>18</v>
+      </c>
+      <c r="P361" t="n">
+        <v>8</v>
+      </c>
+      <c r="Q361" t="n">
+        <v>12</v>
+      </c>
+      <c r="R361" t="n">
+        <v>19</v>
+      </c>
+      <c r="S361" t="n">
+        <v>21</v>
+      </c>
+      <c r="T361" t="n">
+        <v>4</v>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>2487936</t>
+        </is>
+      </c>
+      <c r="V361" t="n">
+        <v>75</v>
+      </c>
+      <c r="W361" t="n">
+        <v>86.36</v>
+      </c>
+      <c r="X361" t="n">
+        <v>0.9726725335803613</v>
+      </c>
+      <c r="Y361" t="n">
+        <v>75.36</v>
+      </c>
+      <c r="Z361" t="n">
+        <v>111.4649681528662</v>
+      </c>
+      <c r="AA361" t="n">
+        <v>0.9204712812960235</v>
+      </c>
+      <c r="AB361" t="n">
+        <v>99.36406995230524</v>
+      </c>
+      <c r="AC361" t="n">
+        <v>0.3548387096774194</v>
+      </c>
+      <c r="AD361" t="n">
+        <v>0.7931034482758621</v>
+      </c>
+      <c r="AE361" t="n">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="AF361" t="n">
+        <v>12.10089820056101</v>
+      </c>
+      <c r="AG361" t="inlineStr">
+        <is>
+          <t>C.B. STARLABS MORÓN</t>
+        </is>
+      </c>
+      <c r="AH361" t="inlineStr">
+        <is>
+          <t>INSOLAC CAJA 87</t>
+        </is>
+      </c>
+      <c r="AI361" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B362" t="n">
+        <v>26</v>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="E362" t="n">
+        <v>200</v>
+      </c>
+      <c r="F362" t="n">
+        <v>73</v>
+      </c>
+      <c r="G362" t="n">
+        <v>10</v>
+      </c>
+      <c r="H362" t="n">
+        <v>29</v>
+      </c>
+      <c r="I362" t="n">
+        <v>12</v>
+      </c>
+      <c r="J362" t="n">
+        <v>30</v>
+      </c>
+      <c r="K362" t="n">
+        <v>17</v>
+      </c>
+      <c r="L362" t="n">
+        <v>20</v>
+      </c>
+      <c r="M362" t="n">
+        <v>10</v>
+      </c>
+      <c r="N362" t="n">
+        <v>18</v>
+      </c>
+      <c r="O362" t="n">
+        <v>13</v>
+      </c>
+      <c r="P362" t="n">
+        <v>10</v>
+      </c>
+      <c r="Q362" t="n">
+        <v>13</v>
+      </c>
+      <c r="R362" t="n">
+        <v>29</v>
+      </c>
+      <c r="S362" t="n">
+        <v>20</v>
+      </c>
+      <c r="T362" t="n">
+        <v>1</v>
+      </c>
+      <c r="U362" t="inlineStr">
+        <is>
+          <t>2487935</t>
+        </is>
+      </c>
+      <c r="V362" t="n">
+        <v>69</v>
+      </c>
+      <c r="W362" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="X362" t="n">
+        <v>0.9034653465346535</v>
+      </c>
+      <c r="Y362" t="n">
+        <v>70.8</v>
+      </c>
+      <c r="Z362" t="n">
+        <v>103.1073446327684</v>
+      </c>
+      <c r="AA362" t="n">
+        <v>0.7649667405764966</v>
+      </c>
+      <c r="AB362" t="n">
+        <v>88.23529411764706</v>
+      </c>
+      <c r="AC362" t="n">
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="AD362" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AE362" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="AF362" t="n">
+        <v>14.8720505151213</v>
+      </c>
+      <c r="AG362" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="AH362" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="AI362" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B363" t="n">
+        <v>26</v>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="E363" t="n">
+        <v>200</v>
+      </c>
+      <c r="F363" t="n">
+        <v>69</v>
+      </c>
+      <c r="G363" t="n">
+        <v>14</v>
+      </c>
+      <c r="H363" t="n">
+        <v>28</v>
+      </c>
+      <c r="I363" t="n">
+        <v>8</v>
+      </c>
+      <c r="J363" t="n">
+        <v>29</v>
+      </c>
+      <c r="K363" t="n">
+        <v>17</v>
+      </c>
+      <c r="L363" t="n">
+        <v>30</v>
+      </c>
+      <c r="M363" t="n">
+        <v>12</v>
+      </c>
+      <c r="N363" t="n">
+        <v>24</v>
+      </c>
+      <c r="O363" t="n">
+        <v>13</v>
+      </c>
+      <c r="P363" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q363" t="n">
+        <v>20</v>
+      </c>
+      <c r="R363" t="n">
+        <v>20</v>
+      </c>
+      <c r="S363" t="n">
+        <v>29</v>
+      </c>
+      <c r="T363" t="n">
+        <v>3</v>
+      </c>
+      <c r="U363" t="inlineStr">
+        <is>
+          <t>2487935</t>
+        </is>
+      </c>
+      <c r="V363" t="n">
+        <v>73</v>
+      </c>
+      <c r="W363" t="n">
+        <v>90.2</v>
+      </c>
+      <c r="X363" t="n">
+        <v>0.7649667405764966</v>
+      </c>
+      <c r="Y363" t="n">
+        <v>78.2</v>
+      </c>
+      <c r="Z363" t="n">
+        <v>88.23529411764706</v>
+      </c>
+      <c r="AA363" t="n">
+        <v>0.9034653465346535</v>
+      </c>
+      <c r="AB363" t="n">
+        <v>103.1073446327684</v>
+      </c>
+      <c r="AC363" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AD363" t="n">
+        <v>0.7058823529411765</v>
+      </c>
+      <c r="AE363" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="AF363" t="n">
+        <v>-14.8720505151213</v>
+      </c>
+      <c r="AG363" t="inlineStr">
+        <is>
+          <t>LOGROBASKET LOGI7</t>
+        </is>
+      </c>
+      <c r="AH363" t="inlineStr">
+        <is>
+          <t>JAEN PARAÍSO INTERIOR CB</t>
+        </is>
+      </c>
+      <c r="AI363" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B364" t="n">
+        <v>26</v>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="E364" t="n">
+        <v>200</v>
+      </c>
+      <c r="F364" t="n">
+        <v>91</v>
+      </c>
+      <c r="G364" t="n">
+        <v>18</v>
+      </c>
+      <c r="H364" t="n">
+        <v>38</v>
+      </c>
+      <c r="I364" t="n">
+        <v>14</v>
+      </c>
+      <c r="J364" t="n">
+        <v>27</v>
+      </c>
+      <c r="K364" t="n">
+        <v>13</v>
+      </c>
+      <c r="L364" t="n">
+        <v>28</v>
+      </c>
+      <c r="M364" t="n">
+        <v>12</v>
+      </c>
+      <c r="N364" t="n">
+        <v>23</v>
+      </c>
+      <c r="O364" t="n">
+        <v>17</v>
+      </c>
+      <c r="P364" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q364" t="n">
+        <v>14</v>
+      </c>
+      <c r="R364" t="n">
+        <v>22</v>
+      </c>
+      <c r="S364" t="n">
+        <v>25</v>
+      </c>
+      <c r="T364" t="n">
+        <v>3</v>
+      </c>
+      <c r="U364" t="inlineStr">
+        <is>
+          <t>2487938</t>
+        </is>
+      </c>
+      <c r="V364" t="n">
+        <v>88</v>
+      </c>
+      <c r="W364" t="n">
+        <v>91.31999999999999</v>
+      </c>
+      <c r="X364" t="n">
+        <v>0.9964958388085853</v>
+      </c>
+      <c r="Y364" t="n">
+        <v>79.31999999999999</v>
+      </c>
+      <c r="Z364" t="n">
+        <v>114.7251638930913</v>
+      </c>
+      <c r="AA364" t="n">
+        <v>1.030927835051547</v>
+      </c>
+      <c r="AB364" t="n">
+        <v>112.3021949974477</v>
+      </c>
+      <c r="AC364" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="AD364" t="n">
+        <v>0.7666666666666667</v>
+      </c>
+      <c r="AE364" t="n">
+        <v>0.5303030303030303</v>
+      </c>
+      <c r="AF364" t="n">
+        <v>2.422968895643621</v>
+      </c>
+      <c r="AG364" t="inlineStr">
+        <is>
+          <t>REINA PROTEÍNAS CLAVIJO</t>
+        </is>
+      </c>
+      <c r="AH364" t="inlineStr">
+        <is>
+          <t>CULTURAL Y DEPORTIVA LEONESA</t>
+        </is>
+      </c>
+      <c r="AI364" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Liga Regular "OESTE"</t>
+        </is>
+      </c>
+      <c r="B365" t="n">
+        <v>26</v>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="E365" t="n">
+        <v>200</v>
+      </c>
+      <c r="F365" t="n">
+        <v>84</v>
+      </c>
+      <c r="G365" t="n">
+        <v>25</v>
+      </c>
+      <c r="H365" t="n">
+        <v>45</v>
+      </c>
+      <c r="I365" t="n">
+        <v>5</v>
+      </c>
+      <c r="J365" t="n">
+        <v>16</v>
+      </c>
+      <c r="K365" t="n">
+        <v>19</v>
+      </c>
+      <c r="L365" t="n">
+        <v>27</v>
+      </c>
+      <c r="M365" t="n">
+        <v>8</v>
+      </c>
+      <c r="N365" t="n">
+        <v>18</v>
+      </c>
+      <c r="O365" t="n">
+        <v>12</v>
+      </c>
+      <c r="P365" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q365" t="n">
+        <v>12</v>
+      </c>
+      <c r="R365" t="n">
+        <v>24</v>
+      </c>
+      <c r="S365" t="n">
+        <v>23</v>
+      </c>
+      <c r="T365" t="n">
+        <v>2</v>
+      </c>
+      <c r="U365" t="inlineStr">
+        <is>
+          <t>2487934</t>
+        </is>
+      </c>
+      <c r="V365" t="n">
+        <v>100</v>
+      </c>
+      <c r="W365" t="n">
+        <v>84.88</v>
+      </c>
+      <c r="X365" t="n">
+        <v>0.9896324222431668</v>
+      </c>
+      <c r="Y365" t="n">
+        <v>76.88</v>
+      </c>
+      <c r="Z365" t="n">
+        <v>109.261186264308</v>
+      </c>
+      <c r="AA365" t="n">
+        <v>1.196744853997128</v>
+      </c>
+      <c r="AB365" t="n">
+        <v>134.1201716738197</v>
+      </c>
+      <c r="AC365" t="n">
+        <v>0.2666666666666667</v>
+      </c>
+      <c r="AD365" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="AE365" t="n">
+        <v>0.456140350877193</v>
+      </c>
+      <c r="AF365" t="n">
+        <v>-24.8589854095117</v>
+      </c>
+      <c r="AG365" t="inlineStr">
+        <is>
+          <t>UEMC BALONCESTO VALLADOLID</t>
+        </is>
+      </c>
+      <c r="AH365" t="inlineStr">
+        <is>
+          <t>BIELE ISB</t>
+        </is>
+      </c>
+      <c r="AI365" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
